--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>16452</v>
       </c>
       <c r="B7" t="n">
-        <v>58073</v>
+        <v>58336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1401,11 +1401,15 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>V316, Upl</t>
@@ -1462,6 +1466,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1473,12 +1478,12 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Lars-Thure Nordin</t>
+          <t>Gerard Malsher</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för hotade arter</t>
+          <t>Åtgärdsprogram för hotade arter, ÅGP gölgroda</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>16452</v>
       </c>
       <c r="B7" t="n">
-        <v>58336</v>
+        <v>58342</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>16452</v>
       </c>
       <c r="B7" t="n">
-        <v>58342</v>
+        <v>58345</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,7 +1370,7 @@
         <v>16452</v>
       </c>
       <c r="B7" t="n">
-        <v>58345</v>
+        <v>58346</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>64056680</v>
+        <v>69990870</v>
       </c>
       <c r="B8" t="n">
-        <v>57572</v>
+        <v>95519</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1501,60 +1501,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100119</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>316, Upl</t>
+          <t>Forsmark, kring telemasten vid Reningsverket, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675407.8965961811</v>
+        <v>675337.0926959377</v>
       </c>
       <c r="R8" t="n">
-        <v>6700370.90812204</v>
+        <v>6700379.361994122</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1578,7 +1559,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1588,7 +1569,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>1993-12-31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1596,6 +1577,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1604,26 +1590,35 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Igenväxande ruderatmark</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Zachariassen</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Zachariassen, Jannike Fagerlund, Ekoplan Ekologigruppen</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Mats Thuresson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69990870</v>
+        <v>72151914</v>
       </c>
       <c r="B9" t="n">
-        <v>95519</v>
+        <v>57140</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1636,37 +1631,61 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100088</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Forsmark, kring telemasten vid Reningsverket, Upl</t>
+          <t>12, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>675337.0926959377</v>
+        <v>675406.1571145536</v>
       </c>
       <c r="R9" t="n">
-        <v>6700379.361994122</v>
+        <v>6700365.874703395</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1690,27 +1709,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>2017-06-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1993-12-31</t>
+          <t>2017-06-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>Årlig uppföljningsinventering i samarbete med SKB. Observerades i samband med inventering av gölgroda</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1724,29 +1743,25 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Igenväxande ruderatmark</t>
+          <t>kalkgöl</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Jannike Fagerlund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mats Thuresson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Jannike Fagerlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>72151914</v>
+        <v>73078905</v>
       </c>
       <c r="B10" t="n">
         <v>57140</v>
@@ -1781,7 +1796,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1789,16 +1804,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1806,14 +1811,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>12, Upl</t>
+          <t>13a, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>675406.1571145536</v>
+        <v>675472.0445002537</v>
       </c>
       <c r="R10" t="n">
-        <v>6700365.874703395</v>
+        <v>6700213.156731391</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1840,27 +1845,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-06-14</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-06-14</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Årlig uppföljningsinventering i samarbete med SKB. Observerades i samband med inventering av gölgroda</t>
+          <t>Årlig uppföljningsinventering i samarbete med SKB. Fynd gjorts i samband med spelinventering av gölgroda</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1874,7 +1879,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>kalkgöl</t>
+          <t>göl med vassar</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1885,17 +1890,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jannike Fagerlund</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>73078905</v>
+        <v>73078571</v>
       </c>
       <c r="B11" t="n">
-        <v>57140</v>
+        <v>57577</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1908,26 +1913,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100088</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1937,7 +1942,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1981,22 +1986,22 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-05-28</t>
+          <t>2018-05-29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Årlig uppföljningsinventering i samarbete med SKB. Fynd gjorts i samband med spelinventering av gölgroda</t>
+          <t>Årlig uppföljningsinventering i samarbete med SKB. Fynd gjorts i samband med salamanderinventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2005,6 +2010,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2021,17 +2027,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Ellinor Scharin, Fingal Gyllang</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73078571</v>
+        <v>73078741</v>
       </c>
       <c r="B12" t="n">
-        <v>57577</v>
+        <v>57549</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2044,26 +2050,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2073,7 +2079,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>lampa</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2112,27 +2118,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2018-05-28</t>
+          <t>2018-05-16</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2018-05-29</t>
+          <t>2018-05-16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Årlig uppföljningsinventering i samarbete med SKB. Fynd gjorts i samband med salamanderinventering</t>
+          <t>Årlig uppföljningsinventering i samarbete med SKB. Fynd gjorts i samband med spelinventering av gölgroda</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2141,7 +2147,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2158,17 +2163,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ellinor Scharin, Fingal Gyllang</t>
+          <t>Jesper Arnström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>73078741</v>
+        <v>73078912</v>
       </c>
       <c r="B13" t="n">
-        <v>57549</v>
+        <v>44580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2181,21 +2186,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208245</v>
+        <v>102918</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Citronfläckad kärrtrollslända</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Leucorrhinia pectoralis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Charpentier, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2208,6 +2213,9 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2215,14 +2223,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>13a, Upl</t>
+          <t>12, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>675472.0445002537</v>
+        <v>675406.1571145536</v>
       </c>
       <c r="R13" t="n">
-        <v>6700213.156731391</v>
+        <v>6700365.874703395</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2249,22 +2257,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2018-05-16</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2018-05-16</t>
+          <t>2018-05-28</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2278,12 +2286,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>göl med vassar</t>
+          <t>kalkgöl</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2294,17 +2303,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jesper Arnström</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>73078912</v>
+        <v>77979531</v>
       </c>
       <c r="B14" t="n">
-        <v>44580</v>
+        <v>56311</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2313,55 +2322,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102918</v>
+        <v>100067</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Citronfläckad kärrtrollslända</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucorrhinia pectoralis</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Charpentier, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>12, Upl</t>
+          <t>1458, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>675406.1571145536</v>
+        <v>675478.9928670353</v>
       </c>
       <c r="R14" t="n">
-        <v>6700365.874703395</v>
+        <v>6700212.998009352</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2388,27 +2395,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2018-05-28</t>
+          <t>2019-05-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2018-05-28</t>
+          <t>2019-05-24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Årlig uppföljningsinventering i samarbete med SKB. Fynd gjorts i samband med spelinventering av gölgroda</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2417,34 +2419,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>kalkgöl</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jannike Fagerlund</t>
+          <t>Erik Zachariassen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Erik Zachariassen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>77979531</v>
+        <v>80664636</v>
       </c>
       <c r="B15" t="n">
-        <v>56311</v>
+        <v>57585</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2453,20 +2449,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100067</v>
+        <v>208242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2474,32 +2470,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1458, Upl</t>
+          <t>13a, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>675478.9928670353</v>
+        <v>675472.0445002537</v>
       </c>
       <c r="R15" t="n">
-        <v>6700212.998009352</v>
+        <v>6700213.156731391</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2526,22 +2507,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
+          <t>2019-05-23</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
+          <t>2019-05-23</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Årlig uppföljningsinventering i samarbete med SKB. Inventeringstillfälle: vattensalamander</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2556,22 +2542,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Zachariassen</t>
+          <t>Emma Holmberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Zachariassen</t>
+          <t>Emma Holmberg, Anna-Sara Liman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80664636</v>
+        <v>80662245</v>
       </c>
       <c r="B16" t="n">
-        <v>57585</v>
+        <v>57572</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2580,28 +2566,57 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208242</v>
+        <v>100119</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Camerano, 1882)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>13a, Upl</t>
@@ -2638,27 +2653,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
+          <t>2019-05-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
+          <t>2019-05-24</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Årlig uppföljningsinventering i samarbete med SKB. Inventeringstillfälle: vattensalamander</t>
+          <t>Årlig uppföljningsinventering i samarbete med SKB. Inventeringstillfälle:spelinventering gölgroda</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2667,8 +2682,14 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>göl med vassar</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2678,17 +2699,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emma Holmberg, Anna-Sara Liman</t>
+          <t>Erik Zachariassen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>80662245</v>
+        <v>85813817</v>
       </c>
       <c r="B17" t="n">
-        <v>57572</v>
+        <v>57585</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2697,67 +2718,55 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>13a, Upl</t>
+          <t>Göl 12, Forsmarks kkv, bron över kanalen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>675472.0445002537</v>
+        <v>675403.9638131006</v>
       </c>
       <c r="R17" t="n">
-        <v>6700213.156731391</v>
+        <v>6700370.222954342</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2784,27 +2793,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Årlig uppföljningsinventering i samarbete med SKB. Inventeringstillfälle:spelinventering gölgroda</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2817,30 +2821,25 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>göl med vassar</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emma Holmberg</t>
+          <t>Magnus Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Zachariassen</t>
+          <t>Magnus Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>85813817</v>
+        <v>85813813</v>
       </c>
       <c r="B18" t="n">
-        <v>57585</v>
+        <v>57587</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2853,26 +2852,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -2967,10 +2966,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>85813813</v>
+        <v>85813879</v>
       </c>
       <c r="B19" t="n">
-        <v>57587</v>
+        <v>56730</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2979,42 +2978,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100141</v>
+        <v>102961</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3024,10 +3018,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>675403.9638131006</v>
+        <v>675404</v>
       </c>
       <c r="R19" t="n">
-        <v>6700370.222954342</v>
+        <v>6700370</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -3054,22 +3048,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3078,7 +3062,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3097,10 +3080,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>85813879</v>
+        <v>85813925</v>
       </c>
       <c r="B20" t="n">
-        <v>56730</v>
+        <v>54688</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3109,25 +3092,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102961</v>
+        <v>206063</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Ål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Anguilla anguilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3135,24 +3118,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Göl 12, Forsmarks kkv, bron över kanalen, Upl</t>
+          <t>Göl 13A, Forsmarks kkv, bron över kanalen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>675404</v>
+        <v>675476.806575259</v>
       </c>
       <c r="R20" t="n">
-        <v>6700370</v>
+        <v>6700206.95281553</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -3182,17 +3170,28 @@
           <t>2020-05-25</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-05-25</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3211,10 +3210,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>85813925</v>
+        <v>85813809</v>
       </c>
       <c r="B21" t="n">
-        <v>54688</v>
+        <v>57549</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3223,20 +3222,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>206063</v>
+        <v>208245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ål</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anguilla anguilla</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3258,20 +3257,20 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Göl 13A, Forsmarks kkv, bron över kanalen, Upl</t>
+          <t>Göl 12, Forsmarks kkv, bron över kanalen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>675476.806575259</v>
+        <v>675403.9638131006</v>
       </c>
       <c r="R21" t="n">
-        <v>6700206.95281553</v>
+        <v>6700370.222954342</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -3298,7 +3297,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-05-25</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3308,7 +3307,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-05-25</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3341,67 +3340,67 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>85813809</v>
+        <v>64056681</v>
       </c>
       <c r="B22" t="n">
-        <v>57549</v>
+        <v>57572</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>100119</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>(Camerano, 1882)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Göl 12, Forsmarks kkv, bron över kanalen, Upl</t>
+          <t>1458, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>675403.9638131006</v>
+        <v>675478.9928670353</v>
       </c>
       <c r="R22" t="n">
-        <v>6700370.222954342</v>
+        <v>6700212.998009352</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3428,7 +3427,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3438,7 +3437,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3447,31 +3446,30 @@
         </is>
       </c>
       <c r="AD22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Magnus Nilsson</t>
+          <t>Erik Zachariassen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Nilsson</t>
+          <t>Erik Zachariassen, Jannike Fagerlund, Ekoplan Ekologigruppen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>64056681</v>
+        <v>21451</v>
       </c>
       <c r="B23" t="n">
         <v>57572</v>
@@ -3505,36 +3503,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1458, Upl</t>
+          <t>SVID1458. Forsmark, C-gölen intill reningsverket, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>675478.9928670353</v>
+        <v>675478.051446066</v>
       </c>
       <c r="R23" t="n">
-        <v>6700212.998009352</v>
+        <v>6700211.962554575</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3558,7 +3539,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>2009-05-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3568,12 +3549,17 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2016-06-13</t>
+          <t>2009-05-25</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Eftersökt men ej noterad. Inventerad av Beatrice Lindgren.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3588,67 +3574,78 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Zachariassen</t>
+          <t>Lars-Thure Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Zachariassen, Jannike Fagerlund, Ekoplan Ekologigruppen</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Via Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>73078576</v>
+        <v>87645788</v>
       </c>
       <c r="B24" t="n">
-        <v>57587</v>
+        <v>56411</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100141</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>13a, Upl</t>
+          <t>Forsmark, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>675472.0445002537</v>
+        <v>675386.7712825494</v>
       </c>
       <c r="R24" t="n">
-        <v>6700213.156731391</v>
+        <v>6700192.698154352</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3675,17 +3672,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2018-05-28</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2018-05-29</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3693,88 +3690,82 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Årlig uppföljningsinventering i samarbete med SKB. Inventeringstillfälle: vattensalamander</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>göl med vassar</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jannike Fagerlund</t>
+          <t>Stina Hällholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ellinor Scharin, Fingal Gyllang</t>
+          <t>Stina Hällholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>21451</v>
+        <v>89737419</v>
       </c>
       <c r="B25" t="n">
-        <v>57572</v>
+        <v>57549</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100119</v>
+        <v>208245</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>SVID1458. Forsmark, C-gölen intill reningsverket, Upl</t>
+          <t>12 Liten sjö öster om gamla reningsverket, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>675478.051446066</v>
+        <v>675406.1571145536</v>
       </c>
       <c r="R25" t="n">
-        <v>6700211.962554575</v>
+        <v>6700365.874703395</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3798,7 +3789,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2009-05-25</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3808,7 +3799,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2009-05-25</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3818,11 +3809,11 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Eftersökt men ej noterad. Inventerad av Beatrice Lindgren.</t>
+          <t>Nattinventering efter större vattensalamander</t>
         </is>
       </c>
       <c r="AD25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
@@ -3833,26 +3824,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars-Thure Nordin</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Lars-Thure Nordin</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Magnus Nilsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>87645788</v>
+        <v>99304776</v>
       </c>
       <c r="B26" t="n">
-        <v>56411</v>
+        <v>56717</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3865,16 +3852,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>103008</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3887,27 +3874,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Forsmark, Upl</t>
+          <t>FM-10198-2-22, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>675386.7712825494</v>
+        <v>675286.1734591905</v>
       </c>
       <c r="R26" t="n">
-        <v>6700192.698154352</v>
+        <v>6700304.64051431</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3931,22 +3910,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2003-05-16</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>03:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2003-05-16</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>03:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3961,22 +3940,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Stina Hällholm</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Stina Hällholm</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89737419</v>
+        <v>99318428</v>
       </c>
       <c r="B27" t="n">
-        <v>57549</v>
+        <v>56521</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3985,46 +3968,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>208245</v>
+        <v>103035</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>12 Liten sjö öster om gamla reningsverket, Upl</t>
+          <t>FM-14267-5-89, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>675406.1571145536</v>
+        <v>675281.7804510443</v>
       </c>
       <c r="R27" t="n">
-        <v>6700365.874703395</v>
+        <v>6700323.730545319</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4048,27 +4030,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2003-04-28</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2003-04-28</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Nattinventering efter större vattensalamander</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4083,22 +4060,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Nilsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96876431</v>
+        <v>99318423</v>
       </c>
       <c r="B28" t="n">
-        <v>57572</v>
+        <v>55946</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4107,65 +4088,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100119</v>
+        <v>102963</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>13a, Upl</t>
+          <t>FM-14267-5-89, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>675472.0683941499</v>
+        <v>675281.7804510443</v>
       </c>
       <c r="R28" t="n">
-        <v>6700212.662938139</v>
+        <v>6700323.730545319</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4189,22 +4150,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2003-04-28</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2003-04-28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4219,22 +4180,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emma Holmberg</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Emma Holmberg, Lark Davis</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>99304776</v>
+        <v>99328900</v>
       </c>
       <c r="B29" t="n">
-        <v>56717</v>
+        <v>57007</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4243,20 +4208,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103008</v>
+        <v>103042</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4266,19 +4231,19 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>FM-10198-2-22, Upl</t>
+          <t>FM-19990-1-87, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>675286.1734591905</v>
+        <v>675300.2196980701</v>
       </c>
       <c r="R29" t="n">
-        <v>6700304.64051431</v>
+        <v>6700290.966397149</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4303,24 +4268,25 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2003-05-16</t>
+          <t>2007-06-12</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>03:50</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2003-05-16</t>
+          <t>2007-06-12</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>03:50</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4351,10 +4317,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>99318428</v>
+        <v>99341159</v>
       </c>
       <c r="B30" t="n">
-        <v>56521</v>
+        <v>57064</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4367,16 +4333,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103035</v>
+        <v>103055</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4391,14 +4357,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>FM-14267-5-89, Upl</t>
+          <t>FM-2-3-11, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>675281.7804510443</v>
+        <v>675278.3342199761</v>
       </c>
       <c r="R30" t="n">
-        <v>6700323.730545319</v>
+        <v>6700261.697000471</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4425,22 +4391,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2003-04-28</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2003-04-28</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4471,10 +4437,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>99318423</v>
+        <v>99365975</v>
       </c>
       <c r="B31" t="n">
-        <v>55946</v>
+        <v>56779</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4483,42 +4449,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102963</v>
+        <v>103037</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>FM-14267-5-89, Upl</t>
+          <t>FM-7106-3-37, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>675281.7804510443</v>
+        <v>675231.4017315002</v>
       </c>
       <c r="R31" t="n">
-        <v>6700323.730545319</v>
+        <v>6700360.889965601</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4545,22 +4511,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2003-04-28</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2003-04-28</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4591,10 +4557,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>99328900</v>
+        <v>99369904</v>
       </c>
       <c r="B32" t="n">
-        <v>57007</v>
+        <v>56672</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4603,42 +4569,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103042</v>
+        <v>103006</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Rörsångare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Acrocephalus scirpaceus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hermann, 1804)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>FM-19990-1-87, Upl</t>
+          <t>FM-8-3-36, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>675300.2196980701</v>
+        <v>675289.9508042063</v>
       </c>
       <c r="R32" t="n">
-        <v>6700290.966397149</v>
+        <v>6700400.839089851</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4666,22 +4632,22 @@
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2007-06-12</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2007-06-12</t>
+          <t>2018-05-30</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4712,10 +4678,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>99341159</v>
+        <v>99365968</v>
       </c>
       <c r="B33" t="n">
-        <v>57064</v>
+        <v>56717</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4728,21 +4694,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103055</v>
+        <v>103008</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4752,14 +4718,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>FM-2-3-11, Upl</t>
+          <t>FM-7106-3-37, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>675278.3342199761</v>
+        <v>675231.4017315002</v>
       </c>
       <c r="R33" t="n">
-        <v>6700261.697000471</v>
+        <v>6700360.889965601</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4832,10 +4798,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>99365975</v>
+        <v>99351854</v>
       </c>
       <c r="B34" t="n">
-        <v>56779</v>
+        <v>55903</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4844,20 +4810,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103037</v>
+        <v>102961</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4867,19 +4833,19 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>FM-7106-3-37, Upl</t>
+          <t>FM-2-3-11, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>675231.4017315002</v>
+        <v>675278.3342199761</v>
       </c>
       <c r="R34" t="n">
-        <v>6700360.889965601</v>
+        <v>6700261.697000471</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4906,22 +4872,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2018-05-30</t>
+          <t>2013-05-28</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>03:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2018-05-30</t>
+          <t>2013-05-28</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>03:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4952,10 +4918,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>99369904</v>
+        <v>101130573</v>
       </c>
       <c r="B35" t="n">
-        <v>56672</v>
+        <v>96367</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4964,42 +4930,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103006</v>
+        <v>219874</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rörsångare</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Acrocephalus scirpaceus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hermann, 1804)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>FM-8-3-36, Upl</t>
+          <t>Barrskog Forsmark, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>675289.9508042063</v>
+        <v>675411.1282053352</v>
       </c>
       <c r="R35" t="n">
-        <v>6700400.839089851</v>
+        <v>6700468.068878242</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -5024,10 +4994,9 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2018-05-30</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -5037,7 +5006,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2018-05-30</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5045,38 +5014,40 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Troligen fler plantor</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Mathias Andersson</t>
+          <t>Stina Hällholm</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Via Mathias Andersson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Forsmark platsundersökning</t>
-        </is>
-      </c>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>99365968</v>
+        <v>101130566</v>
       </c>
       <c r="B36" t="n">
-        <v>56717</v>
+        <v>96356</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5085,42 +5056,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103008</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>FM-7106-3-37, Upl</t>
+          <t>Barrskog Forsmark, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>675231.4017315002</v>
+        <v>675411.1282053352</v>
       </c>
       <c r="R36" t="n">
-        <v>6700360.889965601</v>
+        <v>6700468.068878242</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -5147,7 +5122,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2018-05-30</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -5157,7 +5132,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2018-05-30</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5165,38 +5140,40 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Minst 70-80 stycken plantor, möjligen ännu fler</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mathias Andersson</t>
+          <t>Stina Hällholm</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Via Mathias Andersson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forsmark platsundersökning</t>
-        </is>
-      </c>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>99351854</v>
+        <v>101283900</v>
       </c>
       <c r="B37" t="n">
-        <v>55903</v>
+        <v>56540</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5209,21 +5186,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102961</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5231,16 +5208,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>FM-2-3-11, Upl</t>
+          <t>FM-9969-5-16, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>675278.3342199761</v>
+        <v>675389.2057918769</v>
       </c>
       <c r="R37" t="n">
-        <v>6700261.697000471</v>
+        <v>6700285.865484138</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -5265,24 +5250,25 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2013-05-28</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>03:41</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2013-05-28</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>03:41</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5302,21 +5288,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Via Mathias Andersson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Forsmark platsundersökning</t>
-        </is>
-      </c>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>101130573</v>
+        <v>103952240</v>
       </c>
       <c r="B38" t="n">
-        <v>96367</v>
+        <v>57572</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5325,49 +5307,60 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219874</v>
+        <v>100119</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barrskog Forsmark, Upl</t>
+          <t>12, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>675411.1282053352</v>
+        <v>675413.9439997618</v>
       </c>
       <c r="R38" t="n">
-        <v>6700468.068878242</v>
+        <v>6700379.119487345</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5391,7 +5384,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5401,7 +5394,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5411,7 +5404,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Troligen fler plantor</t>
+          <t>Årlig uppföljningsinventering i samarbete med SKB. Inventeringstillfälle:spelinventering gölgroda</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5420,29 +5413,32 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Stina Hällholm</t>
+          <t>Emma Holmberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Stina Hällholm</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Emma Holmberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SKB groddjursinventeringar </t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>101130566</v>
+        <v>103952158</v>
       </c>
       <c r="B39" t="n">
-        <v>96356</v>
+        <v>57572</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5451,49 +5447,60 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219847</v>
+        <v>100119</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Barrskog Forsmark, Upl</t>
+          <t>13b, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>675411.1282053352</v>
+        <v>675483.1338892153</v>
       </c>
       <c r="R39" t="n">
-        <v>6700468.068878242</v>
+        <v>6700117.176921089</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5517,7 +5524,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5527,7 +5534,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5537,7 +5544,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minst 70-80 stycken plantor, möjligen ännu fler</t>
+          <t>Årlig uppföljningsinventering i samarbete med SKB. Inventeringstillfälle:spelinventering gölgroda</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5546,29 +5553,32 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Stina Hällholm</t>
+          <t>Emma Holmberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Stina Hällholm</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Emma Holmberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SKB groddjursinventeringar </t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>101283900</v>
+        <v>103952235</v>
       </c>
       <c r="B40" t="n">
-        <v>56540</v>
+        <v>57587</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5577,53 +5587,60 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>100141</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>FM-9969-5-16, Upl</t>
+          <t>12, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>675389.2057918769</v>
+        <v>675413.9439997618</v>
       </c>
       <c r="R40" t="n">
-        <v>6700285.865484138</v>
+        <v>6700379.119487345</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5645,25 +5662,29 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Årlig uppföljningsinventering i samarbete med SKB. Inventeringstillfälle:spelinventering gölgroda</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5678,22 +5699,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Mathias Andersson</t>
+          <t>Emma Holmberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mathias Andersson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Emma Holmberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SKB groddjursinventeringar </t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>103952240</v>
+        <v>103952236</v>
       </c>
       <c r="B41" t="n">
-        <v>57572</v>
+        <v>57585</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5702,30 +5727,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5779,7 +5804,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -5789,7 +5814,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5830,10 +5855,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>103952158</v>
+        <v>103952241</v>
       </c>
       <c r="B42" t="n">
-        <v>57572</v>
+        <v>57577</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5842,25 +5867,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100119</v>
+        <v>208249</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5885,14 +5910,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>13b, Upl</t>
+          <t>12, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>675483.1338892153</v>
+        <v>675413.9439997618</v>
       </c>
       <c r="R42" t="n">
-        <v>6700117.176921089</v>
+        <v>6700379.119487345</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5970,10 +5995,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>103952235</v>
+        <v>99369916</v>
       </c>
       <c r="B43" t="n">
-        <v>57587</v>
+        <v>56866</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5982,60 +6007,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100141</v>
+        <v>102993</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Svart rödstjärt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Phoenicurus ochruros</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(S.G. Gmelin, 1774)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>12, Upl</t>
+          <t>FM-8-3-36, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>675413.9439997618</v>
+        <v>675289.9508042063</v>
       </c>
       <c r="R43" t="n">
-        <v>6700379.119487345</v>
+        <v>6700400.839089851</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6057,29 +6067,25 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2013-05-28</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>03:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2013-05-28</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Årlig uppföljningsinventering i samarbete med SKB. Inventeringstillfälle:spelinventering gölgroda</t>
+          <t>03:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6094,26 +6100,26 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emma Holmberg</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emma Holmberg</t>
+          <t>Via Mathias Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKB groddjursinventeringar </t>
+          <t>Forsmark platsundersökning</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>103952236</v>
+        <v>113423567</v>
       </c>
       <c r="B44" t="n">
-        <v>57585</v>
+        <v>58073</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6122,57 +6128,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>208242</v>
+        <v>100119</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Camerano, 1882)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>12, Upl</t>
+          <t>13b, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>675413.9439997618</v>
+        <v>675438</v>
       </c>
       <c r="R44" t="n">
-        <v>6700379.119487345</v>
+        <v>6700154</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -6199,27 +6186,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Årlig uppföljningsinventering i samarbete med SKB. Inventeringstillfälle:spelinventering gölgroda</t>
+          <t>OBS: Nollobservation</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6234,26 +6211,26 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emma Holmberg</t>
+          <t>Michael Wzdulski</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emma Holmberg</t>
+          <t>Michael Wzdulski</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKB groddjursinventeringar </t>
+          <t>Forsmark platsundersökning</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>103952241</v>
+        <v>113423556</v>
       </c>
       <c r="B45" t="n">
-        <v>57577</v>
+        <v>58073</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6262,57 +6239,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>208249</v>
+        <v>100119</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Camerano, 1882)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>12, Upl</t>
+          <t>13a, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>675413.9439997618</v>
+        <v>675491</v>
       </c>
       <c r="R45" t="n">
-        <v>6700379.119487345</v>
+        <v>6700209</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -6339,27 +6297,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Årlig uppföljningsinventering i samarbete med SKB. Inventeringstillfälle:spelinventering gölgroda</t>
+          <t>OBS: Nollobservation</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6374,26 +6322,26 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emma Holmberg</t>
+          <t>Michael Wzdulski</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emma Holmberg</t>
+          <t>Michael Wzdulski</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKB groddjursinventeringar </t>
+          <t>Forsmark platsundersökning</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>99369916</v>
+        <v>113423776</v>
       </c>
       <c r="B46" t="n">
-        <v>56866</v>
+        <v>58089</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6402,25 +6350,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102993</v>
+        <v>100141</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart rödstjärt</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phoenicurus ochruros</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.G. Gmelin, 1774)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6428,19 +6376,29 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>FM-8-3-36, Upl</t>
+          <t>12, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>675289.9508042063</v>
+        <v>675399</v>
       </c>
       <c r="R46" t="n">
-        <v>6700400.839089851</v>
+        <v>6700375</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6462,25 +6420,19 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2013-05-28</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>03:41</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2013-05-28</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>03:41</t>
+          <t>2023-08-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>OBS: Yngel innanför stängslet</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6495,12 +6447,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mathias Andersson</t>
+          <t>Michael Wzdulski</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Via Mathias Andersson</t>
+          <t>Michael Wzdulski</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -6511,10 +6463,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113423567</v>
+        <v>113423851</v>
       </c>
       <c r="B47" t="n">
-        <v>58073</v>
+        <v>58089</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6523,38 +6475,57 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100119</v>
+        <v>100141</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>13b, Upl</t>
+          <t>12, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>675438</v>
+        <v>675369</v>
       </c>
       <c r="R47" t="n">
-        <v>6700154</v>
+        <v>6700370</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -6591,7 +6562,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>OBS: Nollobservation</t>
+          <t>OBS: Obestämt kön</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6622,7 +6593,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113423556</v>
+        <v>113423599</v>
       </c>
       <c r="B48" t="n">
         <v>58073</v>
@@ -6655,17 +6626,31 @@
           <t>(Camerano, 1882)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>13a, Upl</t>
+          <t>12, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>675491</v>
+        <v>675386</v>
       </c>
       <c r="R48" t="n">
-        <v>6700209</v>
+        <v>6700348</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -6692,17 +6677,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>OBS: Nollobservation</t>
+          <t>OBS: Semidadult / Fjolårsunge</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6733,10 +6718,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113423776</v>
+        <v>113423555</v>
       </c>
       <c r="B49" t="n">
-        <v>58089</v>
+        <v>58073</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6745,52 +6730,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Camerano, 1882)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>12, Upl</t>
+          <t>13b, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>675399</v>
+        <v>675446</v>
       </c>
       <c r="R49" t="n">
-        <v>6700375</v>
+        <v>6700153</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -6817,17 +6788,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>OBS: Yngel innanför stängslet</t>
+          <t>OBS: Nollobservation</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6858,10 +6829,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113423851</v>
+        <v>113424165</v>
       </c>
       <c r="B50" t="n">
-        <v>58089</v>
+        <v>58050</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6874,31 +6845,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -6917,10 +6888,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>675369</v>
+        <v>675436</v>
       </c>
       <c r="R50" t="n">
-        <v>6700370</v>
+        <v>6700329</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6947,17 +6918,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>OBS: Obestämt kön</t>
+          <t>Utanför hägnad</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6988,7 +6959,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113423599</v>
+        <v>113423569</v>
       </c>
       <c r="B51" t="n">
         <v>58073</v>
@@ -7021,31 +6992,17 @@
           <t>(Camerano, 1882)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>12, Upl</t>
+          <t>13a, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>675386</v>
+        <v>675466</v>
       </c>
       <c r="R51" t="n">
-        <v>6700348</v>
+        <v>6700250</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -7072,17 +7029,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>OBS: Semidadult / Fjolårsunge</t>
+          <t>OBS: Nollobservation</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7113,10 +7070,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113423555</v>
+        <v>113423796</v>
       </c>
       <c r="B52" t="n">
-        <v>58073</v>
+        <v>58089</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7125,38 +7082,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100119</v>
+        <v>100141</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>13b, Upl</t>
+          <t>13a, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>675446</v>
+        <v>675461</v>
       </c>
       <c r="R52" t="n">
-        <v>6700153</v>
+        <v>6700203</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -7193,7 +7150,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>OBS: Nollobservation</t>
+          <t>OBS: nollobservation</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7224,10 +7181,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113424165</v>
+        <v>113423712</v>
       </c>
       <c r="B53" t="n">
-        <v>58050</v>
+        <v>58073</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7236,40 +7193,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>208245</v>
+        <v>100119</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7283,10 +7245,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>675436</v>
+        <v>675404</v>
       </c>
       <c r="R53" t="n">
-        <v>6700329</v>
+        <v>6700380</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -7313,17 +7275,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Utanför hägnad</t>
+          <t>Snok, fisk</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7354,7 +7316,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113423569</v>
+        <v>113423565</v>
       </c>
       <c r="B54" t="n">
         <v>58073</v>
@@ -7390,14 +7352,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>13a, Upl</t>
+          <t>12, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>675466</v>
+        <v>675369</v>
       </c>
       <c r="R54" t="n">
-        <v>6700250</v>
+        <v>6700370</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -7465,7 +7427,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113423796</v>
+        <v>113423781</v>
       </c>
       <c r="B55" t="n">
         <v>58089</v>
@@ -7501,14 +7463,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>13a, Upl</t>
+          <t>12, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>675461</v>
+        <v>675420</v>
       </c>
       <c r="R55" t="n">
-        <v>6700203</v>
+        <v>6700358</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -7535,12 +7497,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7576,7 +7538,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113423712</v>
+        <v>113423730</v>
       </c>
       <c r="B56" t="n">
         <v>58073</v>
@@ -7611,7 +7573,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -7640,10 +7602,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>675404</v>
+        <v>675378</v>
       </c>
       <c r="R56" t="n">
-        <v>6700380</v>
+        <v>6700370</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -7670,17 +7632,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Snok, fisk</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7711,10 +7668,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113423565</v>
+        <v>113423928</v>
       </c>
       <c r="B57" t="n">
-        <v>58073</v>
+        <v>58086</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7723,38 +7680,52 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>12, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>675369</v>
+        <v>675399</v>
       </c>
       <c r="R57" t="n">
-        <v>6700370</v>
+        <v>6700379</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -7781,17 +7752,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>OBS: Nollobservation</t>
+          <t>Yngel innanför stängsel, obestämt kön</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7822,10 +7793,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113423781</v>
+        <v>116387908</v>
       </c>
       <c r="B58" t="n">
-        <v>58089</v>
+        <v>56335</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7838,34 +7809,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100141</v>
+        <v>100045</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>12, Upl</t>
+          <t>13a, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>675420</v>
+        <v>675461</v>
       </c>
       <c r="R58" t="n">
-        <v>6700358</v>
+        <v>6700203</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -7892,17 +7875,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>OBS: nollobservation</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7917,398 +7905,15 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Michael Wzdulski</t>
+          <t>Mathias Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Michael Wzdulski</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forsmark platsundersökning</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>113423730</v>
-      </c>
-      <c r="B59" t="n">
-        <v>58073</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>100119</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Gölgroda</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Pelophylax lessonae</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Camerano, 1882)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>12, Upl</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>675378</v>
-      </c>
-      <c r="R59" t="n">
-        <v>6700370</v>
-      </c>
-      <c r="S59" t="n">
-        <v>50</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Östhammar</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Forsmark</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Michael Wzdulski</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Michael Wzdulski</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Forsmark platsundersökning</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>113423928</v>
-      </c>
-      <c r="B60" t="n">
-        <v>58086</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>208242</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Lissotriton vulgaris</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>12, Upl</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>675399</v>
-      </c>
-      <c r="R60" t="n">
-        <v>6700379</v>
-      </c>
-      <c r="S60" t="n">
-        <v>50</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Östhammar</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Forsmark</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2023-08-23</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2023-08-23</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Yngel innanför stängsel, obestämt kön</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Michael Wzdulski</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Michael Wzdulski</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Forsmark platsundersökning</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>116387908</v>
-      </c>
-      <c r="B61" t="n">
-        <v>56335</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>100045</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Sångsvan</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Cygnus cygnus</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>13a, Upl</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>675461</v>
-      </c>
-      <c r="R61" t="n">
-        <v>6700203</v>
-      </c>
-      <c r="S61" t="n">
-        <v>50</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Östhammar</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Forsmark</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
           <t>Mathias Andersson</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Mathias Andersson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -1483,7 +1483,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för hotade arter, ÅGP gölgroda</t>
+          <t>ÅGP gölgroda</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -21042,7 +21042,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130050578</v>
+        <v>130047148</v>
       </c>
       <c r="B162" t="n">
         <v>58612</v>
@@ -21092,7 +21092,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -21101,10 +21101,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>675403</v>
+        <v>675430</v>
       </c>
       <c r="R162" t="n">
-        <v>6700428</v>
+        <v>6700324</v>
       </c>
       <c r="S162" t="n">
         <v>1</v>
@@ -21129,14 +21129,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>length:68mm|bodymass:6g (same size 6)</t>
+        </is>
+      </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
@@ -21172,10 +21177,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130050779</v>
+        <v>130047393</v>
       </c>
       <c r="B163" t="n">
-        <v>56664</v>
+        <v>58612</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -21183,21 +21188,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>208257</v>
+        <v>100141</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -21210,21 +21215,31 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>675375</v>
+        <v>675430</v>
       </c>
       <c r="R163" t="n">
-        <v>6700315</v>
+        <v>6700409</v>
       </c>
       <c r="S163" t="n">
         <v>1</v>
@@ -21249,14 +21264,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>length:70mm|bodymass:5g (same size 2)</t>
+        </is>
+      </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
@@ -21292,7 +21312,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130050542</v>
+        <v>130047387</v>
       </c>
       <c r="B164" t="n">
         <v>58612</v>
@@ -21332,12 +21352,17 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -21346,10 +21371,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>675370</v>
+        <v>675414</v>
       </c>
       <c r="R164" t="n">
-        <v>6700367</v>
+        <v>6700288</v>
       </c>
       <c r="S164" t="n">
         <v>1</v>
@@ -21374,14 +21399,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>length:76mm|bodymass:6g</t>
+        </is>
+      </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
@@ -21417,32 +21447,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130046353</v>
+        <v>130049447</v>
       </c>
       <c r="B165" t="n">
-        <v>58596</v>
+        <v>58609</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -21457,7 +21487,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -21471,10 +21506,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>675372</v>
+        <v>675366</v>
       </c>
       <c r="R165" t="n">
-        <v>6700346</v>
+        <v>6700382</v>
       </c>
       <c r="S165" t="n">
         <v>1</v>
@@ -21499,19 +21534,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>length:30mm|bodymass:2.6g (same size 3)</t>
-        </is>
-      </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
@@ -21547,32 +21577,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130046337</v>
+        <v>130049854</v>
       </c>
       <c r="B166" t="n">
-        <v>58596</v>
+        <v>58601</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100119</v>
+        <v>208249</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -21585,11 +21615,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N166" t="inlineStr">
         <is>
           <t>fälla</t>
@@ -21601,10 +21626,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>675435</v>
+        <v>675414</v>
       </c>
       <c r="R166" t="n">
-        <v>6700368</v>
+        <v>6700288</v>
       </c>
       <c r="S166" t="n">
         <v>1</v>
@@ -21629,19 +21654,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>length:33mm|bodymass:3.2g</t>
-        </is>
-      </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr">
@@ -21677,10 +21697,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>130047148</v>
+        <v>130049759</v>
       </c>
       <c r="B167" t="n">
-        <v>58612</v>
+        <v>58609</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -21688,21 +21708,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -21715,19 +21735,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -21739,7 +21749,7 @@
         <v>675430</v>
       </c>
       <c r="R167" t="n">
-        <v>6700324</v>
+        <v>6700409</v>
       </c>
       <c r="S167" t="n">
         <v>1</v>
@@ -21764,19 +21774,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X167" t="inlineStr">
-        <is>
-          <t>length:68mm|bodymass:6g (same size 6)</t>
-        </is>
-      </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
@@ -21812,10 +21817,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130047393</v>
+        <v>130049432</v>
       </c>
       <c r="B168" t="n">
-        <v>58612</v>
+        <v>58609</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -21823,21 +21828,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -21857,12 +21862,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -21871,10 +21876,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>675430</v>
+        <v>675371</v>
       </c>
       <c r="R168" t="n">
-        <v>6700409</v>
+        <v>6700345</v>
       </c>
       <c r="S168" t="n">
         <v>1</v>
@@ -21899,19 +21904,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X168" t="inlineStr">
-        <is>
-          <t>length:70mm|bodymass:5g (same size 2)</t>
-        </is>
-      </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AC168" t="inlineStr">
@@ -21947,10 +21947,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>130047387</v>
+        <v>130049843</v>
       </c>
       <c r="B169" t="n">
-        <v>58612</v>
+        <v>58601</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -21958,21 +21958,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100141</v>
+        <v>208249</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -21985,16 +21985,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N169" t="inlineStr">
         <is>
           <t>fälla</t>
@@ -22006,10 +21996,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>675414</v>
+        <v>675369</v>
       </c>
       <c r="R169" t="n">
-        <v>6700288</v>
+        <v>6700355</v>
       </c>
       <c r="S169" t="n">
         <v>1</v>
@@ -22034,19 +22024,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>length:76mm|bodymass:6g</t>
-        </is>
-      </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
@@ -22082,10 +22067,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>130049447</v>
+        <v>130049863</v>
       </c>
       <c r="B170" t="n">
-        <v>58609</v>
+        <v>58601</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -22093,21 +22078,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -22120,19 +22105,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -22141,10 +22116,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>675366</v>
+        <v>675382</v>
       </c>
       <c r="R170" t="n">
-        <v>6700382</v>
+        <v>6700441</v>
       </c>
       <c r="S170" t="n">
         <v>1</v>
@@ -22171,12 +22146,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AC170" t="inlineStr">
@@ -22212,10 +22187,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>130049854</v>
+        <v>130049532</v>
       </c>
       <c r="B171" t="n">
-        <v>58601</v>
+        <v>58609</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -22223,21 +22198,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -22250,9 +22225,19 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -22261,10 +22246,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>675414</v>
+        <v>675438</v>
       </c>
       <c r="R171" t="n">
-        <v>6700288</v>
+        <v>6700349</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -22291,12 +22276,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AC171" t="inlineStr">
@@ -22332,10 +22317,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>130049759</v>
+        <v>130049867</v>
       </c>
       <c r="B172" t="n">
-        <v>58609</v>
+        <v>58601</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -22343,21 +22328,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -22381,10 +22366,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>675430</v>
+        <v>675414</v>
       </c>
       <c r="R172" t="n">
-        <v>6700409</v>
+        <v>6700424</v>
       </c>
       <c r="S172" t="n">
         <v>1</v>
@@ -22411,12 +22396,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
@@ -22452,7 +22437,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>130049432</v>
+        <v>130049629</v>
       </c>
       <c r="B173" t="n">
         <v>58609</v>
@@ -22511,10 +22496,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>675371</v>
+        <v>675436</v>
       </c>
       <c r="R173" t="n">
-        <v>6700345</v>
+        <v>6700363</v>
       </c>
       <c r="S173" t="n">
         <v>1</v>
@@ -22541,12 +22526,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
@@ -22582,7 +22567,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>130049843</v>
+        <v>130049871</v>
       </c>
       <c r="B174" t="n">
         <v>58601</v>
@@ -22631,10 +22616,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>675369</v>
+        <v>675381</v>
       </c>
       <c r="R174" t="n">
-        <v>6700355</v>
+        <v>6700306</v>
       </c>
       <c r="S174" t="n">
         <v>1</v>
@@ -22661,12 +22646,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
@@ -22702,10 +22687,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>130049863</v>
+        <v>130049808</v>
       </c>
       <c r="B175" t="n">
-        <v>58601</v>
+        <v>58599</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -22713,21 +22698,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>208249</v>
+        <v>208250</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -22751,10 +22736,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>675382</v>
+        <v>675373</v>
       </c>
       <c r="R175" t="n">
-        <v>6700441</v>
+        <v>6700355</v>
       </c>
       <c r="S175" t="n">
         <v>1</v>
@@ -22781,12 +22766,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
@@ -22822,10 +22807,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>130049532</v>
+        <v>130050259</v>
       </c>
       <c r="B176" t="n">
-        <v>58609</v>
+        <v>58612</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -22833,21 +22818,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -22872,7 +22857,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -22881,10 +22866,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>675438</v>
+        <v>675413</v>
       </c>
       <c r="R176" t="n">
-        <v>6700349</v>
+        <v>6700338</v>
       </c>
       <c r="S176" t="n">
         <v>1</v>
@@ -22911,12 +22896,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
@@ -22952,10 +22937,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130049867</v>
+        <v>130050468</v>
       </c>
       <c r="B177" t="n">
-        <v>58601</v>
+        <v>58612</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -22963,21 +22948,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>208249</v>
+        <v>100141</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -22990,9 +22975,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -23001,10 +22991,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>675414</v>
+        <v>675395</v>
       </c>
       <c r="R177" t="n">
-        <v>6700424</v>
+        <v>6700432</v>
       </c>
       <c r="S177" t="n">
         <v>1</v>
@@ -23031,12 +23021,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr">
@@ -23072,10 +23062,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130049629</v>
+        <v>130049819</v>
       </c>
       <c r="B178" t="n">
-        <v>58609</v>
+        <v>58601</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -23083,21 +23073,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -23131,10 +23121,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>675436</v>
+        <v>675394</v>
       </c>
       <c r="R178" t="n">
-        <v>6700363</v>
+        <v>6700378</v>
       </c>
       <c r="S178" t="n">
         <v>1</v>
@@ -23161,12 +23151,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
@@ -23202,7 +23192,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>130049871</v>
+        <v>130049828</v>
       </c>
       <c r="B179" t="n">
         <v>58601</v>
@@ -23251,10 +23241,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>675381</v>
+        <v>675364</v>
       </c>
       <c r="R179" t="n">
-        <v>6700306</v>
+        <v>6700414</v>
       </c>
       <c r="S179" t="n">
         <v>1</v>
@@ -23281,12 +23271,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
@@ -23322,10 +23312,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>130049808</v>
+        <v>130050491</v>
       </c>
       <c r="B180" t="n">
-        <v>58599</v>
+        <v>58612</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -23333,21 +23323,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>208250</v>
+        <v>100141</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -23360,9 +23350,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -23371,10 +23366,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>675373</v>
+        <v>675431</v>
       </c>
       <c r="R180" t="n">
-        <v>6700355</v>
+        <v>6700401</v>
       </c>
       <c r="S180" t="n">
         <v>1</v>
@@ -23401,12 +23396,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
@@ -23442,32 +23437,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>130050259</v>
+        <v>130046353</v>
       </c>
       <c r="B181" t="n">
-        <v>58612</v>
+        <v>58596</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -23482,12 +23477,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -23501,10 +23491,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>675413</v>
+        <v>675372</v>
       </c>
       <c r="R181" t="n">
-        <v>6700338</v>
+        <v>6700346</v>
       </c>
       <c r="S181" t="n">
         <v>1</v>
@@ -23529,14 +23519,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>length:30mm|bodymass:2.6g (same size 3)</t>
+        </is>
+      </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
@@ -23572,32 +23567,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>130050468</v>
+        <v>130046337</v>
       </c>
       <c r="B182" t="n">
-        <v>58612</v>
+        <v>58596</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -23617,7 +23612,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -23626,10 +23621,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>675395</v>
+        <v>675435</v>
       </c>
       <c r="R182" t="n">
-        <v>6700432</v>
+        <v>6700368</v>
       </c>
       <c r="S182" t="n">
         <v>1</v>
@@ -23654,14 +23649,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>length:33mm|bodymass:3.2g</t>
+        </is>
+      </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
@@ -23697,10 +23697,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>130049819</v>
+        <v>130050578</v>
       </c>
       <c r="B183" t="n">
-        <v>58601</v>
+        <v>58612</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -23708,21 +23708,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>208249</v>
+        <v>100141</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -23742,12 +23742,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -23756,10 +23756,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>675394</v>
+        <v>675403</v>
       </c>
       <c r="R183" t="n">
-        <v>6700378</v>
+        <v>6700428</v>
       </c>
       <c r="S183" t="n">
         <v>1</v>
@@ -23786,12 +23786,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC183" t="inlineStr">
@@ -23827,10 +23827,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130049828</v>
+        <v>130050779</v>
       </c>
       <c r="B184" t="n">
-        <v>58601</v>
+        <v>56664</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -23838,16 +23838,16 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>208249</v>
+        <v>208257</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -23867,19 +23867,19 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>675364</v>
+        <v>675375</v>
       </c>
       <c r="R184" t="n">
-        <v>6700414</v>
+        <v>6700315</v>
       </c>
       <c r="S184" t="n">
         <v>1</v>
@@ -23906,12 +23906,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AC184" t="inlineStr">
@@ -23947,7 +23947,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130050491</v>
+        <v>130050542</v>
       </c>
       <c r="B185" t="n">
         <v>58612</v>
@@ -23992,7 +23992,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -24001,10 +24001,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>675431</v>
+        <v>675370</v>
       </c>
       <c r="R185" t="n">
-        <v>6700401</v>
+        <v>6700367</v>
       </c>
       <c r="S185" t="n">
         <v>1</v>
@@ -24031,12 +24031,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
@@ -26497,10 +26497,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>130050705</v>
+        <v>130047272</v>
       </c>
       <c r="B205" t="n">
-        <v>56683</v>
+        <v>58612</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -26508,21 +26508,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100088</v>
+        <v>100141</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -26535,9 +26535,19 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -26546,10 +26556,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>675413</v>
+        <v>675435</v>
       </c>
       <c r="R205" t="n">
-        <v>6700338</v>
+        <v>6700395</v>
       </c>
       <c r="S205" t="n">
         <v>1</v>
@@ -26574,14 +26584,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>length:76mm|bodymass:8g (same size 2)</t>
+        </is>
+      </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AC205" t="inlineStr">
@@ -26617,10 +26632,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>130049848</v>
+        <v>130049744</v>
       </c>
       <c r="B206" t="n">
-        <v>58601</v>
+        <v>58609</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -26628,21 +26643,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -26666,10 +26681,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>675366</v>
+        <v>675372</v>
       </c>
       <c r="R206" t="n">
-        <v>6700382</v>
+        <v>6700346</v>
       </c>
       <c r="S206" t="n">
         <v>1</v>
@@ -26696,12 +26711,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AC206" t="inlineStr">
@@ -26737,32 +26752,32 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>130046460</v>
+        <v>130049804</v>
       </c>
       <c r="B207" t="n">
-        <v>58596</v>
+        <v>58599</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100119</v>
+        <v>208250</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -26775,14 +26790,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -26791,10 +26801,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>675373</v>
+        <v>675381</v>
       </c>
       <c r="R207" t="n">
-        <v>6700355</v>
+        <v>6700306</v>
       </c>
       <c r="S207" t="n">
         <v>1</v>
@@ -26819,19 +26829,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>length:30mm|bodymass:3g (same size 5)</t>
-        </is>
-      </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
@@ -26867,32 +26872,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>130046464</v>
+        <v>130049522</v>
       </c>
       <c r="B208" t="n">
-        <v>58596</v>
+        <v>58609</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -26907,12 +26912,17 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -26921,10 +26931,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>675397</v>
+        <v>675431</v>
       </c>
       <c r="R208" t="n">
-        <v>6700446</v>
+        <v>6700406</v>
       </c>
       <c r="S208" t="n">
         <v>1</v>
@@ -26949,19 +26959,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>length:33mm|bodymass:3g (same size 5)</t>
-        </is>
-      </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
@@ -26997,32 +27002,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>130046334</v>
+        <v>130049856</v>
       </c>
       <c r="B209" t="n">
-        <v>58596</v>
+        <v>58601</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100119</v>
+        <v>208249</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -27035,11 +27040,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N209" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -27051,10 +27051,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>675372</v>
+        <v>675441</v>
       </c>
       <c r="R209" t="n">
-        <v>6700347</v>
+        <v>6700338</v>
       </c>
       <c r="S209" t="n">
         <v>1</v>
@@ -27079,19 +27079,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>length:35mm|bodymass:4.2g</t>
-        </is>
-      </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC209" t="inlineStr">
@@ -27127,32 +27122,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>130046309</v>
+        <v>130049503</v>
       </c>
       <c r="B210" t="n">
-        <v>58596</v>
+        <v>58609</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -27167,7 +27162,12 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -27181,7 +27181,7 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>675413</v>
+        <v>675374</v>
       </c>
       <c r="R210" t="n">
         <v>6700338</v>
@@ -27209,19 +27209,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>length:33mm|bodymass:3.4g</t>
-        </is>
-      </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC210" t="inlineStr">
@@ -27257,32 +27252,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>130046320</v>
+        <v>130049848</v>
       </c>
       <c r="B211" t="n">
-        <v>58596</v>
+        <v>58601</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>100119</v>
+        <v>208249</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -27295,11 +27290,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N211" t="inlineStr">
         <is>
           <t>fälla</t>
@@ -27311,10 +27301,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>675426</v>
+        <v>675366</v>
       </c>
       <c r="R211" t="n">
-        <v>6700410</v>
+        <v>6700382</v>
       </c>
       <c r="S211" t="n">
         <v>1</v>
@@ -27339,19 +27329,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X211" t="inlineStr">
-        <is>
-          <t>length:38mm|bodymass:5.4g</t>
-        </is>
-      </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
@@ -27387,32 +27372,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>130046425</v>
+        <v>130050487</v>
       </c>
       <c r="B212" t="n">
-        <v>58596</v>
+        <v>58612</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100119</v>
+        <v>100141</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -27432,7 +27417,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -27441,10 +27426,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>675370</v>
+        <v>675372</v>
       </c>
       <c r="R212" t="n">
-        <v>6700367</v>
+        <v>6700347</v>
       </c>
       <c r="S212" t="n">
         <v>1</v>
@@ -27469,19 +27454,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>length:27mm|bodymass:1.9g (same size 1)</t>
-        </is>
-      </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr">
@@ -27517,10 +27497,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>130048244</v>
+        <v>130050454</v>
       </c>
       <c r="B213" t="n">
-        <v>58573</v>
+        <v>58612</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -27528,21 +27508,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -27557,17 +27537,12 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -27576,10 +27551,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>675379</v>
+        <v>675420</v>
       </c>
       <c r="R213" t="n">
-        <v>6700441</v>
+        <v>6700424</v>
       </c>
       <c r="S213" t="n">
         <v>1</v>
@@ -27606,12 +27581,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AC213" t="inlineStr">
@@ -27647,10 +27622,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130048186</v>
+        <v>130050467</v>
       </c>
       <c r="B214" t="n">
-        <v>58573</v>
+        <v>58612</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -27658,21 +27633,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -27772,10 +27747,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>130048227</v>
+        <v>130050298</v>
       </c>
       <c r="B215" t="n">
-        <v>58573</v>
+        <v>58612</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -27783,21 +27758,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -27812,7 +27787,12 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -27826,10 +27806,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>675395</v>
+        <v>675394</v>
       </c>
       <c r="R215" t="n">
-        <v>6700289</v>
+        <v>6700378</v>
       </c>
       <c r="S215" t="n">
         <v>1</v>
@@ -27856,12 +27836,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
@@ -27897,10 +27877,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>130048132</v>
+        <v>130050465</v>
       </c>
       <c r="B216" t="n">
-        <v>58573</v>
+        <v>58612</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -27908,21 +27888,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -27935,9 +27915,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -27946,10 +27931,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>675433</v>
+        <v>675371</v>
       </c>
       <c r="R216" t="n">
-        <v>6700327</v>
+        <v>6700345</v>
       </c>
       <c r="S216" t="n">
         <v>1</v>
@@ -27976,12 +27961,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
@@ -28017,10 +28002,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>130048386</v>
+        <v>130050705</v>
       </c>
       <c r="B217" t="n">
-        <v>58573</v>
+        <v>56683</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -28028,16 +28013,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>208245</v>
+        <v>100088</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -28057,7 +28042,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -28066,10 +28051,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>675426</v>
+        <v>675413</v>
       </c>
       <c r="R217" t="n">
-        <v>6700295</v>
+        <v>6700338</v>
       </c>
       <c r="S217" t="n">
         <v>1</v>
@@ -28096,12 +28081,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr">
@@ -28137,32 +28122,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>130048252</v>
+        <v>130046460</v>
       </c>
       <c r="B218" t="n">
-        <v>58573</v>
+        <v>58596</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>208245</v>
+        <v>100119</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -28177,12 +28162,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -28196,10 +28176,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>675364</v>
+        <v>675373</v>
       </c>
       <c r="R218" t="n">
-        <v>6700411</v>
+        <v>6700355</v>
       </c>
       <c r="S218" t="n">
         <v>1</v>
@@ -28224,14 +28204,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>length:30mm|bodymass:3g (same size 5)</t>
+        </is>
+      </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="AC218" t="inlineStr">
@@ -28267,32 +28252,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>130047272</v>
+        <v>130046464</v>
       </c>
       <c r="B219" t="n">
-        <v>58612</v>
+        <v>58596</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -28307,12 +28292,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -28326,10 +28306,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>675435</v>
+        <v>675397</v>
       </c>
       <c r="R219" t="n">
-        <v>6700395</v>
+        <v>6700446</v>
       </c>
       <c r="S219" t="n">
         <v>1</v>
@@ -28356,17 +28336,17 @@
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>length:76mm|bodymass:8g (same size 2)</t>
+          <t>length:33mm|bodymass:3g (same size 5)</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AC219" t="inlineStr">
@@ -28402,32 +28382,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>130049744</v>
+        <v>130046334</v>
       </c>
       <c r="B220" t="n">
-        <v>58609</v>
+        <v>58596</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>208242</v>
+        <v>100119</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -28440,9 +28420,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -28454,7 +28439,7 @@
         <v>675372</v>
       </c>
       <c r="R220" t="n">
-        <v>6700346</v>
+        <v>6700347</v>
       </c>
       <c r="S220" t="n">
         <v>1</v>
@@ -28479,14 +28464,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>length:35mm|bodymass:4.2g</t>
+        </is>
+      </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
@@ -28522,32 +28512,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>130049804</v>
+        <v>130046309</v>
       </c>
       <c r="B221" t="n">
-        <v>58599</v>
+        <v>58596</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>208250</v>
+        <v>100119</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -28560,6 +28550,11 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N221" t="inlineStr">
         <is>
           <t>fälla</t>
@@ -28571,10 +28566,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>675381</v>
+        <v>675413</v>
       </c>
       <c r="R221" t="n">
-        <v>6700306</v>
+        <v>6700338</v>
       </c>
       <c r="S221" t="n">
         <v>1</v>
@@ -28599,14 +28594,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>length:33mm|bodymass:3.4g</t>
+        </is>
+      </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AC221" t="inlineStr">
@@ -28642,32 +28642,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>130049522</v>
+        <v>130046320</v>
       </c>
       <c r="B222" t="n">
-        <v>58609</v>
+        <v>58596</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>208242</v>
+        <v>100119</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -28682,12 +28682,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -28701,10 +28696,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>675431</v>
+        <v>675426</v>
       </c>
       <c r="R222" t="n">
-        <v>6700406</v>
+        <v>6700410</v>
       </c>
       <c r="S222" t="n">
         <v>1</v>
@@ -28729,14 +28724,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>length:38mm|bodymass:5.4g</t>
+        </is>
+      </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr">
@@ -28772,32 +28772,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>130049856</v>
+        <v>130046425</v>
       </c>
       <c r="B223" t="n">
-        <v>58601</v>
+        <v>58596</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>208249</v>
+        <v>100119</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -28810,6 +28810,11 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N223" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -28821,10 +28826,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>675441</v>
+        <v>675370</v>
       </c>
       <c r="R223" t="n">
-        <v>6700338</v>
+        <v>6700367</v>
       </c>
       <c r="S223" t="n">
         <v>1</v>
@@ -28849,14 +28854,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>length:27mm|bodymass:1.9g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC223" t="inlineStr">
@@ -28892,10 +28902,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>130049503</v>
+        <v>130048244</v>
       </c>
       <c r="B224" t="n">
-        <v>58609</v>
+        <v>58573</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -28903,16 +28913,16 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -28937,12 +28947,12 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -28951,10 +28961,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>675374</v>
+        <v>675379</v>
       </c>
       <c r="R224" t="n">
-        <v>6700338</v>
+        <v>6700441</v>
       </c>
       <c r="S224" t="n">
         <v>1</v>
@@ -28981,12 +28991,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
@@ -29022,10 +29032,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>130050487</v>
+        <v>130048186</v>
       </c>
       <c r="B225" t="n">
-        <v>58612</v>
+        <v>58573</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -29033,21 +29043,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -29076,10 +29086,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>675372</v>
+        <v>675362</v>
       </c>
       <c r="R225" t="n">
-        <v>6700347</v>
+        <v>6700387</v>
       </c>
       <c r="S225" t="n">
         <v>1</v>
@@ -29106,12 +29116,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC225" t="inlineStr">
@@ -29147,10 +29157,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>130050454</v>
+        <v>130048227</v>
       </c>
       <c r="B226" t="n">
-        <v>58612</v>
+        <v>58573</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29158,21 +29168,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -29192,7 +29202,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -29201,10 +29211,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>675420</v>
+        <v>675395</v>
       </c>
       <c r="R226" t="n">
-        <v>6700424</v>
+        <v>6700289</v>
       </c>
       <c r="S226" t="n">
         <v>1</v>
@@ -29231,12 +29241,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AC226" t="inlineStr">
@@ -29272,10 +29282,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>130050467</v>
+        <v>130048132</v>
       </c>
       <c r="B227" t="n">
-        <v>58612</v>
+        <v>58573</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -29283,21 +29293,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -29310,14 +29320,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -29326,10 +29331,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>675362</v>
+        <v>675433</v>
       </c>
       <c r="R227" t="n">
-        <v>6700387</v>
+        <v>6700327</v>
       </c>
       <c r="S227" t="n">
         <v>1</v>
@@ -29356,12 +29361,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AC227" t="inlineStr">
@@ -29397,10 +29402,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>130050298</v>
+        <v>130048386</v>
       </c>
       <c r="B228" t="n">
-        <v>58612</v>
+        <v>58573</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -29408,21 +29413,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -29435,16 +29440,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N228" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -29456,10 +29451,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>675394</v>
+        <v>675426</v>
       </c>
       <c r="R228" t="n">
-        <v>6700378</v>
+        <v>6700295</v>
       </c>
       <c r="S228" t="n">
         <v>1</v>
@@ -29486,12 +29481,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AC228" t="inlineStr">
@@ -29527,10 +29522,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>130050465</v>
+        <v>130048252</v>
       </c>
       <c r="B229" t="n">
-        <v>58612</v>
+        <v>58573</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -29538,21 +29533,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -29567,12 +29562,17 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -29581,10 +29581,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>675371</v>
+        <v>675364</v>
       </c>
       <c r="R229" t="n">
-        <v>6700345</v>
+        <v>6700411</v>
       </c>
       <c r="S229" t="n">
         <v>1</v>
@@ -29611,12 +29611,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC229" t="inlineStr">
@@ -32562,10 +32562,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>130050469</v>
+        <v>130048243</v>
       </c>
       <c r="B253" t="n">
-        <v>58612</v>
+        <v>58573</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -32573,21 +32573,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -32616,10 +32616,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>675431</v>
+        <v>675389</v>
       </c>
       <c r="R253" t="n">
-        <v>6700406</v>
+        <v>6700438</v>
       </c>
       <c r="S253" t="n">
         <v>1</v>
@@ -32646,12 +32646,12 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC253" t="inlineStr">
@@ -32687,10 +32687,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>130050708</v>
+        <v>130048273</v>
       </c>
       <c r="B254" t="n">
-        <v>56683</v>
+        <v>58573</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -32698,16 +32698,16 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100088</v>
+        <v>208245</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -32725,21 +32725,31 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>(SKB 19a), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>675389</v>
+        <v>675412</v>
       </c>
       <c r="R254" t="n">
-        <v>6700356</v>
+        <v>6700424</v>
       </c>
       <c r="S254" t="n">
         <v>1</v>
@@ -32766,12 +32776,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC254" t="inlineStr">
@@ -32807,32 +32817,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>130046582</v>
+        <v>130049786</v>
       </c>
       <c r="B255" t="n">
-        <v>58596</v>
+        <v>58599</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>100119</v>
+        <v>208250</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -32852,7 +32862,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -32866,10 +32876,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>675414</v>
+        <v>675374</v>
       </c>
       <c r="R255" t="n">
-        <v>6700288</v>
+        <v>6700401</v>
       </c>
       <c r="S255" t="n">
         <v>1</v>
@@ -32894,19 +32904,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>chip:22048|capture:2|length:48mm|bodymass:11g|Bd:Negative</t>
-        </is>
-      </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC255" t="inlineStr">
@@ -32942,32 +32947,32 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>130046406</v>
+        <v>130049442</v>
       </c>
       <c r="B256" t="n">
-        <v>58596</v>
+        <v>58609</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -32982,7 +32987,12 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -32996,10 +33006,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>675371</v>
+        <v>675379</v>
       </c>
       <c r="R256" t="n">
-        <v>6700349</v>
+        <v>6700309</v>
       </c>
       <c r="S256" t="n">
         <v>1</v>
@@ -33024,19 +33034,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X256" t="inlineStr">
-        <is>
-          <t>length:30mm|bodymass:2.2g</t>
-        </is>
-      </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AC256" t="inlineStr">
@@ -33072,32 +33077,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>130046328</v>
+        <v>130049476</v>
       </c>
       <c r="B257" t="n">
-        <v>58596</v>
+        <v>58609</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -33112,12 +33117,17 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
@@ -33126,10 +33136,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>675372</v>
+        <v>675370</v>
       </c>
       <c r="R257" t="n">
-        <v>6700344</v>
+        <v>6700367</v>
       </c>
       <c r="S257" t="n">
         <v>1</v>
@@ -33154,19 +33164,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>length:29mm|bodymass:2.6g (same size 3)</t>
-        </is>
-      </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC257" t="inlineStr">
@@ -33202,32 +33207,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>130046715</v>
+        <v>130049259</v>
       </c>
       <c r="B258" t="n">
-        <v>58596</v>
+        <v>58609</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -33247,7 +33252,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -33261,10 +33266,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>675432</v>
+        <v>675394</v>
       </c>
       <c r="R258" t="n">
-        <v>6700307</v>
+        <v>6700378</v>
       </c>
       <c r="S258" t="n">
         <v>1</v>
@@ -33289,19 +33294,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>chip:20097|capture:3|length:53mm|bodymass:15g|Bd:Negative</t>
-        </is>
-      </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AC258" t="inlineStr">
@@ -33337,10 +33337,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>130048243</v>
+        <v>130049792</v>
       </c>
       <c r="B259" t="n">
-        <v>58573</v>
+        <v>58599</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -33348,21 +33348,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>208245</v>
+        <v>208250</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -33377,12 +33377,17 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
@@ -33391,10 +33396,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>675389</v>
+        <v>675374</v>
       </c>
       <c r="R259" t="n">
-        <v>6700438</v>
+        <v>6700338</v>
       </c>
       <c r="S259" t="n">
         <v>1</v>
@@ -33421,12 +33426,12 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC259" t="inlineStr">
@@ -33462,10 +33467,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>130048273</v>
+        <v>130050469</v>
       </c>
       <c r="B260" t="n">
-        <v>58573</v>
+        <v>58612</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -33473,21 +33478,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -33502,12 +33507,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -33521,10 +33521,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>675412</v>
+        <v>675431</v>
       </c>
       <c r="R260" t="n">
-        <v>6700424</v>
+        <v>6700406</v>
       </c>
       <c r="S260" t="n">
         <v>1</v>
@@ -33551,12 +33551,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC260" t="inlineStr">
@@ -33592,10 +33592,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>130049786</v>
+        <v>130050708</v>
       </c>
       <c r="B261" t="n">
-        <v>58599</v>
+        <v>56683</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -33603,21 +33603,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>208250</v>
+        <v>100088</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -33630,16 +33630,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N261" t="inlineStr">
         <is>
           <t>fälla</t>
@@ -33647,14 +33637,14 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB 19a), Upl</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>675374</v>
+        <v>675389</v>
       </c>
       <c r="R261" t="n">
-        <v>6700401</v>
+        <v>6700356</v>
       </c>
       <c r="S261" t="n">
         <v>1</v>
@@ -33722,32 +33712,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>130049442</v>
+        <v>130046582</v>
       </c>
       <c r="B262" t="n">
-        <v>58609</v>
+        <v>58596</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>208242</v>
+        <v>100119</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -33772,7 +33762,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
@@ -33781,10 +33771,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>675379</v>
+        <v>675414</v>
       </c>
       <c r="R262" t="n">
-        <v>6700309</v>
+        <v>6700288</v>
       </c>
       <c r="S262" t="n">
         <v>1</v>
@@ -33809,14 +33799,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>chip:22048|capture:2|length:48mm|bodymass:11g|Bd:Negative</t>
+        </is>
+      </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AC262" t="inlineStr">
@@ -33852,32 +33847,32 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>130049476</v>
+        <v>130046406</v>
       </c>
       <c r="B263" t="n">
-        <v>58609</v>
+        <v>58596</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>208242</v>
+        <v>100119</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -33892,12 +33887,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -33911,10 +33901,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>675370</v>
+        <v>675371</v>
       </c>
       <c r="R263" t="n">
-        <v>6700367</v>
+        <v>6700349</v>
       </c>
       <c r="S263" t="n">
         <v>1</v>
@@ -33939,14 +33929,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>length:30mm|bodymass:2.2g</t>
+        </is>
+      </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AC263" t="inlineStr">
@@ -33982,32 +33977,32 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>130049259</v>
+        <v>130046328</v>
       </c>
       <c r="B264" t="n">
-        <v>58609</v>
+        <v>58596</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>208242</v>
+        <v>100119</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -34022,17 +34017,12 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
@@ -34041,10 +34031,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>675394</v>
+        <v>675372</v>
       </c>
       <c r="R264" t="n">
-        <v>6700378</v>
+        <v>6700344</v>
       </c>
       <c r="S264" t="n">
         <v>1</v>
@@ -34069,14 +34059,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>length:29mm|bodymass:2.6g (same size 3)</t>
+        </is>
+      </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AC264" t="inlineStr">
@@ -34112,32 +34107,32 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>130049792</v>
+        <v>130046715</v>
       </c>
       <c r="B265" t="n">
-        <v>58599</v>
+        <v>58596</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>208250</v>
+        <v>100119</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -34162,7 +34157,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
@@ -34171,10 +34166,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>675374</v>
+        <v>675432</v>
       </c>
       <c r="R265" t="n">
-        <v>6700338</v>
+        <v>6700307</v>
       </c>
       <c r="S265" t="n">
         <v>1</v>
@@ -34199,14 +34194,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>chip:20097|capture:3|length:53mm|bodymass:15g|Bd:Negative</t>
+        </is>
+      </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC265" t="inlineStr">
@@ -34242,32 +34242,32 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>130050608</v>
+        <v>130046469</v>
       </c>
       <c r="B266" t="n">
-        <v>58612</v>
+        <v>58596</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -34296,10 +34296,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>675432</v>
+        <v>675384</v>
       </c>
       <c r="R266" t="n">
-        <v>6700377</v>
+        <v>6700305</v>
       </c>
       <c r="S266" t="n">
         <v>1</v>
@@ -34324,14 +34324,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>length:32mm|bodymass:3g (same size 3)</t>
+        </is>
+      </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC266" t="inlineStr">
@@ -34367,7 +34372,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>130050558</v>
+        <v>130050608</v>
       </c>
       <c r="B267" t="n">
         <v>58612</v>
@@ -34412,7 +34417,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
@@ -34421,10 +34426,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>675385</v>
+        <v>675432</v>
       </c>
       <c r="R267" t="n">
-        <v>6700439</v>
+        <v>6700377</v>
       </c>
       <c r="S267" t="n">
         <v>1</v>
@@ -34451,12 +34456,12 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AC267" t="inlineStr">
@@ -34492,7 +34497,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>130050576</v>
+        <v>130050558</v>
       </c>
       <c r="B268" t="n">
         <v>58612</v>
@@ -34532,17 +34537,12 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
@@ -34551,7 +34551,7 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>675387</v>
+        <v>675385</v>
       </c>
       <c r="R268" t="n">
         <v>6700439</v>
@@ -34581,12 +34581,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC268" t="inlineStr">
@@ -34622,32 +34622,32 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>130046369</v>
+        <v>130050576</v>
       </c>
       <c r="B269" t="n">
-        <v>58596</v>
+        <v>58612</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>100119</v>
+        <v>100141</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -34662,12 +34662,17 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
@@ -34676,10 +34681,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>675365</v>
+        <v>675387</v>
       </c>
       <c r="R269" t="n">
-        <v>6700380</v>
+        <v>6700439</v>
       </c>
       <c r="S269" t="n">
         <v>1</v>
@@ -34704,19 +34709,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>length:32mm|bodymass:3.1g (same size 2)</t>
-        </is>
-      </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC269" t="inlineStr">
@@ -34752,7 +34752,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>130046469</v>
+        <v>130046369</v>
       </c>
       <c r="B270" t="n">
         <v>58596</v>
@@ -34797,7 +34797,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
@@ -34806,10 +34806,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>675384</v>
+        <v>675365</v>
       </c>
       <c r="R270" t="n">
-        <v>6700305</v>
+        <v>6700380</v>
       </c>
       <c r="S270" t="n">
         <v>1</v>
@@ -34836,17 +34836,17 @@
       </c>
       <c r="X270" t="inlineStr">
         <is>
-          <t>length:32mm|bodymass:3g (same size 3)</t>
+          <t>length:32mm|bodymass:3.1g (same size 2)</t>
         </is>
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC270" t="inlineStr">
@@ -34882,32 +34882,32 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>130049847</v>
+        <v>130046428</v>
       </c>
       <c r="B271" t="n">
-        <v>58601</v>
+        <v>58596</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>208249</v>
+        <v>100119</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -34922,17 +34922,12 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
@@ -34941,10 +34936,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>675374</v>
+        <v>675385</v>
       </c>
       <c r="R271" t="n">
-        <v>6700338</v>
+        <v>6700298</v>
       </c>
       <c r="S271" t="n">
         <v>1</v>
@@ -34969,14 +34964,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>length:35mm|bodymass:4g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC271" t="inlineStr">
@@ -35012,7 +35012,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>130046428</v>
+        <v>130046434</v>
       </c>
       <c r="B272" t="n">
         <v>58596</v>
@@ -35057,7 +35057,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
@@ -35066,10 +35066,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>675385</v>
+        <v>675404</v>
       </c>
       <c r="R272" t="n">
-        <v>6700298</v>
+        <v>6700427</v>
       </c>
       <c r="S272" t="n">
         <v>1</v>
@@ -35096,17 +35096,17 @@
       </c>
       <c r="X272" t="inlineStr">
         <is>
-          <t>length:35mm|bodymass:4g (same size 1)</t>
+          <t>length:30mm|bodymass:2.8g</t>
         </is>
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -35142,32 +35142,32 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>130046434</v>
+        <v>130048107</v>
       </c>
       <c r="B273" t="n">
-        <v>58596</v>
+        <v>58573</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100119</v>
+        <v>208245</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -35182,12 +35182,17 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
@@ -35196,10 +35201,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>675404</v>
+        <v>675413</v>
       </c>
       <c r="R273" t="n">
-        <v>6700427</v>
+        <v>6700425</v>
       </c>
       <c r="S273" t="n">
         <v>1</v>
@@ -35224,19 +35229,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X273" t="inlineStr">
-        <is>
-          <t>length:30mm|bodymass:2.8g</t>
-        </is>
-      </c>
       <c r="Y273" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -35272,7 +35272,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>130048107</v>
+        <v>130048178</v>
       </c>
       <c r="B274" t="n">
         <v>58573</v>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
@@ -35331,10 +35331,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>675413</v>
+        <v>675435</v>
       </c>
       <c r="R274" t="n">
-        <v>6700425</v>
+        <v>6700368</v>
       </c>
       <c r="S274" t="n">
         <v>1</v>
@@ -35361,12 +35361,12 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -35402,7 +35402,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>130048178</v>
+        <v>130048265</v>
       </c>
       <c r="B275" t="n">
         <v>58573</v>
@@ -35442,12 +35442,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L275" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -35461,10 +35456,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>675435</v>
+        <v>675383</v>
       </c>
       <c r="R275" t="n">
-        <v>6700368</v>
+        <v>6700304</v>
       </c>
       <c r="S275" t="n">
         <v>1</v>
@@ -35491,12 +35486,12 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -35532,10 +35527,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>130048265</v>
+        <v>130047404</v>
       </c>
       <c r="B276" t="n">
-        <v>58573</v>
+        <v>58612</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -35543,21 +35538,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -35572,12 +35567,17 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P276" t="inlineStr">
@@ -35586,10 +35586,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>675383</v>
+        <v>675430</v>
       </c>
       <c r="R276" t="n">
-        <v>6700304</v>
+        <v>6700305</v>
       </c>
       <c r="S276" t="n">
         <v>1</v>
@@ -35614,14 +35614,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>length:69mm|bodymass:5g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -35657,10 +35662,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>130047404</v>
+        <v>130049847</v>
       </c>
       <c r="B277" t="n">
-        <v>58612</v>
+        <v>58601</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -35668,21 +35673,21 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100141</v>
+        <v>208249</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -35707,7 +35712,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P277" t="inlineStr">
@@ -35716,10 +35721,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>675430</v>
+        <v>675374</v>
       </c>
       <c r="R277" t="n">
-        <v>6700305</v>
+        <v>6700338</v>
       </c>
       <c r="S277" t="n">
         <v>1</v>
@@ -35744,19 +35749,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>length:69mm|bodymass:5g (same size 1)</t>
-        </is>
-      </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -45807,10 +45807,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>130050714</v>
+        <v>130048259</v>
       </c>
       <c r="B357" t="n">
-        <v>56683</v>
+        <v>58573</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -45818,16 +45818,16 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>100088</v>
+        <v>208245</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -45845,6 +45845,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N357" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -45852,14 +45862,14 @@
       </c>
       <c r="P357" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>675369</v>
+        <v>675420</v>
       </c>
       <c r="R357" t="n">
-        <v>6700430</v>
+        <v>6700420</v>
       </c>
       <c r="S357" t="n">
         <v>1</v>
@@ -45886,12 +45896,12 @@
       </c>
       <c r="Y357" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -45927,10 +45937,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>130050607</v>
+        <v>130048062</v>
       </c>
       <c r="B358" t="n">
-        <v>58612</v>
+        <v>58573</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -45938,21 +45948,21 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -45967,12 +45977,7 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -45986,10 +45991,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>675389</v>
+        <v>675394</v>
       </c>
       <c r="R358" t="n">
-        <v>6700438</v>
+        <v>6700378</v>
       </c>
       <c r="S358" t="n">
         <v>1</v>
@@ -46016,12 +46021,12 @@
       </c>
       <c r="Y358" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -46057,7 +46062,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>130048259</v>
+        <v>130048306</v>
       </c>
       <c r="B359" t="n">
         <v>58573</v>
@@ -46095,16 +46100,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N359" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -46116,10 +46111,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>675420</v>
+        <v>675387</v>
       </c>
       <c r="R359" t="n">
-        <v>6700420</v>
+        <v>6700439</v>
       </c>
       <c r="S359" t="n">
         <v>1</v>
@@ -46146,12 +46141,12 @@
       </c>
       <c r="Y359" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -46187,10 +46182,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>130048062</v>
+        <v>130047348</v>
       </c>
       <c r="B360" t="n">
-        <v>58573</v>
+        <v>58612</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -46198,21 +46193,21 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -46227,7 +46222,12 @@
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -46241,10 +46241,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>675394</v>
+        <v>675422</v>
       </c>
       <c r="R360" t="n">
-        <v>6700378</v>
+        <v>6700428</v>
       </c>
       <c r="S360" t="n">
         <v>1</v>
@@ -46269,14 +46269,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>length:71mm|bodymass:6g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y360" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -46312,10 +46317,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>130048306</v>
+        <v>130049798</v>
       </c>
       <c r="B361" t="n">
-        <v>58573</v>
+        <v>58599</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -46323,21 +46328,21 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>208245</v>
+        <v>208250</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -46361,10 +46366,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>675387</v>
+        <v>675369</v>
       </c>
       <c r="R361" t="n">
-        <v>6700439</v>
+        <v>6700355</v>
       </c>
       <c r="S361" t="n">
         <v>1</v>
@@ -46432,7 +46437,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>130047348</v>
+        <v>130050472</v>
       </c>
       <c r="B362" t="n">
         <v>58612</v>
@@ -46472,12 +46477,7 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -46491,10 +46491,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>675422</v>
+        <v>675369</v>
       </c>
       <c r="R362" t="n">
-        <v>6700428</v>
+        <v>6700430</v>
       </c>
       <c r="S362" t="n">
         <v>1</v>
@@ -46519,19 +46519,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X362" t="inlineStr">
-        <is>
-          <t>length:71mm|bodymass:6g (same size 1)</t>
-        </is>
-      </c>
       <c r="Y362" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -46567,10 +46562,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>130049798</v>
+        <v>130050714</v>
       </c>
       <c r="B363" t="n">
-        <v>58599</v>
+        <v>56683</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -46578,21 +46573,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>208250</v>
+        <v>100088</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -46612,14 +46607,14 @@
       </c>
       <c r="P363" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q363" t="n">
         <v>675369</v>
       </c>
       <c r="R363" t="n">
-        <v>6700355</v>
+        <v>6700430</v>
       </c>
       <c r="S363" t="n">
         <v>1</v>
@@ -46646,12 +46641,12 @@
       </c>
       <c r="Y363" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -46687,7 +46682,7 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>130050472</v>
+        <v>130050607</v>
       </c>
       <c r="B364" t="n">
         <v>58612</v>
@@ -46727,7 +46722,12 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -46741,10 +46741,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>675369</v>
+        <v>675389</v>
       </c>
       <c r="R364" t="n">
-        <v>6700430</v>
+        <v>6700438</v>
       </c>
       <c r="S364" t="n">
         <v>1</v>
@@ -46771,12 +46771,12 @@
       </c>
       <c r="Y364" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -46812,10 +46812,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>130048150</v>
+        <v>130050703</v>
       </c>
       <c r="B365" t="n">
-        <v>58573</v>
+        <v>56683</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -46823,16 +46823,16 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>208245</v>
+        <v>100088</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -46850,11 +46850,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N365" t="inlineStr">
         <is>
           <t>fälla</t>
@@ -46866,10 +46861,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>675414</v>
+        <v>675428</v>
       </c>
       <c r="R365" t="n">
-        <v>6700289</v>
+        <v>6700381</v>
       </c>
       <c r="S365" t="n">
         <v>1</v>
@@ -46896,12 +46891,12 @@
       </c>
       <c r="Y365" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -46937,7 +46932,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>130050703</v>
+        <v>130050719</v>
       </c>
       <c r="B366" t="n">
         <v>56683</v>
@@ -46977,19 +46972,19 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P366" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q366" t="n">
         <v>675428</v>
       </c>
       <c r="R366" t="n">
-        <v>6700381</v>
+        <v>6700297</v>
       </c>
       <c r="S366" t="n">
         <v>1</v>
@@ -47016,12 +47011,12 @@
       </c>
       <c r="Y366" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -47057,10 +47052,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>130050719</v>
+        <v>130050781</v>
       </c>
       <c r="B367" t="n">
-        <v>56683</v>
+        <v>56664</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -47068,21 +47063,21 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>100088</v>
+        <v>208257</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -47106,10 +47101,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>675428</v>
+        <v>675390</v>
       </c>
       <c r="R367" t="n">
-        <v>6700297</v>
+        <v>6700437</v>
       </c>
       <c r="S367" t="n">
         <v>1</v>
@@ -47136,12 +47131,12 @@
       </c>
       <c r="Y367" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -47177,10 +47172,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>130050781</v>
+        <v>130050549</v>
       </c>
       <c r="B368" t="n">
-        <v>56664</v>
+        <v>58612</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -47188,21 +47183,21 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>208257</v>
+        <v>100141</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -47215,6 +47210,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N368" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -47222,14 +47227,14 @@
       </c>
       <c r="P368" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>675390</v>
+        <v>675432</v>
       </c>
       <c r="R368" t="n">
-        <v>6700437</v>
+        <v>6700384</v>
       </c>
       <c r="S368" t="n">
         <v>1</v>
@@ -47256,12 +47261,12 @@
       </c>
       <c r="Y368" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -47297,10 +47302,10 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>130050549</v>
+        <v>130050782</v>
       </c>
       <c r="B369" t="n">
-        <v>58612</v>
+        <v>56664</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -47308,21 +47313,21 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>100141</v>
+        <v>208257</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -47335,31 +47340,21 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L369" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P369" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>675432</v>
+        <v>675372</v>
       </c>
       <c r="R369" t="n">
-        <v>6700384</v>
+        <v>6700347</v>
       </c>
       <c r="S369" t="n">
         <v>1</v>
@@ -47386,12 +47381,12 @@
       </c>
       <c r="Y369" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -47427,32 +47422,32 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>130050782</v>
+        <v>130046698</v>
       </c>
       <c r="B370" t="n">
-        <v>56664</v>
+        <v>58596</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>208257</v>
+        <v>100119</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -47465,21 +47460,31 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P370" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>675372</v>
+        <v>675438</v>
       </c>
       <c r="R370" t="n">
-        <v>6700347</v>
+        <v>6700354</v>
       </c>
       <c r="S370" t="n">
         <v>1</v>
@@ -47504,14 +47509,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X370" t="inlineStr">
+        <is>
+          <t>chip:20226|capture:2|length:56mm|bodymass:24.7g|Bd:Positive</t>
+        </is>
+      </c>
       <c r="Y370" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -47547,7 +47557,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>130046698</v>
+        <v>130046318</v>
       </c>
       <c r="B371" t="n">
         <v>58596</v>
@@ -47587,17 +47597,12 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L371" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P371" t="inlineStr">
@@ -47606,10 +47611,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>675438</v>
+        <v>675374</v>
       </c>
       <c r="R371" t="n">
-        <v>6700354</v>
+        <v>6700401</v>
       </c>
       <c r="S371" t="n">
         <v>1</v>
@@ -47636,17 +47641,17 @@
       </c>
       <c r="X371" t="inlineStr">
         <is>
-          <t>chip:20226|capture:2|length:56mm|bodymass:24.7g|Bd:Positive</t>
+          <t>length:33mm|bodymass:4.2g</t>
         </is>
       </c>
       <c r="Y371" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -47682,32 +47687,32 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>130046318</v>
+        <v>130049861</v>
       </c>
       <c r="B372" t="n">
-        <v>58596</v>
+        <v>58601</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>100119</v>
+        <v>208249</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -47720,14 +47725,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P372" t="inlineStr">
@@ -47736,10 +47736,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>675374</v>
+        <v>675381</v>
       </c>
       <c r="R372" t="n">
-        <v>6700401</v>
+        <v>6700307</v>
       </c>
       <c r="S372" t="n">
         <v>1</v>
@@ -47764,19 +47764,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X372" t="inlineStr">
-        <is>
-          <t>length:33mm|bodymass:4.2g</t>
-        </is>
-      </c>
       <c r="Y372" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AC372" t="inlineStr">
@@ -47812,10 +47807,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>130049861</v>
+        <v>130049430</v>
       </c>
       <c r="B373" t="n">
-        <v>58601</v>
+        <v>58609</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -47823,21 +47818,21 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -47850,6 +47845,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N373" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -47861,10 +47866,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>675381</v>
+        <v>675370</v>
       </c>
       <c r="R373" t="n">
-        <v>6700307</v>
+        <v>6700432</v>
       </c>
       <c r="S373" t="n">
         <v>1</v>
@@ -47891,12 +47896,12 @@
       </c>
       <c r="Y373" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
@@ -47932,10 +47937,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>130049430</v>
+        <v>130048150</v>
       </c>
       <c r="B374" t="n">
-        <v>58609</v>
+        <v>58573</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -47943,16 +47948,16 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -47972,17 +47977,12 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L374" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P374" t="inlineStr">
@@ -47991,10 +47991,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>675370</v>
+        <v>675414</v>
       </c>
       <c r="R374" t="n">
-        <v>6700432</v>
+        <v>6700289</v>
       </c>
       <c r="S374" t="n">
         <v>1</v>
@@ -48021,12 +48021,12 @@
       </c>
       <c r="Y374" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -24062,10 +24062,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>130050563</v>
+        <v>130048285</v>
       </c>
       <c r="B186" t="n">
-        <v>58614</v>
+        <v>58575</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -24073,21 +24073,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -24100,14 +24100,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -24116,10 +24111,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>675431</v>
+        <v>675368</v>
       </c>
       <c r="R186" t="n">
-        <v>6700403</v>
+        <v>6700428</v>
       </c>
       <c r="S186" t="n">
         <v>1</v>
@@ -24146,12 +24141,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
@@ -24187,10 +24182,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>130050588</v>
+        <v>130048217</v>
       </c>
       <c r="B187" t="n">
-        <v>58614</v>
+        <v>58575</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -24198,21 +24193,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -24227,12 +24222,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -24246,10 +24236,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>675426</v>
+        <v>675372</v>
       </c>
       <c r="R187" t="n">
-        <v>6700420</v>
+        <v>6700347</v>
       </c>
       <c r="S187" t="n">
         <v>1</v>
@@ -24274,19 +24264,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>length:65mm|bodymass:4g (same size 1)</t>
-        </is>
-      </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
@@ -24322,10 +24307,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>130050527</v>
+        <v>130050777</v>
       </c>
       <c r="B188" t="n">
-        <v>58614</v>
+        <v>56665</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -24333,21 +24318,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100141</v>
+        <v>208257</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -24360,19 +24345,14 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q188" t="n">
@@ -24406,12 +24386,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AC188" t="inlineStr">
@@ -24447,32 +24427,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>130050697</v>
+        <v>130046326</v>
       </c>
       <c r="B189" t="n">
-        <v>56673</v>
+        <v>58598</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>208255</v>
+        <v>100119</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -24485,21 +24465,26 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>675435</v>
+        <v>675389</v>
       </c>
       <c r="R189" t="n">
-        <v>6700368</v>
+        <v>6700356</v>
       </c>
       <c r="S189" t="n">
         <v>1</v>
@@ -24524,14 +24509,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>length:34mm|bodymass:4g (same size 5)</t>
+        </is>
+      </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
@@ -24567,32 +24557,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>130050777</v>
+        <v>130046661</v>
       </c>
       <c r="B190" t="n">
-        <v>56665</v>
+        <v>58598</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>208257</v>
+        <v>100119</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -24605,6 +24595,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N190" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -24612,14 +24612,14 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>675404</v>
+        <v>675426</v>
       </c>
       <c r="R190" t="n">
-        <v>6700427</v>
+        <v>6700295</v>
       </c>
       <c r="S190" t="n">
         <v>1</v>
@@ -24644,14 +24644,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>chip:20762|capture:6|length:54mm|bodymass:15g|Bd:Negative</t>
+        </is>
+      </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC190" t="inlineStr">
@@ -24687,32 +24692,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>130047273</v>
+        <v>130046409</v>
       </c>
       <c r="B191" t="n">
-        <v>58614</v>
+        <v>58598</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -24727,12 +24732,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -24776,17 +24776,17 @@
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>length:70mm|bodymass:6g (same size 8)</t>
+          <t>length:31mm|bodymass:2.7g (same size 1)</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AC191" t="inlineStr">
@@ -24822,32 +24822,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>130047408</v>
+        <v>130046704</v>
       </c>
       <c r="B192" t="n">
-        <v>58614</v>
+        <v>58598</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -24881,10 +24881,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>675400</v>
+        <v>675394</v>
       </c>
       <c r="R192" t="n">
-        <v>6700425</v>
+        <v>6700294</v>
       </c>
       <c r="S192" t="n">
         <v>1</v>
@@ -24911,17 +24911,17 @@
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>length:70mm|bodymass:6g (same size 1)</t>
+          <t>chip:20164|capture:4|length:53mm|bodymass:15g|Bd:Negative</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
@@ -24957,7 +24957,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>130046326</v>
+        <v>130046561</v>
       </c>
       <c r="B193" t="n">
         <v>58598</v>
@@ -24997,7 +24997,12 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -25011,10 +25016,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>675389</v>
+        <v>675379</v>
       </c>
       <c r="R193" t="n">
-        <v>6700356</v>
+        <v>6700441</v>
       </c>
       <c r="S193" t="n">
         <v>1</v>
@@ -25041,17 +25046,17 @@
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>length:34mm|bodymass:4g (same size 5)</t>
+          <t>chip:23891|capture:3|length:50mm|bodymass:14g|Bd:Negative</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="AC193" t="inlineStr">
@@ -25087,7 +25092,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>130046661</v>
+        <v>130046357</v>
       </c>
       <c r="B194" t="n">
         <v>58598</v>
@@ -25127,17 +25132,12 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -25146,10 +25146,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>675426</v>
+        <v>675362</v>
       </c>
       <c r="R194" t="n">
-        <v>6700295</v>
+        <v>6700387</v>
       </c>
       <c r="S194" t="n">
         <v>1</v>
@@ -25176,17 +25176,17 @@
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>chip:20762|capture:6|length:54mm|bodymass:15g|Bd:Negative</t>
+          <t>length:40mm|bodymass:4.5g</t>
         </is>
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC194" t="inlineStr">
@@ -25222,32 +25222,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>130046409</v>
+        <v>130047273</v>
       </c>
       <c r="B195" t="n">
-        <v>58598</v>
+        <v>58614</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100119</v>
+        <v>100141</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -25262,7 +25262,12 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -25306,17 +25311,17 @@
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>length:31mm|bodymass:2.7g (same size 1)</t>
+          <t>length:70mm|bodymass:6g (same size 8)</t>
         </is>
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
@@ -25352,32 +25357,32 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>130046704</v>
+        <v>130047408</v>
       </c>
       <c r="B196" t="n">
-        <v>58598</v>
+        <v>58614</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100119</v>
+        <v>100141</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -25411,10 +25416,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>675394</v>
+        <v>675400</v>
       </c>
       <c r="R196" t="n">
-        <v>6700294</v>
+        <v>6700425</v>
       </c>
       <c r="S196" t="n">
         <v>1</v>
@@ -25441,17 +25446,17 @@
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>chip:20164|capture:4|length:53mm|bodymass:15g|Bd:Negative</t>
+          <t>length:70mm|bodymass:6g (same size 1)</t>
         </is>
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
@@ -25487,32 +25492,32 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>130046561</v>
+        <v>130048423</v>
       </c>
       <c r="B197" t="n">
-        <v>58598</v>
+        <v>58575</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100119</v>
+        <v>208245</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -25525,19 +25530,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -25546,10 +25541,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>675379</v>
+        <v>675375</v>
       </c>
       <c r="R197" t="n">
-        <v>6700441</v>
+        <v>6700326</v>
       </c>
       <c r="S197" t="n">
         <v>1</v>
@@ -25574,19 +25569,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>chip:23891|capture:3|length:50mm|bodymass:14g|Bd:Negative</t>
-        </is>
-      </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
@@ -25622,32 +25612,32 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>130046357</v>
+        <v>130050563</v>
       </c>
       <c r="B198" t="n">
-        <v>58598</v>
+        <v>58614</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100119</v>
+        <v>100141</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -25676,10 +25666,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>675362</v>
+        <v>675431</v>
       </c>
       <c r="R198" t="n">
-        <v>6700387</v>
+        <v>6700403</v>
       </c>
       <c r="S198" t="n">
         <v>1</v>
@@ -25704,19 +25694,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>length:40mm|bodymass:4.5g</t>
-        </is>
-      </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC198" t="inlineStr">
@@ -25752,10 +25737,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>130048285</v>
+        <v>130050588</v>
       </c>
       <c r="B199" t="n">
-        <v>58575</v>
+        <v>58614</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -25763,21 +25748,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -25790,6 +25775,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N199" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -25801,10 +25796,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>675368</v>
+        <v>675426</v>
       </c>
       <c r="R199" t="n">
-        <v>6700428</v>
+        <v>6700420</v>
       </c>
       <c r="S199" t="n">
         <v>1</v>
@@ -25829,14 +25824,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>length:65mm|bodymass:4g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="AC199" t="inlineStr">
@@ -25872,10 +25872,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>130048423</v>
+        <v>130050527</v>
       </c>
       <c r="B200" t="n">
-        <v>58575</v>
+        <v>58614</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -25883,21 +25883,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -25910,9 +25910,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -25921,10 +25926,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>675375</v>
+        <v>675404</v>
       </c>
       <c r="R200" t="n">
-        <v>6700326</v>
+        <v>6700427</v>
       </c>
       <c r="S200" t="n">
         <v>1</v>
@@ -25951,12 +25956,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC200" t="inlineStr">
@@ -25992,10 +25997,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>130048217</v>
+        <v>130050697</v>
       </c>
       <c r="B201" t="n">
-        <v>58575</v>
+        <v>56673</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -26003,21 +26008,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>208245</v>
+        <v>208255</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -26030,11 +26035,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N201" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -26042,14 +26042,14 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>675372</v>
+        <v>675435</v>
       </c>
       <c r="R201" t="n">
-        <v>6700347</v>
+        <v>6700368</v>
       </c>
       <c r="S201" t="n">
         <v>1</v>
@@ -26076,12 +26076,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC201" t="inlineStr">
@@ -27267,10 +27267,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>130049744</v>
+        <v>130047272</v>
       </c>
       <c r="B211" t="n">
-        <v>58611</v>
+        <v>58614</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -27278,21 +27278,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -27305,9 +27305,19 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -27316,10 +27326,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>675372</v>
+        <v>675435</v>
       </c>
       <c r="R211" t="n">
-        <v>6700346</v>
+        <v>6700395</v>
       </c>
       <c r="S211" t="n">
         <v>1</v>
@@ -27344,14 +27354,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>length:76mm|bodymass:8g (same size 2)</t>
+        </is>
+      </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
@@ -27387,10 +27402,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>130048186</v>
+        <v>130050454</v>
       </c>
       <c r="B212" t="n">
-        <v>58575</v>
+        <v>58614</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -27398,21 +27413,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -27441,10 +27456,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>675362</v>
+        <v>675420</v>
       </c>
       <c r="R212" t="n">
-        <v>6700387</v>
+        <v>6700424</v>
       </c>
       <c r="S212" t="n">
         <v>1</v>
@@ -27471,12 +27486,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr">
@@ -27512,10 +27527,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>130048132</v>
+        <v>130050467</v>
       </c>
       <c r="B213" t="n">
-        <v>58575</v>
+        <v>58614</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -27523,21 +27538,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -27550,9 +27565,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -27561,10 +27581,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>675433</v>
+        <v>675362</v>
       </c>
       <c r="R213" t="n">
-        <v>6700327</v>
+        <v>6700387</v>
       </c>
       <c r="S213" t="n">
         <v>1</v>
@@ -27591,12 +27611,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC213" t="inlineStr">
@@ -27632,7 +27652,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>130050454</v>
+        <v>130050465</v>
       </c>
       <c r="B214" t="n">
         <v>58614</v>
@@ -27686,10 +27706,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>675420</v>
+        <v>675371</v>
       </c>
       <c r="R214" t="n">
-        <v>6700424</v>
+        <v>6700345</v>
       </c>
       <c r="S214" t="n">
         <v>1</v>
@@ -27716,12 +27736,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC214" t="inlineStr">
@@ -27757,10 +27777,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>130050467</v>
+        <v>130048244</v>
       </c>
       <c r="B215" t="n">
-        <v>58614</v>
+        <v>58575</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -27768,21 +27788,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -27797,12 +27817,17 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -27811,10 +27836,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>675362</v>
+        <v>675379</v>
       </c>
       <c r="R215" t="n">
-        <v>6700387</v>
+        <v>6700441</v>
       </c>
       <c r="S215" t="n">
         <v>1</v>
@@ -27841,12 +27866,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
@@ -27882,10 +27907,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>130050465</v>
+        <v>130049804</v>
       </c>
       <c r="B216" t="n">
-        <v>58614</v>
+        <v>58601</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -27893,21 +27918,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100141</v>
+        <v>208250</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -27920,11 +27945,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N216" t="inlineStr">
         <is>
           <t>fälla</t>
@@ -27936,10 +27956,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>675371</v>
+        <v>675381</v>
       </c>
       <c r="R216" t="n">
-        <v>6700345</v>
+        <v>6700306</v>
       </c>
       <c r="S216" t="n">
         <v>1</v>
@@ -27966,12 +27986,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
@@ -28007,10 +28027,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>130047272</v>
+        <v>130049856</v>
       </c>
       <c r="B217" t="n">
-        <v>58614</v>
+        <v>58603</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -28018,21 +28038,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100141</v>
+        <v>208249</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -28045,16 +28065,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N217" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -28066,10 +28076,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>675435</v>
+        <v>675441</v>
       </c>
       <c r="R217" t="n">
-        <v>6700395</v>
+        <v>6700338</v>
       </c>
       <c r="S217" t="n">
         <v>1</v>
@@ -28094,19 +28104,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>length:76mm|bodymass:8g (same size 2)</t>
-        </is>
-      </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr">
@@ -28142,10 +28147,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>130048227</v>
+        <v>130049848</v>
       </c>
       <c r="B218" t="n">
-        <v>58575</v>
+        <v>58603</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -28153,21 +28158,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -28180,14 +28185,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -28196,10 +28196,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>675395</v>
+        <v>675366</v>
       </c>
       <c r="R218" t="n">
-        <v>6700289</v>
+        <v>6700382</v>
       </c>
       <c r="S218" t="n">
         <v>1</v>
@@ -28226,12 +28226,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC218" t="inlineStr">
@@ -28267,10 +28267,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>130049522</v>
+        <v>130048252</v>
       </c>
       <c r="B219" t="n">
-        <v>58611</v>
+        <v>58575</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -28278,16 +28278,16 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -28317,7 +28317,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -28326,10 +28326,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>675431</v>
+        <v>675364</v>
       </c>
       <c r="R219" t="n">
-        <v>6700406</v>
+        <v>6700411</v>
       </c>
       <c r="S219" t="n">
         <v>1</v>
@@ -28356,12 +28356,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC219" t="inlineStr">
@@ -28397,10 +28397,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>130048386</v>
+        <v>130050705</v>
       </c>
       <c r="B220" t="n">
-        <v>58575</v>
+        <v>56684</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -28408,16 +28408,16 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>208245</v>
+        <v>100088</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -28437,7 +28437,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -28446,10 +28446,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>675426</v>
+        <v>675413</v>
       </c>
       <c r="R220" t="n">
-        <v>6700295</v>
+        <v>6700338</v>
       </c>
       <c r="S220" t="n">
         <v>1</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
@@ -28517,10 +28517,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>130049503</v>
+        <v>130050487</v>
       </c>
       <c r="B221" t="n">
-        <v>58611</v>
+        <v>58614</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -28528,21 +28528,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -28557,12 +28557,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -28576,10 +28571,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>675374</v>
+        <v>675372</v>
       </c>
       <c r="R221" t="n">
-        <v>6700338</v>
+        <v>6700347</v>
       </c>
       <c r="S221" t="n">
         <v>1</v>
@@ -28606,12 +28601,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AC221" t="inlineStr">
@@ -28647,10 +28642,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>130048244</v>
+        <v>130050298</v>
       </c>
       <c r="B222" t="n">
-        <v>58575</v>
+        <v>58614</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -28658,21 +28653,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -28706,10 +28701,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>675379</v>
+        <v>675394</v>
       </c>
       <c r="R222" t="n">
-        <v>6700441</v>
+        <v>6700378</v>
       </c>
       <c r="S222" t="n">
         <v>1</v>
@@ -28736,12 +28731,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr">
@@ -28777,10 +28772,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>130049804</v>
+        <v>130049438</v>
       </c>
       <c r="B223" t="n">
-        <v>58601</v>
+        <v>58611</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -28788,21 +28783,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -28815,9 +28810,19 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -28826,10 +28831,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>675381</v>
+        <v>675372</v>
       </c>
       <c r="R223" t="n">
-        <v>6700306</v>
+        <v>6700346</v>
       </c>
       <c r="S223" t="n">
         <v>1</v>
@@ -28856,12 +28861,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AC223" t="inlineStr">
@@ -28897,10 +28902,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>130049856</v>
+        <v>130048186</v>
       </c>
       <c r="B224" t="n">
-        <v>58603</v>
+        <v>58575</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -28908,21 +28913,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -28935,9 +28940,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -28946,10 +28956,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>675441</v>
+        <v>675362</v>
       </c>
       <c r="R224" t="n">
-        <v>6700338</v>
+        <v>6700387</v>
       </c>
       <c r="S224" t="n">
         <v>1</v>
@@ -28976,12 +28986,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
@@ -29017,10 +29027,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>130049848</v>
+        <v>130048227</v>
       </c>
       <c r="B225" t="n">
-        <v>58603</v>
+        <v>58575</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -29028,21 +29038,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -29055,9 +29065,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -29066,10 +29081,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>675366</v>
+        <v>675395</v>
       </c>
       <c r="R225" t="n">
-        <v>6700382</v>
+        <v>6700289</v>
       </c>
       <c r="S225" t="n">
         <v>1</v>
@@ -29096,12 +29111,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AC225" t="inlineStr">
@@ -29137,7 +29152,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>130048252</v>
+        <v>130048132</v>
       </c>
       <c r="B226" t="n">
         <v>58575</v>
@@ -29175,16 +29190,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N226" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -29196,10 +29201,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>675364</v>
+        <v>675433</v>
       </c>
       <c r="R226" t="n">
-        <v>6700411</v>
+        <v>6700327</v>
       </c>
       <c r="S226" t="n">
         <v>1</v>
@@ -29226,12 +29231,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AC226" t="inlineStr">
@@ -29267,10 +29272,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>130050705</v>
+        <v>130048386</v>
       </c>
       <c r="B227" t="n">
-        <v>56684</v>
+        <v>58575</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -29278,16 +29283,16 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100088</v>
+        <v>208245</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -29307,7 +29312,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -29316,10 +29321,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>675413</v>
+        <v>675426</v>
       </c>
       <c r="R227" t="n">
-        <v>6700338</v>
+        <v>6700295</v>
       </c>
       <c r="S227" t="n">
         <v>1</v>
@@ -29346,12 +29351,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AC227" t="inlineStr">
@@ -29387,10 +29392,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>130050487</v>
+        <v>130049522</v>
       </c>
       <c r="B228" t="n">
-        <v>58614</v>
+        <v>58611</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -29398,21 +29403,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -29427,7 +29432,12 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -29441,10 +29451,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>675372</v>
+        <v>675431</v>
       </c>
       <c r="R228" t="n">
-        <v>6700347</v>
+        <v>6700406</v>
       </c>
       <c r="S228" t="n">
         <v>1</v>
@@ -29471,12 +29481,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AC228" t="inlineStr">
@@ -29512,10 +29522,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>130050298</v>
+        <v>130049503</v>
       </c>
       <c r="B229" t="n">
-        <v>58614</v>
+        <v>58611</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -29523,21 +29533,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -29557,12 +29567,12 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -29571,10 +29581,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>675394</v>
+        <v>675374</v>
       </c>
       <c r="R229" t="n">
-        <v>6700378</v>
+        <v>6700338</v>
       </c>
       <c r="S229" t="n">
         <v>1</v>
@@ -29601,12 +29611,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC229" t="inlineStr">
@@ -29642,32 +29652,32 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>130050722</v>
+        <v>130046393</v>
       </c>
       <c r="B230" t="n">
-        <v>56684</v>
+        <v>58598</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100088</v>
+        <v>100119</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -29680,21 +29690,26 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>675368</v>
+        <v>675372</v>
       </c>
       <c r="R230" t="n">
-        <v>6700357</v>
+        <v>6700345</v>
       </c>
       <c r="S230" t="n">
         <v>1</v>
@@ -29719,14 +29734,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>length:28mm|bodymass:2.3g (same size 3)</t>
+        </is>
+      </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="AC230" t="inlineStr">
@@ -29762,32 +29782,32 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>130050716</v>
+        <v>130046297</v>
       </c>
       <c r="B231" t="n">
-        <v>56684</v>
+        <v>58598</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100088</v>
+        <v>100119</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -29800,21 +29820,26 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>675441</v>
+        <v>675433</v>
       </c>
       <c r="R231" t="n">
-        <v>6700338</v>
+        <v>6700345</v>
       </c>
       <c r="S231" t="n">
         <v>1</v>
@@ -29839,14 +29864,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>length:29mm|bodymass:2.2g (same size 2)</t>
+        </is>
+      </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AC231" t="inlineStr">
@@ -29882,32 +29912,32 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>130050526</v>
+        <v>130046476</v>
       </c>
       <c r="B232" t="n">
-        <v>58614</v>
+        <v>58598</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -29927,7 +29957,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -29936,10 +29966,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>675403</v>
+        <v>675375</v>
       </c>
       <c r="R232" t="n">
-        <v>6700425</v>
+        <v>6700326</v>
       </c>
       <c r="S232" t="n">
         <v>1</v>
@@ -29964,14 +29994,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>length:28mm|bodymass:1g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2023-05-16</t>
         </is>
       </c>
       <c r="AC232" t="inlineStr">
@@ -30007,32 +30042,32 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>130046393</v>
+        <v>130049505</v>
       </c>
       <c r="B233" t="n">
-        <v>58598</v>
+        <v>58611</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -30047,12 +30082,17 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -30061,10 +30101,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>675372</v>
+        <v>675432</v>
       </c>
       <c r="R233" t="n">
-        <v>6700345</v>
+        <v>6700375</v>
       </c>
       <c r="S233" t="n">
         <v>1</v>
@@ -30089,19 +30129,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>length:28mm|bodymass:2.3g (same size 3)</t>
-        </is>
-      </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AC233" t="inlineStr">
@@ -30137,32 +30172,32 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>130046297</v>
+        <v>130049493</v>
       </c>
       <c r="B234" t="n">
-        <v>58598</v>
+        <v>58611</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -30177,7 +30212,12 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -30191,10 +30231,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>675433</v>
+        <v>675365</v>
       </c>
       <c r="R234" t="n">
-        <v>6700345</v>
+        <v>6700380</v>
       </c>
       <c r="S234" t="n">
         <v>1</v>
@@ -30219,19 +30259,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X234" t="inlineStr">
-        <is>
-          <t>length:29mm|bodymass:2.2g (same size 2)</t>
-        </is>
-      </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC234" t="inlineStr">
@@ -30267,32 +30302,32 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>130046476</v>
+        <v>130050526</v>
       </c>
       <c r="B235" t="n">
-        <v>58598</v>
+        <v>58614</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100119</v>
+        <v>100141</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -30312,7 +30347,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -30321,10 +30356,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>675375</v>
+        <v>675403</v>
       </c>
       <c r="R235" t="n">
-        <v>6700326</v>
+        <v>6700425</v>
       </c>
       <c r="S235" t="n">
         <v>1</v>
@@ -30349,19 +30384,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>length:28mm|bodymass:1g (same size 1)</t>
-        </is>
-      </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC235" t="inlineStr">
@@ -30397,10 +30427,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>130049505</v>
+        <v>130047344</v>
       </c>
       <c r="B236" t="n">
-        <v>58611</v>
+        <v>58614</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -30408,21 +30438,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -30442,7 +30472,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -30456,10 +30486,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>675432</v>
+        <v>675370</v>
       </c>
       <c r="R236" t="n">
-        <v>6700375</v>
+        <v>6700358</v>
       </c>
       <c r="S236" t="n">
         <v>1</v>
@@ -30484,14 +30514,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>length:60mm|bodymass:5g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="AC236" t="inlineStr">
@@ -30527,10 +30562,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>130049493</v>
+        <v>130048282</v>
       </c>
       <c r="B237" t="n">
-        <v>58611</v>
+        <v>58575</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -30538,16 +30573,16 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -30565,19 +30600,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -30586,10 +30611,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>675365</v>
+        <v>675376</v>
       </c>
       <c r="R237" t="n">
-        <v>6700380</v>
+        <v>6700331</v>
       </c>
       <c r="S237" t="n">
         <v>1</v>
@@ -30616,12 +30641,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AC237" t="inlineStr">
@@ -30657,10 +30682,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>130049457</v>
+        <v>130048133</v>
       </c>
       <c r="B238" t="n">
-        <v>58611</v>
+        <v>58575</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -30668,16 +30693,16 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -30697,12 +30722,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -30716,10 +30736,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>675412</v>
+        <v>675436</v>
       </c>
       <c r="R238" t="n">
-        <v>6700288</v>
+        <v>6700363</v>
       </c>
       <c r="S238" t="n">
         <v>1</v>
@@ -30746,12 +30766,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AC238" t="inlineStr">
@@ -30787,10 +30807,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>130049796</v>
+        <v>130048608</v>
       </c>
       <c r="B239" t="n">
-        <v>58601</v>
+        <v>58575</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -30798,21 +30818,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>208250</v>
+        <v>208245</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -30836,10 +30856,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>675426</v>
+        <v>675373</v>
       </c>
       <c r="R239" t="n">
-        <v>6700296</v>
+        <v>6700437</v>
       </c>
       <c r="S239" t="n">
         <v>1</v>
@@ -30866,12 +30886,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AC239" t="inlineStr">
@@ -30907,7 +30927,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>130048144</v>
+        <v>130048260</v>
       </c>
       <c r="B240" t="n">
         <v>58575</v>
@@ -30947,12 +30967,17 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -30961,10 +30986,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>675369</v>
+        <v>675431</v>
       </c>
       <c r="R240" t="n">
-        <v>6700345</v>
+        <v>6700406</v>
       </c>
       <c r="S240" t="n">
         <v>1</v>
@@ -30991,12 +31016,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC240" t="inlineStr">
@@ -31032,7 +31057,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>130048294</v>
+        <v>130048289</v>
       </c>
       <c r="B241" t="n">
         <v>58575</v>
@@ -31091,10 +31116,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>675362</v>
+        <v>675375</v>
       </c>
       <c r="R241" t="n">
-        <v>6700403</v>
+        <v>6700315</v>
       </c>
       <c r="S241" t="n">
         <v>1</v>
@@ -31162,10 +31187,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>130049815</v>
+        <v>130049457</v>
       </c>
       <c r="B242" t="n">
-        <v>58603</v>
+        <v>58611</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -31173,21 +31198,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -31207,7 +31232,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -31221,10 +31246,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>675389</v>
+        <v>675412</v>
       </c>
       <c r="R242" t="n">
-        <v>6700356</v>
+        <v>6700288</v>
       </c>
       <c r="S242" t="n">
         <v>1</v>
@@ -31251,12 +31276,12 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AC242" t="inlineStr">
@@ -31292,10 +31317,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>130047344</v>
+        <v>130049796</v>
       </c>
       <c r="B243" t="n">
-        <v>58614</v>
+        <v>58601</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -31303,21 +31328,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100141</v>
+        <v>208250</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -31330,16 +31355,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N243" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -31351,10 +31366,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>675370</v>
+        <v>675426</v>
       </c>
       <c r="R243" t="n">
-        <v>6700358</v>
+        <v>6700296</v>
       </c>
       <c r="S243" t="n">
         <v>1</v>
@@ -31379,19 +31394,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X243" t="inlineStr">
-        <is>
-          <t>length:60mm|bodymass:5g (same size 1)</t>
-        </is>
-      </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AC243" t="inlineStr">
@@ -31427,7 +31437,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>130048282</v>
+        <v>130048144</v>
       </c>
       <c r="B244" t="n">
         <v>58575</v>
@@ -31465,6 +31475,11 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N244" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -31476,10 +31491,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>675376</v>
+        <v>675369</v>
       </c>
       <c r="R244" t="n">
-        <v>6700331</v>
+        <v>6700345</v>
       </c>
       <c r="S244" t="n">
         <v>1</v>
@@ -31506,12 +31521,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AC244" t="inlineStr">
@@ -31547,7 +31562,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>130048133</v>
+        <v>130048294</v>
       </c>
       <c r="B245" t="n">
         <v>58575</v>
@@ -31587,12 +31602,17 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
@@ -31601,10 +31621,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>675436</v>
+        <v>675362</v>
       </c>
       <c r="R245" t="n">
-        <v>6700363</v>
+        <v>6700403</v>
       </c>
       <c r="S245" t="n">
         <v>1</v>
@@ -31631,12 +31651,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC245" t="inlineStr">
@@ -31672,10 +31692,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>130048608</v>
+        <v>130049815</v>
       </c>
       <c r="B246" t="n">
-        <v>58575</v>
+        <v>58603</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -31683,21 +31703,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -31710,9 +31730,19 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
@@ -31721,10 +31751,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>675373</v>
+        <v>675389</v>
       </c>
       <c r="R246" t="n">
-        <v>6700437</v>
+        <v>6700356</v>
       </c>
       <c r="S246" t="n">
         <v>1</v>
@@ -31751,12 +31781,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AC246" t="inlineStr">
@@ -31792,10 +31822,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>130048260</v>
+        <v>130050722</v>
       </c>
       <c r="B247" t="n">
-        <v>58575</v>
+        <v>56684</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -31803,16 +31833,16 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>208245</v>
+        <v>100088</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -31830,31 +31860,21 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>675431</v>
+        <v>675368</v>
       </c>
       <c r="R247" t="n">
-        <v>6700406</v>
+        <v>6700357</v>
       </c>
       <c r="S247" t="n">
         <v>1</v>
@@ -31881,12 +31901,12 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC247" t="inlineStr">
@@ -31922,10 +31942,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>130048289</v>
+        <v>130050716</v>
       </c>
       <c r="B248" t="n">
-        <v>58575</v>
+        <v>56684</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -31933,16 +31953,16 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>208245</v>
+        <v>100088</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -31960,16 +31980,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N248" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -31977,14 +31987,14 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>675375</v>
+        <v>675441</v>
       </c>
       <c r="R248" t="n">
-        <v>6700315</v>
+        <v>6700338</v>
       </c>
       <c r="S248" t="n">
         <v>1</v>
@@ -32011,12 +32021,12 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AC248" t="inlineStr">
@@ -34232,32 +34242,32 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>130046469</v>
+        <v>130048265</v>
       </c>
       <c r="B266" t="n">
-        <v>58598</v>
+        <v>58575</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>100119</v>
+        <v>208245</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -34277,7 +34287,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
@@ -34286,10 +34296,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>675384</v>
+        <v>675383</v>
       </c>
       <c r="R266" t="n">
-        <v>6700305</v>
+        <v>6700304</v>
       </c>
       <c r="S266" t="n">
         <v>1</v>
@@ -34314,19 +34324,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X266" t="inlineStr">
-        <is>
-          <t>length:32mm|bodymass:3g (same size 3)</t>
-        </is>
-      </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC266" t="inlineStr">
@@ -34362,32 +34367,32 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>130046434</v>
+        <v>130049847</v>
       </c>
       <c r="B267" t="n">
-        <v>58598</v>
+        <v>58603</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>100119</v>
+        <v>208249</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -34402,7 +34407,12 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -34416,10 +34426,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>675404</v>
+        <v>675374</v>
       </c>
       <c r="R267" t="n">
-        <v>6700427</v>
+        <v>6700338</v>
       </c>
       <c r="S267" t="n">
         <v>1</v>
@@ -34444,19 +34454,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>length:30mm|bodymass:2.8g</t>
-        </is>
-      </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC267" t="inlineStr">
@@ -34492,7 +34497,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>130046428</v>
+        <v>130046469</v>
       </c>
       <c r="B268" t="n">
         <v>58598</v>
@@ -34546,10 +34551,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>675385</v>
+        <v>675384</v>
       </c>
       <c r="R268" t="n">
-        <v>6700298</v>
+        <v>6700305</v>
       </c>
       <c r="S268" t="n">
         <v>1</v>
@@ -34576,17 +34581,17 @@
       </c>
       <c r="X268" t="inlineStr">
         <is>
-          <t>length:35mm|bodymass:4g (same size 1)</t>
+          <t>length:32mm|bodymass:3g (same size 3)</t>
         </is>
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC268" t="inlineStr">
@@ -34622,7 +34627,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>130046369</v>
+        <v>130046434</v>
       </c>
       <c r="B269" t="n">
         <v>58598</v>
@@ -34676,10 +34681,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>675365</v>
+        <v>675404</v>
       </c>
       <c r="R269" t="n">
-        <v>6700380</v>
+        <v>6700427</v>
       </c>
       <c r="S269" t="n">
         <v>1</v>
@@ -34706,17 +34711,17 @@
       </c>
       <c r="X269" t="inlineStr">
         <is>
-          <t>length:32mm|bodymass:3.1g (same size 2)</t>
+          <t>length:30mm|bodymass:2.8g</t>
         </is>
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC269" t="inlineStr">
@@ -34752,32 +34757,32 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>130047404</v>
+        <v>130046428</v>
       </c>
       <c r="B270" t="n">
-        <v>58614</v>
+        <v>58598</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -34792,12 +34797,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -34811,10 +34811,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>675430</v>
+        <v>675385</v>
       </c>
       <c r="R270" t="n">
-        <v>6700305</v>
+        <v>6700298</v>
       </c>
       <c r="S270" t="n">
         <v>1</v>
@@ -34841,17 +34841,17 @@
       </c>
       <c r="X270" t="inlineStr">
         <is>
-          <t>length:69mm|bodymass:5g (same size 1)</t>
+          <t>length:35mm|bodymass:4g (same size 1)</t>
         </is>
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC270" t="inlineStr">
@@ -34887,32 +34887,32 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>130048107</v>
+        <v>130046369</v>
       </c>
       <c r="B271" t="n">
-        <v>58575</v>
+        <v>58598</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>208245</v>
+        <v>100119</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -34927,17 +34927,12 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
@@ -34946,10 +34941,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>675413</v>
+        <v>675365</v>
       </c>
       <c r="R271" t="n">
-        <v>6700425</v>
+        <v>6700380</v>
       </c>
       <c r="S271" t="n">
         <v>1</v>
@@ -34974,14 +34969,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>length:32mm|bodymass:3.1g (same size 2)</t>
+        </is>
+      </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC271" t="inlineStr">
@@ -35017,10 +35017,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>130048178</v>
+        <v>130047404</v>
       </c>
       <c r="B272" t="n">
-        <v>58575</v>
+        <v>58614</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -35028,21 +35028,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -35062,12 +35062,12 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P272" t="inlineStr">
@@ -35076,10 +35076,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>675435</v>
+        <v>675430</v>
       </c>
       <c r="R272" t="n">
-        <v>6700368</v>
+        <v>6700305</v>
       </c>
       <c r="S272" t="n">
         <v>1</v>
@@ -35104,14 +35104,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>length:69mm|bodymass:5g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -35147,7 +35152,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>130048265</v>
+        <v>130048107</v>
       </c>
       <c r="B273" t="n">
         <v>58575</v>
@@ -35187,12 +35192,17 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
@@ -35201,10 +35211,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>675383</v>
+        <v>675413</v>
       </c>
       <c r="R273" t="n">
-        <v>6700304</v>
+        <v>6700425</v>
       </c>
       <c r="S273" t="n">
         <v>1</v>
@@ -35231,12 +35241,12 @@
       </c>
       <c r="Y273" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -35272,10 +35282,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>130049847</v>
+        <v>130048178</v>
       </c>
       <c r="B274" t="n">
-        <v>58603</v>
+        <v>58575</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -35283,21 +35293,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -35317,7 +35327,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -35331,10 +35341,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>675374</v>
+        <v>675435</v>
       </c>
       <c r="R274" t="n">
-        <v>6700338</v>
+        <v>6700368</v>
       </c>
       <c r="S274" t="n">
         <v>1</v>
@@ -35361,12 +35371,12 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -35402,7 +35412,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>130050471</v>
+        <v>130050608</v>
       </c>
       <c r="B275" t="n">
         <v>58614</v>
@@ -35456,10 +35466,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>675368</v>
+        <v>675432</v>
       </c>
       <c r="R275" t="n">
-        <v>6700430</v>
+        <v>6700377</v>
       </c>
       <c r="S275" t="n">
         <v>1</v>
@@ -35486,12 +35496,12 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -35527,7 +35537,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>130050513</v>
+        <v>130050471</v>
       </c>
       <c r="B276" t="n">
         <v>58614</v>
@@ -35581,10 +35591,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>675370</v>
+        <v>675368</v>
       </c>
       <c r="R276" t="n">
-        <v>6700432</v>
+        <v>6700430</v>
       </c>
       <c r="S276" t="n">
         <v>1</v>
@@ -35611,12 +35621,12 @@
       </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -35652,7 +35662,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>130050558</v>
+        <v>130050513</v>
       </c>
       <c r="B277" t="n">
         <v>58614</v>
@@ -35697,7 +35707,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P277" t="inlineStr">
@@ -35706,10 +35716,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>675385</v>
+        <v>675370</v>
       </c>
       <c r="R277" t="n">
-        <v>6700439</v>
+        <v>6700432</v>
       </c>
       <c r="S277" t="n">
         <v>1</v>
@@ -35736,12 +35746,12 @@
       </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -35777,7 +35787,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>130050576</v>
+        <v>130050558</v>
       </c>
       <c r="B278" t="n">
         <v>58614</v>
@@ -35817,17 +35827,12 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L278" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
@@ -35836,7 +35841,7 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>675387</v>
+        <v>675385</v>
       </c>
       <c r="R278" t="n">
         <v>6700439</v>
@@ -35866,12 +35871,12 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -35907,7 +35912,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>130050608</v>
+        <v>130050576</v>
       </c>
       <c r="B279" t="n">
         <v>58614</v>
@@ -35947,7 +35952,12 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -35961,10 +35971,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>675432</v>
+        <v>675387</v>
       </c>
       <c r="R279" t="n">
-        <v>6700377</v>
+        <v>6700439</v>
       </c>
       <c r="S279" t="n">
         <v>1</v>
@@ -35991,12 +36001,12 @@
       </c>
       <c r="Y279" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -36032,32 +36042,32 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>130048231</v>
+        <v>130046335</v>
       </c>
       <c r="B280" t="n">
-        <v>58575</v>
+        <v>58598</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>208245</v>
+        <v>100119</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -36086,10 +36096,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>675404</v>
+        <v>675413</v>
       </c>
       <c r="R280" t="n">
-        <v>6700427</v>
+        <v>6700288</v>
       </c>
       <c r="S280" t="n">
         <v>1</v>
@@ -36114,14 +36124,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>length:40mm|bodymass:6.4g</t>
+        </is>
+      </c>
       <c r="Y280" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -36157,7 +36172,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>130048278</v>
+        <v>130048231</v>
       </c>
       <c r="B281" t="n">
         <v>58575</v>
@@ -36197,17 +36212,12 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
@@ -36216,10 +36226,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>675374</v>
+        <v>675404</v>
       </c>
       <c r="R281" t="n">
-        <v>6700338</v>
+        <v>6700427</v>
       </c>
       <c r="S281" t="n">
         <v>1</v>
@@ -36246,12 +36256,12 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -36287,7 +36297,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>130048288</v>
+        <v>130048278</v>
       </c>
       <c r="B282" t="n">
         <v>58575</v>
@@ -36332,7 +36342,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -36346,10 +36356,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>675395</v>
+        <v>675374</v>
       </c>
       <c r="R282" t="n">
-        <v>6700432</v>
+        <v>6700338</v>
       </c>
       <c r="S282" t="n">
         <v>1</v>
@@ -36376,12 +36386,12 @@
       </c>
       <c r="Y282" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -36417,7 +36427,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>130048316</v>
+        <v>130048288</v>
       </c>
       <c r="B283" t="n">
         <v>58575</v>
@@ -36455,6 +36465,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N283" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -36466,10 +36486,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>675364</v>
+        <v>675395</v>
       </c>
       <c r="R283" t="n">
-        <v>6700419</v>
+        <v>6700432</v>
       </c>
       <c r="S283" t="n">
         <v>1</v>
@@ -36496,12 +36516,12 @@
       </c>
       <c r="Y283" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -36537,32 +36557,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>130046335</v>
+        <v>130047270</v>
       </c>
       <c r="B284" t="n">
-        <v>58598</v>
+        <v>58614</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100119</v>
+        <v>100141</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -36577,12 +36597,17 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P284" t="inlineStr">
@@ -36591,10 +36616,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>675413</v>
+        <v>675398</v>
       </c>
       <c r="R284" t="n">
-        <v>6700288</v>
+        <v>6700432</v>
       </c>
       <c r="S284" t="n">
         <v>1</v>
@@ -36621,17 +36646,17 @@
       </c>
       <c r="X284" t="inlineStr">
         <is>
-          <t>length:40mm|bodymass:6.4g</t>
+          <t>length:67mm|bodymass:6g (same size 4)</t>
         </is>
       </c>
       <c r="Y284" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -36667,10 +36692,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>130047270</v>
+        <v>130048316</v>
       </c>
       <c r="B285" t="n">
-        <v>58614</v>
+        <v>58575</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -36678,21 +36703,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -36705,16 +36730,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L285" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N285" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -36726,10 +36741,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>675398</v>
+        <v>675364</v>
       </c>
       <c r="R285" t="n">
-        <v>6700432</v>
+        <v>6700419</v>
       </c>
       <c r="S285" t="n">
         <v>1</v>
@@ -36754,19 +36769,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X285" t="inlineStr">
-        <is>
-          <t>length:67mm|bodymass:6g (same size 4)</t>
-        </is>
-      </c>
       <c r="Y285" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -48052,10 +48062,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>130047381</v>
+        <v>130048307</v>
       </c>
       <c r="B375" t="n">
-        <v>58614</v>
+        <v>58575</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -48063,21 +48073,21 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -48090,16 +48100,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L375" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N375" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -48111,10 +48111,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>675437</v>
+        <v>675387</v>
       </c>
       <c r="R375" t="n">
-        <v>6700371</v>
+        <v>6700440</v>
       </c>
       <c r="S375" t="n">
         <v>1</v>
@@ -48139,19 +48139,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X375" t="inlineStr">
-        <is>
-          <t>length:67mm|bodymass:7g (same size 1)</t>
-        </is>
-      </c>
       <c r="Y375" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC375" t="inlineStr">
@@ -48187,10 +48182,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>130047383</v>
+        <v>130048234</v>
       </c>
       <c r="B376" t="n">
-        <v>58614</v>
+        <v>58575</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -48198,21 +48193,21 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -48246,10 +48241,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>675416</v>
+        <v>675406</v>
       </c>
       <c r="R376" t="n">
-        <v>6700429</v>
+        <v>6700288</v>
       </c>
       <c r="S376" t="n">
         <v>1</v>
@@ -48274,19 +48269,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X376" t="inlineStr">
-        <is>
-          <t>length:85mm|bodymass:12g</t>
-        </is>
-      </c>
       <c r="Y376" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -48322,32 +48312,32 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>130046471</v>
+        <v>130049814</v>
       </c>
       <c r="B377" t="n">
-        <v>58598</v>
+        <v>58603</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>100119</v>
+        <v>208249</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -48362,12 +48352,12 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P377" t="inlineStr">
@@ -48376,10 +48366,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>675435</v>
+        <v>675433</v>
       </c>
       <c r="R377" t="n">
-        <v>6700393</v>
+        <v>6700345</v>
       </c>
       <c r="S377" t="n">
         <v>1</v>
@@ -48404,19 +48394,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X377" t="inlineStr">
-        <is>
-          <t>length:34mm|bodymass:4g (same size 1)</t>
-        </is>
-      </c>
       <c r="Y377" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -48452,32 +48437,32 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>130046570</v>
+        <v>130049829</v>
       </c>
       <c r="B378" t="n">
-        <v>58598</v>
+        <v>58603</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>100119</v>
+        <v>208249</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -48490,16 +48475,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L378" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N378" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -48511,10 +48486,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>675364</v>
+        <v>675392</v>
       </c>
       <c r="R378" t="n">
-        <v>6700419</v>
+        <v>6700435</v>
       </c>
       <c r="S378" t="n">
         <v>1</v>
@@ -48539,19 +48514,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X378" t="inlineStr">
-        <is>
-          <t>chip:23376|capture:2|length:47mm|bodymass:12.5g|Bd:Negative</t>
-        </is>
-      </c>
       <c r="Y378" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC378" t="inlineStr">
@@ -48587,32 +48557,32 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>130046382</v>
+        <v>130049528</v>
       </c>
       <c r="B379" t="n">
-        <v>58598</v>
+        <v>58611</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -48627,7 +48597,12 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -48641,10 +48616,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>675394</v>
+        <v>675431</v>
       </c>
       <c r="R379" t="n">
-        <v>6700431</v>
+        <v>6700401</v>
       </c>
       <c r="S379" t="n">
         <v>1</v>
@@ -48669,19 +48644,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X379" t="inlineStr">
-        <is>
-          <t>length:28mm|bodymass:2.1g</t>
-        </is>
-      </c>
       <c r="Y379" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC379" t="inlineStr">
@@ -48717,10 +48687,10 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>130047400</v>
+        <v>130049485</v>
       </c>
       <c r="B380" t="n">
-        <v>58614</v>
+        <v>58611</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -48728,21 +48698,21 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -48776,10 +48746,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>675438</v>
+        <v>675439</v>
       </c>
       <c r="R380" t="n">
-        <v>6700368</v>
+        <v>6700347</v>
       </c>
       <c r="S380" t="n">
         <v>1</v>
@@ -48804,19 +48774,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X380" t="inlineStr">
-        <is>
-          <t>length:60mm|bodymass:8g</t>
-        </is>
-      </c>
       <c r="Y380" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC380" t="inlineStr">
@@ -48852,10 +48817,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>130049528</v>
+        <v>130047381</v>
       </c>
       <c r="B381" t="n">
-        <v>58611</v>
+        <v>58614</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -48863,21 +48828,21 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -48911,10 +48876,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>675431</v>
+        <v>675437</v>
       </c>
       <c r="R381" t="n">
-        <v>6700401</v>
+        <v>6700371</v>
       </c>
       <c r="S381" t="n">
         <v>1</v>
@@ -48939,14 +48904,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X381" t="inlineStr">
+        <is>
+          <t>length:67mm|bodymass:7g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y381" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -48982,10 +48952,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>130049485</v>
+        <v>130047383</v>
       </c>
       <c r="B382" t="n">
-        <v>58611</v>
+        <v>58614</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -48993,21 +48963,21 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -49027,7 +48997,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -49041,10 +49011,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>675439</v>
+        <v>675416</v>
       </c>
       <c r="R382" t="n">
-        <v>6700347</v>
+        <v>6700429</v>
       </c>
       <c r="S382" t="n">
         <v>1</v>
@@ -49069,14 +49039,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X382" t="inlineStr">
+        <is>
+          <t>length:85mm|bodymass:12g</t>
+        </is>
+      </c>
       <c r="Y382" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -49112,32 +49087,32 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>130048307</v>
+        <v>130046471</v>
       </c>
       <c r="B383" t="n">
-        <v>58575</v>
+        <v>58598</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>208245</v>
+        <v>100119</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -49150,6 +49125,11 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N383" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -49161,10 +49141,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>675387</v>
+        <v>675435</v>
       </c>
       <c r="R383" t="n">
-        <v>6700440</v>
+        <v>6700393</v>
       </c>
       <c r="S383" t="n">
         <v>1</v>
@@ -49189,14 +49169,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X383" t="inlineStr">
+        <is>
+          <t>length:34mm|bodymass:4g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y383" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -49232,32 +49217,32 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>130048234</v>
+        <v>130046570</v>
       </c>
       <c r="B384" t="n">
-        <v>58575</v>
+        <v>58598</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>208245</v>
+        <v>100119</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -49277,7 +49262,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -49291,10 +49276,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>675406</v>
+        <v>675364</v>
       </c>
       <c r="R384" t="n">
-        <v>6700288</v>
+        <v>6700419</v>
       </c>
       <c r="S384" t="n">
         <v>1</v>
@@ -49319,14 +49304,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X384" t="inlineStr">
+        <is>
+          <t>chip:23376|capture:2|length:47mm|bodymass:12.5g|Bd:Negative</t>
+        </is>
+      </c>
       <c r="Y384" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -49362,32 +49352,32 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>130049814</v>
+        <v>130046382</v>
       </c>
       <c r="B385" t="n">
-        <v>58603</v>
+        <v>58598</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>208249</v>
+        <v>100119</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -49402,12 +49392,12 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P385" t="inlineStr">
@@ -49416,10 +49406,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>675433</v>
+        <v>675394</v>
       </c>
       <c r="R385" t="n">
-        <v>6700345</v>
+        <v>6700431</v>
       </c>
       <c r="S385" t="n">
         <v>1</v>
@@ -49444,14 +49434,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>length:28mm|bodymass:2.1g</t>
+        </is>
+      </c>
       <c r="Y385" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -49487,10 +49482,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>130049829</v>
+        <v>130047400</v>
       </c>
       <c r="B386" t="n">
-        <v>58603</v>
+        <v>58614</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -49498,21 +49493,21 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>208249</v>
+        <v>100141</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -49525,6 +49520,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N386" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -49536,10 +49541,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>675392</v>
+        <v>675438</v>
       </c>
       <c r="R386" t="n">
-        <v>6700435</v>
+        <v>6700368</v>
       </c>
       <c r="S386" t="n">
         <v>1</v>
@@ -49564,14 +49569,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>length:60mm|bodymass:8g</t>
+        </is>
+      </c>
       <c r="Y386" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -49607,32 +49617,32 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>130046341</v>
+        <v>130050775</v>
       </c>
       <c r="B387" t="n">
-        <v>58598</v>
+        <v>56694</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>100119</v>
+        <v>208260</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -49645,26 +49655,21 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>675366</v>
+        <v>675438</v>
       </c>
       <c r="R387" t="n">
-        <v>6700423</v>
+        <v>6700346</v>
       </c>
       <c r="S387" t="n">
         <v>1</v>
@@ -49689,19 +49694,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X387" t="inlineStr">
-        <is>
-          <t>length:30mm|bodymass:3.7g</t>
-        </is>
-      </c>
       <c r="Y387" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -49737,32 +49737,32 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>130048110</v>
+        <v>130046341</v>
       </c>
       <c r="B388" t="n">
-        <v>58575</v>
+        <v>58598</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>208245</v>
+        <v>100119</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -49782,7 +49782,7 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P388" t="inlineStr">
@@ -49791,10 +49791,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>675372</v>
+        <v>675366</v>
       </c>
       <c r="R388" t="n">
-        <v>6700344</v>
+        <v>6700423</v>
       </c>
       <c r="S388" t="n">
         <v>1</v>
@@ -49819,14 +49819,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X388" t="inlineStr">
+        <is>
+          <t>length:30mm|bodymass:3.7g</t>
+        </is>
+      </c>
       <c r="Y388" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -49862,7 +49867,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>130048088</v>
+        <v>130048110</v>
       </c>
       <c r="B389" t="n">
         <v>58575</v>
@@ -49902,12 +49907,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L389" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -49921,10 +49921,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>675360</v>
+        <v>675372</v>
       </c>
       <c r="R389" t="n">
-        <v>6700403</v>
+        <v>6700344</v>
       </c>
       <c r="S389" t="n">
         <v>1</v>
@@ -49951,12 +49951,12 @@
       </c>
       <c r="Y389" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">
@@ -49992,7 +49992,7 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>130048191</v>
+        <v>130048088</v>
       </c>
       <c r="B390" t="n">
         <v>58575</v>
@@ -50032,7 +50032,12 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -50046,10 +50051,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>675398</v>
+        <v>675360</v>
       </c>
       <c r="R390" t="n">
-        <v>6700432</v>
+        <v>6700403</v>
       </c>
       <c r="S390" t="n">
         <v>1</v>
@@ -50076,12 +50081,12 @@
       </c>
       <c r="Y390" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AC390" t="inlineStr">
@@ -50117,10 +50122,10 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>130049463</v>
+        <v>130048191</v>
       </c>
       <c r="B391" t="n">
-        <v>58611</v>
+        <v>58575</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -50128,16 +50133,16 @@
         </is>
       </c>
       <c r="E391" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -50157,12 +50162,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L391" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -50176,10 +50176,10 @@
         </is>
       </c>
       <c r="Q391" t="n">
-        <v>675366</v>
+        <v>675398</v>
       </c>
       <c r="R391" t="n">
-        <v>6700423</v>
+        <v>6700432</v>
       </c>
       <c r="S391" t="n">
         <v>1</v>
@@ -50206,12 +50206,12 @@
       </c>
       <c r="Y391" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA391" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC391" t="inlineStr">
@@ -50247,7 +50247,7 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>130049526</v>
+        <v>130049463</v>
       </c>
       <c r="B392" t="n">
         <v>58611</v>
@@ -50292,7 +50292,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -50306,10 +50306,10 @@
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>675371</v>
+        <v>675366</v>
       </c>
       <c r="R392" t="n">
-        <v>6700349</v>
+        <v>6700423</v>
       </c>
       <c r="S392" t="n">
         <v>1</v>
@@ -50336,12 +50336,12 @@
       </c>
       <c r="Y392" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA392" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AC392" t="inlineStr">
@@ -50377,10 +50377,10 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>130050612</v>
+        <v>130049526</v>
       </c>
       <c r="B393" t="n">
-        <v>58614</v>
+        <v>58611</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -50388,21 +50388,21 @@
         </is>
       </c>
       <c r="E393" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -50436,10 +50436,10 @@
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>675441</v>
+        <v>675371</v>
       </c>
       <c r="R393" t="n">
-        <v>6700338</v>
+        <v>6700349</v>
       </c>
       <c r="S393" t="n">
         <v>1</v>
@@ -50466,12 +50466,12 @@
       </c>
       <c r="Y393" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA393" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC393" t="inlineStr">
@@ -50507,10 +50507,10 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>130050693</v>
+        <v>130049800</v>
       </c>
       <c r="B394" t="n">
-        <v>56673</v>
+        <v>58601</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -50518,21 +50518,21 @@
         </is>
       </c>
       <c r="E394" t="n">
-        <v>208255</v>
+        <v>208250</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -50552,14 +50552,14 @@
       </c>
       <c r="P394" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>675379</v>
+        <v>675430</v>
       </c>
       <c r="R394" t="n">
-        <v>6700309</v>
+        <v>6700324</v>
       </c>
       <c r="S394" t="n">
         <v>1</v>
@@ -50586,12 +50586,12 @@
       </c>
       <c r="Y394" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA394" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC394" t="inlineStr">
@@ -50627,10 +50627,10 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>130050775</v>
+        <v>130050612</v>
       </c>
       <c r="B395" t="n">
-        <v>56694</v>
+        <v>58614</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -50638,21 +50638,21 @@
         </is>
       </c>
       <c r="E395" t="n">
-        <v>208260</v>
+        <v>100141</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -50665,6 +50665,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N395" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -50672,14 +50682,14 @@
       </c>
       <c r="P395" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>675438</v>
+        <v>675441</v>
       </c>
       <c r="R395" t="n">
-        <v>6700346</v>
+        <v>6700338</v>
       </c>
       <c r="S395" t="n">
         <v>1</v>
@@ -50706,12 +50716,12 @@
       </c>
       <c r="Y395" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA395" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AC395" t="inlineStr">
@@ -50747,10 +50757,10 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>130049800</v>
+        <v>130050693</v>
       </c>
       <c r="B396" t="n">
-        <v>58601</v>
+        <v>56673</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -50758,21 +50768,21 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>208250</v>
+        <v>208255</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -50792,14 +50802,14 @@
       </c>
       <c r="P396" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>675430</v>
+        <v>675379</v>
       </c>
       <c r="R396" t="n">
-        <v>6700324</v>
+        <v>6700309</v>
       </c>
       <c r="S396" t="n">
         <v>1</v>
@@ -50826,12 +50836,12 @@
       </c>
       <c r="Y396" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA396" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AC396" t="inlineStr">

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -16332,7 +16332,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130047359</v>
+        <v>130047269</v>
       </c>
       <c r="B125" t="n">
         <v>58699</v>
@@ -16391,10 +16391,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>675408</v>
+        <v>675373</v>
       </c>
       <c r="R125" t="n">
-        <v>6700292</v>
+        <v>6700437</v>
       </c>
       <c r="S125" t="n">
         <v>1</v>
@@ -16421,17 +16421,17 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>length:65mm|bodymass:6g (same size 1)</t>
+          <t>length:61mm|bodymass:4g (same size 1)</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -16467,32 +16467,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130047269</v>
+        <v>130046321</v>
       </c>
       <c r="B126" t="n">
-        <v>58699</v>
+        <v>58683</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -16507,17 +16507,12 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -16526,10 +16521,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>675373</v>
+        <v>675393</v>
       </c>
       <c r="R126" t="n">
-        <v>6700437</v>
+        <v>6700366</v>
       </c>
       <c r="S126" t="n">
         <v>1</v>
@@ -16556,17 +16551,17 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>length:61mm|bodymass:4g (same size 1)</t>
+          <t>length:31mm|bodymass:4g</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -16602,7 +16597,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130050198</v>
+        <v>130047146</v>
       </c>
       <c r="B127" t="n">
         <v>58699</v>
@@ -16642,12 +16637,17 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -16656,10 +16656,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>675393</v>
+        <v>675432</v>
       </c>
       <c r="R127" t="n">
-        <v>6700366</v>
+        <v>6700388</v>
       </c>
       <c r="S127" t="n">
         <v>1</v>
@@ -16684,14 +16684,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>length:45mm|bodymass:2g</t>
+        </is>
+      </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -16727,32 +16732,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130046321</v>
+        <v>130047208</v>
       </c>
       <c r="B128" t="n">
-        <v>58683</v>
+        <v>58699</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100119</v>
+        <v>100141</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -16767,7 +16772,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -16781,10 +16791,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>675393</v>
+        <v>675379</v>
       </c>
       <c r="R128" t="n">
-        <v>6700366</v>
+        <v>6700441</v>
       </c>
       <c r="S128" t="n">
         <v>1</v>
@@ -16811,17 +16821,17 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>length:31mm|bodymass:4g</t>
+          <t>length:64mm|bodymass:5g (same size 4)</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -16857,7 +16867,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130047146</v>
+        <v>130047359</v>
       </c>
       <c r="B129" t="n">
         <v>58699</v>
@@ -16916,10 +16926,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>675432</v>
+        <v>675408</v>
       </c>
       <c r="R129" t="n">
-        <v>6700388</v>
+        <v>6700292</v>
       </c>
       <c r="S129" t="n">
         <v>1</v>
@@ -16946,17 +16956,17 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>length:45mm|bodymass:2g</t>
+          <t>length:65mm|bodymass:6g (same size 1)</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -16992,10 +17002,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130047208</v>
+        <v>130049623</v>
       </c>
       <c r="B130" t="n">
-        <v>58699</v>
+        <v>58696</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -17003,21 +17013,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -17042,7 +17052,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -17051,10 +17061,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>675379</v>
+        <v>675373</v>
       </c>
       <c r="R130" t="n">
-        <v>6700441</v>
+        <v>6700437</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -17079,19 +17089,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>length:64mm|bodymass:5g (same size 4)</t>
-        </is>
-      </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -17127,7 +17132,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130049697</v>
+        <v>130049627</v>
       </c>
       <c r="B131" t="n">
         <v>58696</v>
@@ -17165,9 +17170,19 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -17176,10 +17191,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>675414</v>
+        <v>675432</v>
       </c>
       <c r="R131" t="n">
-        <v>6700288</v>
+        <v>6700388</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -17206,12 +17221,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -17247,7 +17262,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130049623</v>
+        <v>130049631</v>
       </c>
       <c r="B132" t="n">
         <v>58696</v>
@@ -17292,7 +17307,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -17309,7 +17324,7 @@
         <v>675373</v>
       </c>
       <c r="R132" t="n">
-        <v>6700437</v>
+        <v>6700355</v>
       </c>
       <c r="S132" t="n">
         <v>1</v>
@@ -17336,12 +17351,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -17377,7 +17392,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130049627</v>
+        <v>130049479</v>
       </c>
       <c r="B133" t="n">
         <v>58696</v>
@@ -17422,12 +17437,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -17436,10 +17451,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>675432</v>
+        <v>675412</v>
       </c>
       <c r="R133" t="n">
-        <v>6700388</v>
+        <v>6700424</v>
       </c>
       <c r="S133" t="n">
         <v>1</v>
@@ -17466,12 +17481,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -17507,7 +17522,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130049631</v>
+        <v>130049530</v>
       </c>
       <c r="B134" t="n">
         <v>58696</v>
@@ -17566,10 +17581,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>675373</v>
+        <v>675392</v>
       </c>
       <c r="R134" t="n">
-        <v>6700355</v>
+        <v>6700435</v>
       </c>
       <c r="S134" t="n">
         <v>1</v>
@@ -17596,12 +17611,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -17637,7 +17652,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130049479</v>
+        <v>130049684</v>
       </c>
       <c r="B135" t="n">
         <v>58696</v>
@@ -17675,16 +17690,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N135" t="inlineStr">
         <is>
           <t>fälla</t>
@@ -17696,10 +17701,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>675412</v>
+        <v>675381</v>
       </c>
       <c r="R135" t="n">
-        <v>6700424</v>
+        <v>6700306</v>
       </c>
       <c r="S135" t="n">
         <v>1</v>
@@ -17726,12 +17731,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -17767,7 +17772,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130049470</v>
+        <v>130049494</v>
       </c>
       <c r="B136" t="n">
         <v>58696</v>
@@ -17817,7 +17822,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -17826,10 +17831,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>675433</v>
+        <v>675364</v>
       </c>
       <c r="R136" t="n">
-        <v>6700327</v>
+        <v>6700411</v>
       </c>
       <c r="S136" t="n">
         <v>1</v>
@@ -17856,12 +17861,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -17897,10 +17902,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130049530</v>
+        <v>130048192</v>
       </c>
       <c r="B137" t="n">
-        <v>58696</v>
+        <v>58660</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -17908,16 +17913,16 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -17937,12 +17942,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -17956,10 +17956,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>675392</v>
+        <v>675399</v>
       </c>
       <c r="R137" t="n">
-        <v>6700435</v>
+        <v>6700431</v>
       </c>
       <c r="S137" t="n">
         <v>1</v>
@@ -17986,12 +17986,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -18027,10 +18027,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130049684</v>
+        <v>130048196</v>
       </c>
       <c r="B138" t="n">
-        <v>58696</v>
+        <v>58660</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -18038,16 +18038,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -18065,9 +18065,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -18076,10 +18081,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>675381</v>
+        <v>675438</v>
       </c>
       <c r="R138" t="n">
-        <v>6700306</v>
+        <v>6700351</v>
       </c>
       <c r="S138" t="n">
         <v>1</v>
@@ -18106,12 +18111,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -18147,10 +18152,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130049494</v>
+        <v>130048194</v>
       </c>
       <c r="B139" t="n">
-        <v>58696</v>
+        <v>58660</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -18158,16 +18163,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -18187,17 +18192,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -18206,10 +18206,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>675364</v>
+        <v>675424</v>
       </c>
       <c r="R139" t="n">
-        <v>6700411</v>
+        <v>6700424</v>
       </c>
       <c r="S139" t="n">
         <v>1</v>
@@ -18236,12 +18236,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -18277,7 +18277,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130048541</v>
+        <v>130048247</v>
       </c>
       <c r="B140" t="n">
         <v>58660</v>
@@ -18315,6 +18315,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -18326,10 +18336,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>675432</v>
+        <v>675369</v>
       </c>
       <c r="R140" t="n">
-        <v>6700388</v>
+        <v>6700355</v>
       </c>
       <c r="S140" t="n">
         <v>1</v>
@@ -18356,12 +18366,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -18397,7 +18407,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130048192</v>
+        <v>130048188</v>
       </c>
       <c r="B141" t="n">
         <v>58660</v>
@@ -18451,10 +18461,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>675399</v>
+        <v>675392</v>
       </c>
       <c r="R141" t="n">
-        <v>6700431</v>
+        <v>6700435</v>
       </c>
       <c r="S141" t="n">
         <v>1</v>
@@ -18522,7 +18532,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130048196</v>
+        <v>130048280</v>
       </c>
       <c r="B142" t="n">
         <v>58660</v>
@@ -18560,14 +18570,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -18576,10 +18581,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>675438</v>
+        <v>675372</v>
       </c>
       <c r="R142" t="n">
-        <v>6700351</v>
+        <v>6700346</v>
       </c>
       <c r="S142" t="n">
         <v>1</v>
@@ -18606,12 +18611,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
@@ -18647,10 +18652,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130048194</v>
+        <v>130049875</v>
       </c>
       <c r="B143" t="n">
-        <v>58660</v>
+        <v>58688</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -18658,21 +18663,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -18685,14 +18690,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -18701,10 +18701,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>675424</v>
+        <v>675372</v>
       </c>
       <c r="R143" t="n">
-        <v>6700424</v>
+        <v>6700346</v>
       </c>
       <c r="S143" t="n">
         <v>1</v>
@@ -18731,12 +18731,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
@@ -18772,7 +18772,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130048247</v>
+        <v>130048143</v>
       </c>
       <c r="B144" t="n">
         <v>58660</v>
@@ -18810,19 +18810,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -18831,10 +18821,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>675369</v>
+        <v>675412</v>
       </c>
       <c r="R144" t="n">
-        <v>6700355</v>
+        <v>6700288</v>
       </c>
       <c r="S144" t="n">
         <v>1</v>
@@ -18861,12 +18851,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
@@ -18902,7 +18892,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130048188</v>
+        <v>130048314</v>
       </c>
       <c r="B145" t="n">
         <v>58660</v>
@@ -18956,10 +18946,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>675392</v>
+        <v>675429</v>
       </c>
       <c r="R145" t="n">
-        <v>6700435</v>
+        <v>6700323</v>
       </c>
       <c r="S145" t="n">
         <v>1</v>
@@ -18986,12 +18976,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
@@ -19027,7 +19017,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130048280</v>
+        <v>130048156</v>
       </c>
       <c r="B146" t="n">
         <v>58660</v>
@@ -19065,9 +19055,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -19076,10 +19071,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>675372</v>
+        <v>675371</v>
       </c>
       <c r="R146" t="n">
-        <v>6700346</v>
+        <v>6700349</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -19106,12 +19101,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
@@ -19147,10 +19142,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130049875</v>
+        <v>130049697</v>
       </c>
       <c r="B147" t="n">
-        <v>58688</v>
+        <v>58696</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -19158,21 +19153,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -19196,10 +19191,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>675372</v>
+        <v>675414</v>
       </c>
       <c r="R147" t="n">
-        <v>6700346</v>
+        <v>6700288</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -19226,12 +19221,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
@@ -19267,10 +19262,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130048143</v>
+        <v>130049470</v>
       </c>
       <c r="B148" t="n">
-        <v>58660</v>
+        <v>58696</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -19278,16 +19273,16 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -19305,9 +19300,19 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -19316,10 +19321,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>675412</v>
+        <v>675433</v>
       </c>
       <c r="R148" t="n">
-        <v>6700288</v>
+        <v>6700327</v>
       </c>
       <c r="S148" t="n">
         <v>1</v>
@@ -19346,12 +19351,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
@@ -19387,7 +19392,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130048314</v>
+        <v>130048541</v>
       </c>
       <c r="B149" t="n">
         <v>58660</v>
@@ -19425,11 +19430,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -19441,10 +19441,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>675429</v>
+        <v>675432</v>
       </c>
       <c r="R149" t="n">
-        <v>6700323</v>
+        <v>6700388</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -19471,12 +19471,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
@@ -19512,10 +19512,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130048156</v>
+        <v>130049836</v>
       </c>
       <c r="B150" t="n">
-        <v>58660</v>
+        <v>58688</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -19523,21 +19523,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -19552,12 +19552,17 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -19566,10 +19571,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>675371</v>
+        <v>675404</v>
       </c>
       <c r="R150" t="n">
-        <v>6700349</v>
+        <v>6700427</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -19596,12 +19601,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
@@ -19637,10 +19642,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130049836</v>
+        <v>130049809</v>
       </c>
       <c r="B151" t="n">
-        <v>58688</v>
+        <v>58686</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -19648,21 +19653,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>208249</v>
+        <v>208250</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -19675,16 +19680,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N151" t="inlineStr">
         <is>
           <t>fälla</t>
@@ -19696,10 +19691,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>675404</v>
+        <v>675435</v>
       </c>
       <c r="R151" t="n">
-        <v>6700427</v>
+        <v>6700368</v>
       </c>
       <c r="S151" t="n">
         <v>1</v>
@@ -19726,12 +19721,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
@@ -19767,10 +19762,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130049809</v>
+        <v>130050709</v>
       </c>
       <c r="B152" t="n">
-        <v>58686</v>
+        <v>56769</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -19778,21 +19773,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>208250</v>
+        <v>100088</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -19807,19 +19802,19 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>675435</v>
+        <v>675430</v>
       </c>
       <c r="R152" t="n">
-        <v>6700368</v>
+        <v>6700417</v>
       </c>
       <c r="S152" t="n">
         <v>1</v>
@@ -19846,12 +19841,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
@@ -20017,7 +20012,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130050517</v>
+        <v>130050198</v>
       </c>
       <c r="B154" t="n">
         <v>58699</v>
@@ -20071,10 +20066,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>675412</v>
+        <v>675393</v>
       </c>
       <c r="R154" t="n">
-        <v>6700424</v>
+        <v>6700366</v>
       </c>
       <c r="S154" t="n">
         <v>1</v>
@@ -20101,12 +20096,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
@@ -20142,10 +20137,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130050709</v>
+        <v>130050517</v>
       </c>
       <c r="B155" t="n">
-        <v>56769</v>
+        <v>58699</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -20153,21 +20148,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100088</v>
+        <v>100141</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -20180,21 +20175,26 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>675430</v>
+        <v>675412</v>
       </c>
       <c r="R155" t="n">
-        <v>6700417</v>
+        <v>6700424</v>
       </c>
       <c r="S155" t="n">
         <v>1</v>
@@ -20221,12 +20221,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
@@ -20387,10 +20387,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130047393</v>
+        <v>130050779</v>
       </c>
       <c r="B157" t="n">
-        <v>58699</v>
+        <v>56750</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -20398,21 +20398,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100141</v>
+        <v>208257</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -20425,31 +20425,21 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>675430</v>
+        <v>675375</v>
       </c>
       <c r="R157" t="n">
-        <v>6700409</v>
+        <v>6700315</v>
       </c>
       <c r="S157" t="n">
         <v>1</v>
@@ -20474,19 +20464,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>length:70mm|bodymass:5g (same size 2)</t>
-        </is>
-      </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
@@ -20522,7 +20507,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130047387</v>
+        <v>130050578</v>
       </c>
       <c r="B158" t="n">
         <v>58699</v>
@@ -20581,10 +20566,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>675414</v>
+        <v>675403</v>
       </c>
       <c r="R158" t="n">
-        <v>6700288</v>
+        <v>6700428</v>
       </c>
       <c r="S158" t="n">
         <v>1</v>
@@ -20609,19 +20594,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>length:76mm|bodymass:6g</t>
-        </is>
-      </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
@@ -20657,10 +20637,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130049447</v>
+        <v>130050259</v>
       </c>
       <c r="B159" t="n">
-        <v>58696</v>
+        <v>58699</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -20668,21 +20648,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -20716,10 +20696,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>675366</v>
+        <v>675413</v>
       </c>
       <c r="R159" t="n">
-        <v>6700382</v>
+        <v>6700338</v>
       </c>
       <c r="S159" t="n">
         <v>1</v>
@@ -20746,12 +20726,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
@@ -20787,10 +20767,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130049702</v>
+        <v>130050468</v>
       </c>
       <c r="B160" t="n">
-        <v>58696</v>
+        <v>58699</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -20798,21 +20778,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -20825,9 +20805,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -20836,10 +20821,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>675430</v>
+        <v>675395</v>
       </c>
       <c r="R160" t="n">
-        <v>6700409</v>
+        <v>6700432</v>
       </c>
       <c r="S160" t="n">
         <v>1</v>
@@ -20866,12 +20851,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
@@ -20907,10 +20892,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130049532</v>
+        <v>130050542</v>
       </c>
       <c r="B161" t="n">
-        <v>58696</v>
+        <v>58699</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -20918,21 +20903,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -20947,12 +20932,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -20966,10 +20946,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>675438</v>
+        <v>675370</v>
       </c>
       <c r="R161" t="n">
-        <v>6700349</v>
+        <v>6700367</v>
       </c>
       <c r="S161" t="n">
         <v>1</v>
@@ -20996,12 +20976,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
@@ -21037,10 +21017,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130049629</v>
+        <v>130050491</v>
       </c>
       <c r="B162" t="n">
-        <v>58696</v>
+        <v>58699</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21048,21 +21028,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -21077,17 +21057,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -21096,10 +21071,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>675436</v>
+        <v>675431</v>
       </c>
       <c r="R162" t="n">
-        <v>6700363</v>
+        <v>6700401</v>
       </c>
       <c r="S162" t="n">
         <v>1</v>
@@ -21126,12 +21101,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
@@ -21167,10 +21142,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>130048254</v>
+        <v>130047148</v>
       </c>
       <c r="B163" t="n">
-        <v>58660</v>
+        <v>58699</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -21178,21 +21153,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -21212,7 +21187,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -21226,10 +21201,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>675372</v>
+        <v>675430</v>
       </c>
       <c r="R163" t="n">
-        <v>6700433</v>
+        <v>6700324</v>
       </c>
       <c r="S163" t="n">
         <v>1</v>
@@ -21254,14 +21229,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>length:68mm|bodymass:6g (same size 6)</t>
+        </is>
+      </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
@@ -21297,10 +21277,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130048184</v>
+        <v>130049759</v>
       </c>
       <c r="B164" t="n">
-        <v>58660</v>
+        <v>58696</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -21308,16 +21288,16 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -21335,14 +21315,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -21351,10 +21326,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>675370</v>
+        <v>675430</v>
       </c>
       <c r="R164" t="n">
-        <v>6700351</v>
+        <v>6700409</v>
       </c>
       <c r="S164" t="n">
         <v>1</v>
@@ -21381,12 +21356,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
@@ -21422,10 +21397,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130048236</v>
+        <v>130049532</v>
       </c>
       <c r="B165" t="n">
-        <v>58660</v>
+        <v>58696</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -21433,16 +21408,16 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -21462,7 +21437,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -21476,10 +21456,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>675394</v>
+        <v>675438</v>
       </c>
       <c r="R165" t="n">
-        <v>6700289</v>
+        <v>6700349</v>
       </c>
       <c r="S165" t="n">
         <v>1</v>
@@ -21506,12 +21486,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
@@ -21547,10 +21527,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>130048185</v>
+        <v>130049629</v>
       </c>
       <c r="B166" t="n">
-        <v>58660</v>
+        <v>58696</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -21558,16 +21538,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -21587,7 +21567,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -21601,10 +21586,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>675357</v>
+        <v>675436</v>
       </c>
       <c r="R166" t="n">
-        <v>6700392</v>
+        <v>6700363</v>
       </c>
       <c r="S166" t="n">
         <v>1</v>
@@ -21631,12 +21616,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr">
@@ -21672,10 +21657,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>130049867</v>
+        <v>130049432</v>
       </c>
       <c r="B167" t="n">
-        <v>58688</v>
+        <v>58696</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -21683,21 +21668,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -21710,9 +21695,19 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -21721,10 +21716,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>675414</v>
+        <v>675371</v>
       </c>
       <c r="R167" t="n">
-        <v>6700424</v>
+        <v>6700345</v>
       </c>
       <c r="S167" t="n">
         <v>1</v>
@@ -21751,12 +21746,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
@@ -21792,10 +21787,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130049871</v>
+        <v>130048254</v>
       </c>
       <c r="B168" t="n">
-        <v>58688</v>
+        <v>58660</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -21803,21 +21798,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -21830,9 +21825,19 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -21841,10 +21846,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>675381</v>
+        <v>675372</v>
       </c>
       <c r="R168" t="n">
-        <v>6700306</v>
+        <v>6700433</v>
       </c>
       <c r="S168" t="n">
         <v>1</v>
@@ -21871,12 +21876,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC168" t="inlineStr">
@@ -21912,7 +21917,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>130048255</v>
+        <v>130048184</v>
       </c>
       <c r="B169" t="n">
         <v>58660</v>
@@ -21952,12 +21957,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -21971,10 +21971,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>675381</v>
+        <v>675370</v>
       </c>
       <c r="R169" t="n">
-        <v>6700440</v>
+        <v>6700351</v>
       </c>
       <c r="S169" t="n">
         <v>1</v>
@@ -22001,12 +22001,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
@@ -22042,10 +22042,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>130049854</v>
+        <v>130048236</v>
       </c>
       <c r="B170" t="n">
-        <v>58688</v>
+        <v>58660</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -22053,21 +22053,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -22080,9 +22080,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -22091,10 +22096,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>675414</v>
+        <v>675394</v>
       </c>
       <c r="R170" t="n">
-        <v>6700288</v>
+        <v>6700289</v>
       </c>
       <c r="S170" t="n">
         <v>1</v>
@@ -22121,12 +22126,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC170" t="inlineStr">
@@ -22162,10 +22167,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>130049843</v>
+        <v>130048185</v>
       </c>
       <c r="B171" t="n">
-        <v>58688</v>
+        <v>58660</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -22173,21 +22178,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -22200,9 +22205,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -22211,10 +22221,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>675369</v>
+        <v>675357</v>
       </c>
       <c r="R171" t="n">
-        <v>6700355</v>
+        <v>6700392</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -22241,12 +22251,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC171" t="inlineStr">
@@ -22282,7 +22292,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>130049863</v>
+        <v>130049867</v>
       </c>
       <c r="B172" t="n">
         <v>58688</v>
@@ -22322,7 +22332,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -22331,10 +22341,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>675382</v>
+        <v>675414</v>
       </c>
       <c r="R172" t="n">
-        <v>6700441</v>
+        <v>6700424</v>
       </c>
       <c r="S172" t="n">
         <v>1</v>
@@ -22361,12 +22371,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
@@ -22402,10 +22412,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>130049808</v>
+        <v>130049871</v>
       </c>
       <c r="B173" t="n">
-        <v>58686</v>
+        <v>58688</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -22413,21 +22423,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -22442,7 +22452,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -22451,10 +22461,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>675373</v>
+        <v>675381</v>
       </c>
       <c r="R173" t="n">
-        <v>6700355</v>
+        <v>6700306</v>
       </c>
       <c r="S173" t="n">
         <v>1</v>
@@ -22481,12 +22491,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
@@ -22522,10 +22532,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>130049819</v>
+        <v>130048255</v>
       </c>
       <c r="B174" t="n">
-        <v>58688</v>
+        <v>58660</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -22533,21 +22543,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -22567,7 +22577,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -22581,10 +22591,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>675394</v>
+        <v>675381</v>
       </c>
       <c r="R174" t="n">
-        <v>6700378</v>
+        <v>6700440</v>
       </c>
       <c r="S174" t="n">
         <v>1</v>
@@ -22611,12 +22621,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
@@ -22652,7 +22662,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>130049828</v>
+        <v>130049854</v>
       </c>
       <c r="B175" t="n">
         <v>58688</v>
@@ -22701,10 +22711,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>675364</v>
+        <v>675414</v>
       </c>
       <c r="R175" t="n">
-        <v>6700414</v>
+        <v>6700288</v>
       </c>
       <c r="S175" t="n">
         <v>1</v>
@@ -22731,12 +22741,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
@@ -22772,10 +22782,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>130050491</v>
+        <v>130049843</v>
       </c>
       <c r="B176" t="n">
-        <v>58699</v>
+        <v>58688</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -22783,21 +22793,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100141</v>
+        <v>208249</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -22810,11 +22820,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N176" t="inlineStr">
         <is>
           <t>fälla</t>
@@ -22826,10 +22831,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>675431</v>
+        <v>675369</v>
       </c>
       <c r="R176" t="n">
-        <v>6700401</v>
+        <v>6700355</v>
       </c>
       <c r="S176" t="n">
         <v>1</v>
@@ -22856,12 +22861,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
@@ -22897,10 +22902,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130050578</v>
+        <v>130049863</v>
       </c>
       <c r="B177" t="n">
-        <v>58699</v>
+        <v>58688</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -22908,21 +22913,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100141</v>
+        <v>208249</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -22935,19 +22940,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -22956,10 +22951,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>675403</v>
+        <v>675382</v>
       </c>
       <c r="R177" t="n">
-        <v>6700428</v>
+        <v>6700441</v>
       </c>
       <c r="S177" t="n">
         <v>1</v>
@@ -22986,12 +22981,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr">
@@ -23027,10 +23022,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130050259</v>
+        <v>130049808</v>
       </c>
       <c r="B178" t="n">
-        <v>58699</v>
+        <v>58686</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -23038,21 +23033,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100141</v>
+        <v>208250</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -23065,19 +23060,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -23086,10 +23071,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>675413</v>
+        <v>675373</v>
       </c>
       <c r="R178" t="n">
-        <v>6700338</v>
+        <v>6700355</v>
       </c>
       <c r="S178" t="n">
         <v>1</v>
@@ -23116,12 +23101,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
@@ -23157,10 +23142,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>130050468</v>
+        <v>130049819</v>
       </c>
       <c r="B179" t="n">
-        <v>58699</v>
+        <v>58688</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -23168,21 +23153,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100141</v>
+        <v>208249</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -23197,7 +23182,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -23211,10 +23201,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>675395</v>
+        <v>675394</v>
       </c>
       <c r="R179" t="n">
-        <v>6700432</v>
+        <v>6700378</v>
       </c>
       <c r="S179" t="n">
         <v>1</v>
@@ -23241,12 +23231,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
@@ -23282,10 +23272,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>130050542</v>
+        <v>130049828</v>
       </c>
       <c r="B180" t="n">
-        <v>58699</v>
+        <v>58688</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -23293,21 +23283,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100141</v>
+        <v>208249</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -23320,14 +23310,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -23336,10 +23321,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>675370</v>
+        <v>675364</v>
       </c>
       <c r="R180" t="n">
-        <v>6700367</v>
+        <v>6700414</v>
       </c>
       <c r="S180" t="n">
         <v>1</v>
@@ -23366,12 +23351,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
@@ -23407,32 +23392,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>130046353</v>
+        <v>130047393</v>
       </c>
       <c r="B181" t="n">
-        <v>58683</v>
+        <v>58699</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100119</v>
+        <v>100141</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -23447,7 +23432,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -23461,10 +23451,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>675372</v>
+        <v>675430</v>
       </c>
       <c r="R181" t="n">
-        <v>6700346</v>
+        <v>6700409</v>
       </c>
       <c r="S181" t="n">
         <v>1</v>
@@ -23491,17 +23481,17 @@
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>length:30mm|bodymass:2.6g (same size 3)</t>
+          <t>length:70mm|bodymass:5g (same size 2)</t>
         </is>
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
@@ -23537,32 +23527,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>130046337</v>
+        <v>130047387</v>
       </c>
       <c r="B182" t="n">
-        <v>58683</v>
+        <v>58699</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100119</v>
+        <v>100141</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -23577,7 +23567,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -23591,10 +23586,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>675435</v>
+        <v>675414</v>
       </c>
       <c r="R182" t="n">
-        <v>6700368</v>
+        <v>6700288</v>
       </c>
       <c r="S182" t="n">
         <v>1</v>
@@ -23621,17 +23616,17 @@
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>length:33mm|bodymass:3.2g</t>
+          <t>length:76mm|bodymass:6g</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
@@ -23667,10 +23662,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>130047148</v>
+        <v>130049447</v>
       </c>
       <c r="B183" t="n">
-        <v>58699</v>
+        <v>58696</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -23678,21 +23673,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -23712,12 +23707,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -23726,10 +23721,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>675430</v>
+        <v>675366</v>
       </c>
       <c r="R183" t="n">
-        <v>6700324</v>
+        <v>6700382</v>
       </c>
       <c r="S183" t="n">
         <v>1</v>
@@ -23754,19 +23749,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>length:68mm|bodymass:6g (same size 6)</t>
-        </is>
-      </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AC183" t="inlineStr">
@@ -23802,32 +23792,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130049432</v>
+        <v>130046353</v>
       </c>
       <c r="B184" t="n">
-        <v>58696</v>
+        <v>58683</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>208242</v>
+        <v>100119</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -23842,17 +23832,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -23861,10 +23846,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>675371</v>
+        <v>675372</v>
       </c>
       <c r="R184" t="n">
-        <v>6700345</v>
+        <v>6700346</v>
       </c>
       <c r="S184" t="n">
         <v>1</v>
@@ -23889,14 +23874,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>length:30mm|bodymass:2.6g (same size 3)</t>
+        </is>
+      </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC184" t="inlineStr">
@@ -23932,32 +23922,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130050779</v>
+        <v>130046337</v>
       </c>
       <c r="B185" t="n">
-        <v>56750</v>
+        <v>58683</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>208257</v>
+        <v>100119</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -23970,21 +23960,26 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>675375</v>
+        <v>675435</v>
       </c>
       <c r="R185" t="n">
-        <v>6700315</v>
+        <v>6700368</v>
       </c>
       <c r="S185" t="n">
         <v>1</v>
@@ -24009,14 +24004,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>length:33mm|bodymass:3.2g</t>
+        </is>
+      </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
@@ -36022,32 +36022,32 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>130047270</v>
+        <v>130046335</v>
       </c>
       <c r="B280" t="n">
-        <v>58699</v>
+        <v>58683</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -36062,17 +36062,12 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P280" t="inlineStr">
@@ -36081,10 +36076,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>675398</v>
+        <v>675413</v>
       </c>
       <c r="R280" t="n">
-        <v>6700432</v>
+        <v>6700288</v>
       </c>
       <c r="S280" t="n">
         <v>1</v>
@@ -36111,17 +36106,17 @@
       </c>
       <c r="X280" t="inlineStr">
         <is>
-          <t>length:67mm|bodymass:6g (same size 4)</t>
+          <t>length:40mm|bodymass:6.4g</t>
         </is>
       </c>
       <c r="Y280" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -36157,32 +36152,32 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>130048278</v>
+        <v>130050792</v>
       </c>
       <c r="B281" t="n">
-        <v>58660</v>
+        <v>58683</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>208245</v>
+        <v>100119</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -36197,12 +36192,7 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -36216,10 +36206,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>675374</v>
+        <v>675420</v>
       </c>
       <c r="R281" t="n">
-        <v>6700338</v>
+        <v>6700424</v>
       </c>
       <c r="S281" t="n">
         <v>1</v>
@@ -36246,12 +36236,12 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -36287,7 +36277,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>130048288</v>
+        <v>130048278</v>
       </c>
       <c r="B282" t="n">
         <v>58660</v>
@@ -36332,7 +36322,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -36346,10 +36336,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>675395</v>
+        <v>675374</v>
       </c>
       <c r="R282" t="n">
-        <v>6700432</v>
+        <v>6700338</v>
       </c>
       <c r="S282" t="n">
         <v>1</v>
@@ -36376,12 +36366,12 @@
       </c>
       <c r="Y282" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -36417,32 +36407,32 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>130050792</v>
+        <v>130048288</v>
       </c>
       <c r="B283" t="n">
-        <v>58683</v>
+        <v>58660</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100119</v>
+        <v>208245</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -36457,7 +36447,12 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -36471,10 +36466,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>675420</v>
+        <v>675395</v>
       </c>
       <c r="R283" t="n">
-        <v>6700424</v>
+        <v>6700432</v>
       </c>
       <c r="S283" t="n">
         <v>1</v>
@@ -36501,12 +36496,12 @@
       </c>
       <c r="Y283" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -36542,32 +36537,32 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>130046335</v>
+        <v>130048231</v>
       </c>
       <c r="B284" t="n">
-        <v>58683</v>
+        <v>58660</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100119</v>
+        <v>208245</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -36596,10 +36591,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>675413</v>
+        <v>675404</v>
       </c>
       <c r="R284" t="n">
-        <v>6700288</v>
+        <v>6700427</v>
       </c>
       <c r="S284" t="n">
         <v>1</v>
@@ -36624,19 +36619,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X284" t="inlineStr">
-        <is>
-          <t>length:40mm|bodymass:6.4g</t>
-        </is>
-      </c>
       <c r="Y284" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -36672,7 +36662,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>130048231</v>
+        <v>130048316</v>
       </c>
       <c r="B285" t="n">
         <v>58660</v>
@@ -36710,14 +36700,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P285" t="inlineStr">
@@ -36726,10 +36711,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>675404</v>
+        <v>675364</v>
       </c>
       <c r="R285" t="n">
-        <v>6700427</v>
+        <v>6700419</v>
       </c>
       <c r="S285" t="n">
         <v>1</v>
@@ -36756,12 +36741,12 @@
       </c>
       <c r="Y285" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -36797,10 +36782,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>130048316</v>
+        <v>130047270</v>
       </c>
       <c r="B286" t="n">
-        <v>58660</v>
+        <v>58699</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -36808,21 +36793,21 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -36835,6 +36820,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N286" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -36846,10 +36841,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>675364</v>
+        <v>675398</v>
       </c>
       <c r="R286" t="n">
-        <v>6700419</v>
+        <v>6700432</v>
       </c>
       <c r="S286" t="n">
         <v>1</v>
@@ -36874,14 +36869,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>length:67mm|bodymass:6g (same size 4)</t>
+        </is>
+      </c>
       <c r="Y286" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -38557,32 +38557,32 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>130046493</v>
+        <v>130050692</v>
       </c>
       <c r="B300" t="n">
-        <v>58683</v>
+        <v>56758</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>100119</v>
+        <v>208255</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -38595,26 +38595,21 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB 19a), Upl</t>
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>675387</v>
+        <v>675389</v>
       </c>
       <c r="R300" t="n">
-        <v>6700440</v>
+        <v>6700356</v>
       </c>
       <c r="S300" t="n">
         <v>1</v>
@@ -38639,19 +38634,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X300" t="inlineStr">
-        <is>
-          <t>length:33mm|bodymass:3g (same size 1)</t>
-        </is>
-      </c>
       <c r="Y300" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -38687,32 +38677,32 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>130046405</v>
+        <v>130050715</v>
       </c>
       <c r="B301" t="n">
-        <v>58683</v>
+        <v>56769</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>100119</v>
+        <v>100088</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -38725,26 +38715,21 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>675363</v>
+        <v>675437</v>
       </c>
       <c r="R301" t="n">
-        <v>6700386</v>
+        <v>6700358</v>
       </c>
       <c r="S301" t="n">
         <v>1</v>
@@ -38769,19 +38754,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X301" t="inlineStr">
-        <is>
-          <t>length:33mm|bodymass:3.8g</t>
-        </is>
-      </c>
       <c r="Y301" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -38817,32 +38797,32 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>130050715</v>
+        <v>130046493</v>
       </c>
       <c r="B302" t="n">
-        <v>56769</v>
+        <v>58683</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>100088</v>
+        <v>100119</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -38855,6 +38835,11 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N302" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -38862,14 +38847,14 @@
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>675437</v>
+        <v>675387</v>
       </c>
       <c r="R302" t="n">
-        <v>6700358</v>
+        <v>6700440</v>
       </c>
       <c r="S302" t="n">
         <v>1</v>
@@ -38894,14 +38879,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>length:33mm|bodymass:3g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y302" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -38937,7 +38927,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>130046383</v>
+        <v>130046405</v>
       </c>
       <c r="B303" t="n">
         <v>58683</v>
@@ -38982,7 +38972,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P303" t="inlineStr">
@@ -38991,10 +38981,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>675403</v>
+        <v>675363</v>
       </c>
       <c r="R303" t="n">
-        <v>6700428</v>
+        <v>6700386</v>
       </c>
       <c r="S303" t="n">
         <v>1</v>
@@ -39021,17 +39011,17 @@
       </c>
       <c r="X303" t="inlineStr">
         <is>
-          <t>length:29mm|bodymass:2.5g (same size 1)</t>
+          <t>length:33mm|bodymass:3.8g</t>
         </is>
       </c>
       <c r="Y303" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -39067,32 +39057,32 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>130046384</v>
+        <v>130049517</v>
       </c>
       <c r="B304" t="n">
-        <v>58683</v>
+        <v>58696</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -39107,7 +39097,12 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -39121,10 +39116,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>675415</v>
+        <v>675420</v>
       </c>
       <c r="R304" t="n">
-        <v>6700424</v>
+        <v>6700420</v>
       </c>
       <c r="S304" t="n">
         <v>1</v>
@@ -39149,19 +39144,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X304" t="inlineStr">
-        <is>
-          <t>length:32mm|bodymass:4.3g</t>
-        </is>
-      </c>
       <c r="Y304" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AC304" t="inlineStr">
@@ -39197,32 +39187,32 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>130046410</v>
+        <v>130049513</v>
       </c>
       <c r="B305" t="n">
-        <v>58683</v>
+        <v>58696</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -39237,7 +39227,12 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -39254,7 +39249,7 @@
         <v>675403</v>
       </c>
       <c r="R305" t="n">
-        <v>6700425</v>
+        <v>6700428</v>
       </c>
       <c r="S305" t="n">
         <v>1</v>
@@ -39279,19 +39274,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X305" t="inlineStr">
-        <is>
-          <t>length:26mm|bodymass:2.1g</t>
-        </is>
-      </c>
       <c r="Y305" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -39327,32 +39317,32 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>130046412</v>
+        <v>130049465</v>
       </c>
       <c r="B306" t="n">
-        <v>58683</v>
+        <v>58696</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -39367,12 +39357,17 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P306" t="inlineStr">
@@ -39381,10 +39376,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>675369</v>
+        <v>675375</v>
       </c>
       <c r="R306" t="n">
-        <v>6700355</v>
+        <v>6700340</v>
       </c>
       <c r="S306" t="n">
         <v>1</v>
@@ -39409,19 +39404,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X306" t="inlineStr">
-        <is>
-          <t>length:32mm|bodymass:3.3g</t>
-        </is>
-      </c>
       <c r="Y306" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -39457,10 +39447,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>130047380</v>
+        <v>130049431</v>
       </c>
       <c r="B307" t="n">
-        <v>58699</v>
+        <v>58696</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -39468,21 +39458,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -39516,10 +39506,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>675424</v>
+        <v>675368</v>
       </c>
       <c r="R307" t="n">
-        <v>6700426</v>
+        <v>6700430</v>
       </c>
       <c r="S307" t="n">
         <v>1</v>
@@ -39544,19 +39534,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X307" t="inlineStr">
-        <is>
-          <t>length:69mm|bodymass:6g (same size 2)</t>
-        </is>
-      </c>
       <c r="Y307" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -39592,32 +39577,32 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>130046343</v>
+        <v>130048093</v>
       </c>
       <c r="B308" t="n">
-        <v>58683</v>
+        <v>58660</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>100119</v>
+        <v>208245</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -39632,12 +39617,12 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P308" t="inlineStr">
@@ -39646,10 +39631,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>675364</v>
+        <v>675426</v>
       </c>
       <c r="R308" t="n">
-        <v>6700416</v>
+        <v>6700422</v>
       </c>
       <c r="S308" t="n">
         <v>1</v>
@@ -39674,19 +39659,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X308" t="inlineStr">
-        <is>
-          <t>length:35mm|bodymass:4.8g</t>
-        </is>
-      </c>
       <c r="Y308" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -39722,32 +39702,32 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>130046473</v>
+        <v>130049797</v>
       </c>
       <c r="B309" t="n">
-        <v>58683</v>
+        <v>58686</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>100119</v>
+        <v>208250</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -39760,14 +39740,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
@@ -39776,10 +39751,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>675381</v>
+        <v>675372</v>
       </c>
       <c r="R309" t="n">
-        <v>6700307</v>
+        <v>6700347</v>
       </c>
       <c r="S309" t="n">
         <v>1</v>
@@ -39804,19 +39779,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X309" t="inlineStr">
-        <is>
-          <t>length:36mm|bodymass:4g (same size 2)</t>
-        </is>
-      </c>
       <c r="Y309" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -39852,10 +39822,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>130049465</v>
+        <v>130049842</v>
       </c>
       <c r="B310" t="n">
-        <v>58696</v>
+        <v>58688</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -39863,21 +39833,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -39902,7 +39872,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
@@ -39911,10 +39881,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>675375</v>
+        <v>675373</v>
       </c>
       <c r="R310" t="n">
-        <v>6700340</v>
+        <v>6700355</v>
       </c>
       <c r="S310" t="n">
         <v>1</v>
@@ -39941,12 +39911,12 @@
       </c>
       <c r="Y310" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -39982,32 +39952,32 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>130049431</v>
+        <v>130046383</v>
       </c>
       <c r="B311" t="n">
-        <v>58696</v>
+        <v>58683</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>208242</v>
+        <v>100119</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -40022,12 +39992,7 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -40041,10 +40006,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>675368</v>
+        <v>675403</v>
       </c>
       <c r="R311" t="n">
-        <v>6700430</v>
+        <v>6700428</v>
       </c>
       <c r="S311" t="n">
         <v>1</v>
@@ -40069,14 +40034,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>length:29mm|bodymass:2.5g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y311" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -40112,32 +40082,32 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>130048093</v>
+        <v>130046384</v>
       </c>
       <c r="B312" t="n">
-        <v>58660</v>
+        <v>58683</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>208245</v>
+        <v>100119</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -40152,12 +40122,12 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P312" t="inlineStr">
@@ -40166,10 +40136,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>675426</v>
+        <v>675415</v>
       </c>
       <c r="R312" t="n">
-        <v>6700422</v>
+        <v>6700424</v>
       </c>
       <c r="S312" t="n">
         <v>1</v>
@@ -40194,14 +40164,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>length:32mm|bodymass:4.3g</t>
+        </is>
+      </c>
       <c r="Y312" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -40237,32 +40212,32 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>130048216</v>
+        <v>130046410</v>
       </c>
       <c r="B313" t="n">
-        <v>58660</v>
+        <v>58683</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>208245</v>
+        <v>100119</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -40277,12 +40252,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L313" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -40296,10 +40266,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>675371</v>
+        <v>675403</v>
       </c>
       <c r="R313" t="n">
-        <v>6700345</v>
+        <v>6700425</v>
       </c>
       <c r="S313" t="n">
         <v>1</v>
@@ -40324,14 +40294,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>length:26mm|bodymass:2.1g</t>
+        </is>
+      </c>
       <c r="Y313" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -40367,32 +40342,32 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>130049797</v>
+        <v>130046412</v>
       </c>
       <c r="B314" t="n">
-        <v>58686</v>
+        <v>58683</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>208250</v>
+        <v>100119</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -40405,9 +40380,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P314" t="inlineStr">
@@ -40416,10 +40396,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>675372</v>
+        <v>675369</v>
       </c>
       <c r="R314" t="n">
-        <v>6700347</v>
+        <v>6700355</v>
       </c>
       <c r="S314" t="n">
         <v>1</v>
@@ -40444,14 +40424,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>length:32mm|bodymass:3.3g</t>
+        </is>
+      </c>
       <c r="Y314" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -40487,10 +40472,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>130049842</v>
+        <v>130047380</v>
       </c>
       <c r="B315" t="n">
-        <v>58688</v>
+        <v>58699</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -40498,21 +40483,21 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>208249</v>
+        <v>100141</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -40546,10 +40531,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>675373</v>
+        <v>675424</v>
       </c>
       <c r="R315" t="n">
-        <v>6700355</v>
+        <v>6700426</v>
       </c>
       <c r="S315" t="n">
         <v>1</v>
@@ -40574,14 +40559,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>length:69mm|bodymass:6g (same size 2)</t>
+        </is>
+      </c>
       <c r="Y315" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -40617,32 +40607,32 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>130049517</v>
+        <v>130046343</v>
       </c>
       <c r="B316" t="n">
-        <v>58696</v>
+        <v>58683</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>208242</v>
+        <v>100119</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -40657,12 +40647,7 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L316" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -40676,10 +40661,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>675420</v>
+        <v>675364</v>
       </c>
       <c r="R316" t="n">
-        <v>6700420</v>
+        <v>6700416</v>
       </c>
       <c r="S316" t="n">
         <v>1</v>
@@ -40704,14 +40689,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>length:35mm|bodymass:4.8g</t>
+        </is>
+      </c>
       <c r="Y316" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -40747,32 +40737,32 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>130049513</v>
+        <v>130046473</v>
       </c>
       <c r="B317" t="n">
-        <v>58696</v>
+        <v>58683</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>208242</v>
+        <v>100119</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -40787,17 +40777,12 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L317" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P317" t="inlineStr">
@@ -40806,10 +40791,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>675403</v>
+        <v>675381</v>
       </c>
       <c r="R317" t="n">
-        <v>6700428</v>
+        <v>6700307</v>
       </c>
       <c r="S317" t="n">
         <v>1</v>
@@ -40834,14 +40819,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>length:36mm|bodymass:4g (same size 2)</t>
+        </is>
+      </c>
       <c r="Y317" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -40877,10 +40867,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>130050692</v>
+        <v>130048216</v>
       </c>
       <c r="B318" t="n">
-        <v>56758</v>
+        <v>58660</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -40888,21 +40878,21 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>208255</v>
+        <v>208245</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -40915,6 +40905,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N318" t="inlineStr">
         <is>
           <t>fälla</t>
@@ -40922,14 +40922,14 @@
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>(SKB 19a), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>675389</v>
+        <v>675371</v>
       </c>
       <c r="R318" t="n">
-        <v>6700356</v>
+        <v>6700345</v>
       </c>
       <c r="S318" t="n">
         <v>1</v>
@@ -40956,12 +40956,12 @@
       </c>
       <c r="Y318" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -43142,10 +43142,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>130048240</v>
+        <v>130049412</v>
       </c>
       <c r="B336" t="n">
-        <v>58660</v>
+        <v>58696</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -43153,16 +43153,16 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -43182,7 +43182,12 @@
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -43196,10 +43201,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>675370</v>
+        <v>675369</v>
       </c>
       <c r="R336" t="n">
-        <v>6700367</v>
+        <v>6700355</v>
       </c>
       <c r="S336" t="n">
         <v>1</v>
@@ -43226,12 +43231,12 @@
       </c>
       <c r="Y336" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -43267,32 +43272,32 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>130046536</v>
+        <v>130049414</v>
       </c>
       <c r="B337" t="n">
-        <v>58683</v>
+        <v>58696</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -43326,10 +43331,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>675432</v>
+        <v>675370</v>
       </c>
       <c r="R337" t="n">
-        <v>6700388</v>
+        <v>6700351</v>
       </c>
       <c r="S337" t="n">
         <v>1</v>
@@ -43354,19 +43359,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X337" t="inlineStr">
-        <is>
-          <t>chip:24481|capture:4|length:55mm|bodymass:17g</t>
-        </is>
-      </c>
       <c r="Y337" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -43402,10 +43402,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>130049412</v>
+        <v>130050706</v>
       </c>
       <c r="B338" t="n">
-        <v>58696</v>
+        <v>56769</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -43413,16 +43413,16 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>208242</v>
+        <v>100088</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -43440,19 +43440,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P338" t="inlineStr">
@@ -43461,10 +43451,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>675369</v>
+        <v>675393</v>
       </c>
       <c r="R338" t="n">
-        <v>6700355</v>
+        <v>6700366</v>
       </c>
       <c r="S338" t="n">
         <v>1</v>
@@ -43491,12 +43481,12 @@
       </c>
       <c r="Y338" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -43532,10 +43522,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>130049414</v>
+        <v>130050550</v>
       </c>
       <c r="B339" t="n">
-        <v>58696</v>
+        <v>58699</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -43543,21 +43533,21 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -43591,10 +43581,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>675370</v>
+        <v>675439</v>
       </c>
       <c r="R339" t="n">
-        <v>6700351</v>
+        <v>6700347</v>
       </c>
       <c r="S339" t="n">
         <v>1</v>
@@ -43621,12 +43611,12 @@
       </c>
       <c r="Y339" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -43662,32 +43652,32 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>130050706</v>
+        <v>130046536</v>
       </c>
       <c r="B340" t="n">
-        <v>56769</v>
+        <v>58683</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>100088</v>
+        <v>100119</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -43700,9 +43690,19 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P340" t="inlineStr">
@@ -43711,10 +43711,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>675393</v>
+        <v>675432</v>
       </c>
       <c r="R340" t="n">
-        <v>6700366</v>
+        <v>6700388</v>
       </c>
       <c r="S340" t="n">
         <v>1</v>
@@ -43739,14 +43739,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>chip:24481|capture:4|length:55mm|bodymass:17g</t>
+        </is>
+      </c>
       <c r="Y340" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -43782,10 +43787,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>130050550</v>
+        <v>130048240</v>
       </c>
       <c r="B341" t="n">
-        <v>58699</v>
+        <v>58660</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -43793,21 +43798,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -43822,12 +43827,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -43841,10 +43841,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>675439</v>
+        <v>675370</v>
       </c>
       <c r="R341" t="n">
-        <v>6700347</v>
+        <v>6700367</v>
       </c>
       <c r="S341" t="n">
         <v>1</v>
@@ -44532,32 +44532,32 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>130046490</v>
+        <v>130050721</v>
       </c>
       <c r="B347" t="n">
-        <v>58683</v>
+        <v>56769</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>100119</v>
+        <v>100088</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -44570,11 +44570,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N347" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -44582,14 +44577,14 @@
       </c>
       <c r="P347" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>675382</v>
+        <v>675365</v>
       </c>
       <c r="R347" t="n">
-        <v>6700441</v>
+        <v>6700425</v>
       </c>
       <c r="S347" t="n">
         <v>1</v>
@@ -44614,19 +44609,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X347" t="inlineStr">
-        <is>
-          <t>length:30mm|bodymass:2g (same size 1)</t>
-        </is>
-      </c>
       <c r="Y347" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -44662,10 +44652,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>130050721</v>
+        <v>130048229</v>
       </c>
       <c r="B348" t="n">
-        <v>56769</v>
+        <v>58660</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -44673,16 +44663,16 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>100088</v>
+        <v>208245</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -44700,21 +44690,26 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P348" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>675365</v>
+        <v>675364</v>
       </c>
       <c r="R348" t="n">
-        <v>6700425</v>
+        <v>6700416</v>
       </c>
       <c r="S348" t="n">
         <v>1</v>
@@ -44741,12 +44736,12 @@
       </c>
       <c r="Y348" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -44782,32 +44777,32 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>130046953</v>
+        <v>130046490</v>
       </c>
       <c r="B349" t="n">
-        <v>58699</v>
+        <v>58683</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -44822,12 +44817,7 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -44841,10 +44831,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>675432</v>
+        <v>675382</v>
       </c>
       <c r="R349" t="n">
-        <v>6700394</v>
+        <v>6700441</v>
       </c>
       <c r="S349" t="n">
         <v>1</v>
@@ -44871,17 +44861,17 @@
       </c>
       <c r="X349" t="inlineStr">
         <is>
-          <t>length:74mm|bodymass:10g (same size 3)</t>
+          <t>length:30mm|bodymass:2g (same size 1)</t>
         </is>
       </c>
       <c r="Y349" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -44917,10 +44907,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>130048229</v>
+        <v>130046953</v>
       </c>
       <c r="B350" t="n">
-        <v>58660</v>
+        <v>58699</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -44928,21 +44918,21 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -44957,12 +44947,17 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P350" t="inlineStr">
@@ -44971,10 +44966,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>675364</v>
+        <v>675432</v>
       </c>
       <c r="R350" t="n">
-        <v>6700416</v>
+        <v>6700394</v>
       </c>
       <c r="S350" t="n">
         <v>1</v>
@@ -44999,14 +44994,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>length:74mm|bodymass:10g (same size 3)</t>
+        </is>
+      </c>
       <c r="Y350" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -45042,10 +45042,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>130048138</v>
+        <v>130049466</v>
       </c>
       <c r="B351" t="n">
-        <v>58660</v>
+        <v>58696</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -45053,16 +45053,16 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -45080,9 +45080,19 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
@@ -45091,10 +45101,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>675428</v>
+        <v>675383</v>
       </c>
       <c r="R351" t="n">
-        <v>6700413</v>
+        <v>6700304</v>
       </c>
       <c r="S351" t="n">
         <v>1</v>
@@ -45121,12 +45131,12 @@
       </c>
       <c r="Y351" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -45162,10 +45172,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>130049831</v>
+        <v>130049460</v>
       </c>
       <c r="B352" t="n">
-        <v>58688</v>
+        <v>58696</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -45173,21 +45183,21 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -45200,9 +45210,19 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P352" t="inlineStr">
@@ -45211,10 +45231,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>675415</v>
+        <v>675441</v>
       </c>
       <c r="R352" t="n">
-        <v>6700424</v>
+        <v>6700338</v>
       </c>
       <c r="S352" t="n">
         <v>1</v>
@@ -45241,12 +45261,12 @@
       </c>
       <c r="Y352" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -45282,10 +45302,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>130049801</v>
+        <v>130048237</v>
       </c>
       <c r="B353" t="n">
-        <v>58686</v>
+        <v>58660</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -45293,21 +45313,21 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>208250</v>
+        <v>208245</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -45320,6 +45340,11 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N353" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -45331,10 +45356,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>675375</v>
+        <v>675388</v>
       </c>
       <c r="R353" t="n">
-        <v>6700315</v>
+        <v>6700295</v>
       </c>
       <c r="S353" t="n">
         <v>1</v>
@@ -45361,12 +45386,12 @@
       </c>
       <c r="Y353" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -45402,10 +45427,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>130049466</v>
+        <v>130048138</v>
       </c>
       <c r="B354" t="n">
-        <v>58696</v>
+        <v>58660</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -45413,16 +45438,16 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -45440,19 +45465,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P354" t="inlineStr">
@@ -45461,10 +45476,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>675383</v>
+        <v>675428</v>
       </c>
       <c r="R354" t="n">
-        <v>6700304</v>
+        <v>6700413</v>
       </c>
       <c r="S354" t="n">
         <v>1</v>
@@ -45491,12 +45506,12 @@
       </c>
       <c r="Y354" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -45532,10 +45547,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>130049460</v>
+        <v>130049831</v>
       </c>
       <c r="B355" t="n">
-        <v>58696</v>
+        <v>58688</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -45543,21 +45558,21 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -45570,19 +45585,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P355" t="inlineStr">
@@ -45591,10 +45596,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>675441</v>
+        <v>675415</v>
       </c>
       <c r="R355" t="n">
-        <v>6700338</v>
+        <v>6700424</v>
       </c>
       <c r="S355" t="n">
         <v>1</v>
@@ -45621,12 +45626,12 @@
       </c>
       <c r="Y355" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -45662,10 +45667,10 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>130048237</v>
+        <v>130049801</v>
       </c>
       <c r="B356" t="n">
-        <v>58660</v>
+        <v>58686</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -45673,21 +45678,21 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>208245</v>
+        <v>208250</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -45700,11 +45705,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N356" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -45716,10 +45716,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>675388</v>
+        <v>675375</v>
       </c>
       <c r="R356" t="n">
-        <v>6700295</v>
+        <v>6700315</v>
       </c>
       <c r="S356" t="n">
         <v>1</v>
@@ -45746,12 +45746,12 @@
       </c>
       <c r="Y356" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -45787,10 +45787,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>130048062</v>
+        <v>130047348</v>
       </c>
       <c r="B357" t="n">
-        <v>58660</v>
+        <v>58699</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -45798,21 +45798,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -45827,7 +45827,12 @@
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -45841,10 +45846,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>675394</v>
+        <v>675422</v>
       </c>
       <c r="R357" t="n">
-        <v>6700378</v>
+        <v>6700428</v>
       </c>
       <c r="S357" t="n">
         <v>1</v>
@@ -45869,14 +45874,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>length:71mm|bodymass:6g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y357" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -45912,7 +45922,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>130048259</v>
+        <v>130048062</v>
       </c>
       <c r="B358" t="n">
         <v>58660</v>
@@ -45952,12 +45962,7 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -45971,10 +45976,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>675420</v>
+        <v>675394</v>
       </c>
       <c r="R358" t="n">
-        <v>6700420</v>
+        <v>6700378</v>
       </c>
       <c r="S358" t="n">
         <v>1</v>
@@ -46001,12 +46006,12 @@
       </c>
       <c r="Y358" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -46042,7 +46047,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>130048306</v>
+        <v>130048259</v>
       </c>
       <c r="B359" t="n">
         <v>58660</v>
@@ -46080,6 +46085,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N359" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -46091,10 +46106,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>675387</v>
+        <v>675420</v>
       </c>
       <c r="R359" t="n">
-        <v>6700439</v>
+        <v>6700420</v>
       </c>
       <c r="S359" t="n">
         <v>1</v>
@@ -46121,12 +46136,12 @@
       </c>
       <c r="Y359" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -46162,10 +46177,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>130049798</v>
+        <v>130050714</v>
       </c>
       <c r="B360" t="n">
-        <v>58686</v>
+        <v>56769</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -46173,21 +46188,21 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>208250</v>
+        <v>100088</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -46207,14 +46222,14 @@
       </c>
       <c r="P360" t="inlineStr">
         <is>
-          <t>(SKB 12), Upl</t>
+          <t>(SKB outside), Upl</t>
         </is>
       </c>
       <c r="Q360" t="n">
         <v>675369</v>
       </c>
       <c r="R360" t="n">
-        <v>6700355</v>
+        <v>6700430</v>
       </c>
       <c r="S360" t="n">
         <v>1</v>
@@ -46241,12 +46256,12 @@
       </c>
       <c r="Y360" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -46282,10 +46297,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>130050714</v>
+        <v>130050607</v>
       </c>
       <c r="B361" t="n">
-        <v>56769</v>
+        <v>58699</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -46293,21 +46308,21 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>100088</v>
+        <v>100141</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -46320,6 +46335,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N361" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -46327,14 +46352,14 @@
       </c>
       <c r="P361" t="inlineStr">
         <is>
-          <t>(SKB outside), Upl</t>
+          <t>(SKB 12), Upl</t>
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>675369</v>
+        <v>675389</v>
       </c>
       <c r="R361" t="n">
-        <v>6700430</v>
+        <v>6700438</v>
       </c>
       <c r="S361" t="n">
         <v>1</v>
@@ -46361,12 +46386,12 @@
       </c>
       <c r="Y361" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -46527,10 +46552,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>130047348</v>
+        <v>130048306</v>
       </c>
       <c r="B363" t="n">
-        <v>58699</v>
+        <v>58660</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -46538,21 +46563,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -46565,16 +46590,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L363" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N363" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -46586,10 +46601,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>675422</v>
+        <v>675387</v>
       </c>
       <c r="R363" t="n">
-        <v>6700428</v>
+        <v>6700439</v>
       </c>
       <c r="S363" t="n">
         <v>1</v>
@@ -46614,19 +46629,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X363" t="inlineStr">
-        <is>
-          <t>length:71mm|bodymass:6g (same size 1)</t>
-        </is>
-      </c>
       <c r="Y363" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -46662,10 +46672,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>130050607</v>
+        <v>130049798</v>
       </c>
       <c r="B364" t="n">
-        <v>58699</v>
+        <v>58686</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -46673,21 +46683,21 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>100141</v>
+        <v>208250</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -46700,16 +46710,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L364" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N364" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -46721,10 +46721,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>675389</v>
+        <v>675369</v>
       </c>
       <c r="R364" t="n">
-        <v>6700438</v>
+        <v>6700355</v>
       </c>
       <c r="S364" t="n">
         <v>1</v>
@@ -46751,12 +46751,12 @@
       </c>
       <c r="Y364" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -48842,32 +48842,32 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>130046471</v>
+        <v>130049528</v>
       </c>
       <c r="B381" t="n">
-        <v>58683</v>
+        <v>58696</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>100119</v>
+        <v>208242</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -48882,7 +48882,12 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -48896,10 +48901,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>675435</v>
+        <v>675431</v>
       </c>
       <c r="R381" t="n">
-        <v>6700393</v>
+        <v>6700401</v>
       </c>
       <c r="S381" t="n">
         <v>1</v>
@@ -48924,19 +48929,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X381" t="inlineStr">
-        <is>
-          <t>length:34mm|bodymass:4g (same size 1)</t>
-        </is>
-      </c>
       <c r="Y381" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -48972,10 +48972,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>130049528</v>
+        <v>130048234</v>
       </c>
       <c r="B382" t="n">
-        <v>58696</v>
+        <v>58660</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -48983,16 +48983,16 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -49017,7 +49017,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -49031,10 +49031,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>675431</v>
+        <v>675406</v>
       </c>
       <c r="R382" t="n">
-        <v>6700401</v>
+        <v>6700288</v>
       </c>
       <c r="S382" t="n">
         <v>1</v>
@@ -49061,12 +49061,12 @@
       </c>
       <c r="Y382" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -49102,7 +49102,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>130048234</v>
+        <v>130048307</v>
       </c>
       <c r="B383" t="n">
         <v>58660</v>
@@ -49140,16 +49140,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L383" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N383" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -49161,10 +49151,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>675406</v>
+        <v>675387</v>
       </c>
       <c r="R383" t="n">
-        <v>6700288</v>
+        <v>6700440</v>
       </c>
       <c r="S383" t="n">
         <v>1</v>
@@ -49191,12 +49181,12 @@
       </c>
       <c r="Y383" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -49232,10 +49222,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>130048307</v>
+        <v>130049814</v>
       </c>
       <c r="B384" t="n">
-        <v>58660</v>
+        <v>58688</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -49243,21 +49233,21 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -49270,9 +49260,14 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P384" t="inlineStr">
@@ -49281,10 +49276,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>675387</v>
+        <v>675433</v>
       </c>
       <c r="R384" t="n">
-        <v>6700440</v>
+        <v>6700345</v>
       </c>
       <c r="S384" t="n">
         <v>1</v>
@@ -49311,12 +49306,12 @@
       </c>
       <c r="Y384" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -49352,7 +49347,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>130049814</v>
+        <v>130049829</v>
       </c>
       <c r="B385" t="n">
         <v>58688</v>
@@ -49390,14 +49385,9 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P385" t="inlineStr">
@@ -49406,10 +49396,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>675433</v>
+        <v>675392</v>
       </c>
       <c r="R385" t="n">
-        <v>6700345</v>
+        <v>6700435</v>
       </c>
       <c r="S385" t="n">
         <v>1</v>
@@ -49436,12 +49426,12 @@
       </c>
       <c r="Y385" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -49477,32 +49467,32 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>130049829</v>
+        <v>130046471</v>
       </c>
       <c r="B386" t="n">
-        <v>58688</v>
+        <v>58683</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>208249</v>
+        <v>100119</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -49515,6 +49505,11 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N386" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -49526,10 +49521,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>675392</v>
+        <v>675435</v>
       </c>
       <c r="R386" t="n">
-        <v>6700435</v>
+        <v>6700393</v>
       </c>
       <c r="S386" t="n">
         <v>1</v>
@@ -49554,14 +49549,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>length:34mm|bodymass:4g (same size 1)</t>
+        </is>
+      </c>
       <c r="Y386" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -50857,32 +50857,32 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>130050584</v>
+        <v>130046388</v>
       </c>
       <c r="B397" t="n">
-        <v>58699</v>
+        <v>58683</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>100141</v>
+        <v>100119</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -50897,17 +50897,12 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P397" t="inlineStr">
@@ -50916,10 +50911,10 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>675437</v>
+        <v>675366</v>
       </c>
       <c r="R397" t="n">
-        <v>6700358</v>
+        <v>6700381</v>
       </c>
       <c r="S397" t="n">
         <v>1</v>
@@ -50946,17 +50941,17 @@
       </c>
       <c r="X397" t="inlineStr">
         <is>
-          <t>length:68mm|bodymass:3g</t>
+          <t>length:27mm|bodymass:1.9g (same size 2)</t>
         </is>
       </c>
       <c r="Y397" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA397" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AC397" t="inlineStr">
@@ -50992,7 +50987,7 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>130050575</v>
+        <v>130047403</v>
       </c>
       <c r="B398" t="n">
         <v>58699</v>
@@ -51037,12 +51032,12 @@
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P398" t="inlineStr">
@@ -51051,10 +51046,10 @@
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>675372</v>
+        <v>675437</v>
       </c>
       <c r="R398" t="n">
-        <v>6700438</v>
+        <v>6700358</v>
       </c>
       <c r="S398" t="n">
         <v>1</v>
@@ -51079,14 +51074,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X398" t="inlineStr">
+        <is>
+          <t>length:68mm|bodymass:3g</t>
+        </is>
+      </c>
       <c r="Y398" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AA398" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="AC398" t="inlineStr">
@@ -51122,32 +51122,32 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>130048168</v>
+        <v>130046564</v>
       </c>
       <c r="B399" t="n">
-        <v>58660</v>
+        <v>58683</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>208245</v>
+        <v>100119</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gölgroda</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Pelophylax lessonae</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Camerano, 1882)</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -51160,6 +51160,16 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="N399" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -51171,10 +51181,10 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>675375</v>
+        <v>675401</v>
       </c>
       <c r="R399" t="n">
-        <v>6700439</v>
+        <v>6700291</v>
       </c>
       <c r="S399" t="n">
         <v>1</v>
@@ -51199,14 +51209,19 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X399" t="inlineStr">
+        <is>
+          <t>chip:23811|capture:2|length:50mm|bodymass:14g|Bd:Negative</t>
+        </is>
+      </c>
       <c r="Y399" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AA399" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="AC399" t="inlineStr">
@@ -51242,7 +51257,7 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>130048166</v>
+        <v>130048199</v>
       </c>
       <c r="B400" t="n">
         <v>58660</v>
@@ -51280,6 +51295,11 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="N400" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -51291,10 +51311,10 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>675429</v>
+        <v>675368</v>
       </c>
       <c r="R400" t="n">
-        <v>6700305</v>
+        <v>6700432</v>
       </c>
       <c r="S400" t="n">
         <v>1</v>
@@ -51321,12 +51341,12 @@
       </c>
       <c r="Y400" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA400" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AC400" t="inlineStr">
@@ -51362,10 +51382,10 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>130048199</v>
+        <v>130049855</v>
       </c>
       <c r="B401" t="n">
-        <v>58660</v>
+        <v>58688</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -51373,21 +51393,21 @@
         </is>
       </c>
       <c r="E401" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -51400,11 +51420,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="N401" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -51416,10 +51431,10 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>675368</v>
+        <v>675429</v>
       </c>
       <c r="R401" t="n">
-        <v>6700432</v>
+        <v>6700411</v>
       </c>
       <c r="S401" t="n">
         <v>1</v>
@@ -51446,12 +51461,12 @@
       </c>
       <c r="Y401" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA401" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AC401" t="inlineStr">
@@ -51487,32 +51502,32 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>130046388</v>
+        <v>130049791</v>
       </c>
       <c r="B402" t="n">
-        <v>58683</v>
+        <v>58686</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>100119</v>
+        <v>208250</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -51527,12 +51542,17 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
         <is>
-          <t>fälla</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P402" t="inlineStr">
@@ -51541,10 +51561,10 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>675366</v>
+        <v>675383</v>
       </c>
       <c r="R402" t="n">
-        <v>6700381</v>
+        <v>6700306</v>
       </c>
       <c r="S402" t="n">
         <v>1</v>
@@ -51569,19 +51589,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X402" t="inlineStr">
-        <is>
-          <t>length:27mm|bodymass:1.9g (same size 2)</t>
-        </is>
-      </c>
       <c r="Y402" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA402" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AC402" t="inlineStr">
@@ -51617,32 +51632,32 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>130046564</v>
+        <v>130048168</v>
       </c>
       <c r="B403" t="n">
-        <v>58683</v>
+        <v>58660</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>100119</v>
+        <v>208245</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -51655,16 +51670,6 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L403" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="N403" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -51676,10 +51681,10 @@
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>675401</v>
+        <v>675375</v>
       </c>
       <c r="R403" t="n">
-        <v>6700291</v>
+        <v>6700439</v>
       </c>
       <c r="S403" t="n">
         <v>1</v>
@@ -51704,19 +51709,14 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X403" t="inlineStr">
-        <is>
-          <t>chip:23811|capture:2|length:50mm|bodymass:14g|Bd:Negative</t>
-        </is>
-      </c>
       <c r="Y403" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="AA403" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="AC403" t="inlineStr">
@@ -51752,10 +51752,10 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>130049855</v>
+        <v>130048166</v>
       </c>
       <c r="B404" t="n">
-        <v>58688</v>
+        <v>58660</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -51763,21 +51763,21 @@
         </is>
       </c>
       <c r="E404" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -51804,7 +51804,7 @@
         <v>675429</v>
       </c>
       <c r="R404" t="n">
-        <v>6700411</v>
+        <v>6700305</v>
       </c>
       <c r="S404" t="n">
         <v>1</v>
@@ -51831,12 +51831,12 @@
       </c>
       <c r="Y404" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="AA404" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="AC404" t="inlineStr">
@@ -51872,10 +51872,10 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>130049791</v>
+        <v>130050575</v>
       </c>
       <c r="B405" t="n">
-        <v>58686</v>
+        <v>58699</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -51883,21 +51883,21 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>208250</v>
+        <v>100141</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -51917,12 +51917,12 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fälla</t>
         </is>
       </c>
       <c r="P405" t="inlineStr">
@@ -51931,10 +51931,10 @@
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>675383</v>
+        <v>675372</v>
       </c>
       <c r="R405" t="n">
-        <v>6700306</v>
+        <v>6700438</v>
       </c>
       <c r="S405" t="n">
         <v>1</v>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -1492,12 +1492,7 @@
         <v>69990870</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675337.0926959377</v>
+        <v>675337</v>
       </c>
       <c r="R8" t="n">
-        <v>6700379.361994122</v>
+        <v>6700379</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1562,19 +1557,9 @@
           <t>1993-01-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1993-12-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
         <v>69990870</v>
       </c>
       <c r="B8" t="n">
-        <v>97898</v>
+        <v>97899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
         <v>69990870</v>
       </c>
       <c r="B8" t="n">
-        <v>97899</v>
+        <v>97900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
         <v>69990870</v>
       </c>
       <c r="B8" t="n">
-        <v>97900</v>
+        <v>97903</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
         <v>69990870</v>
       </c>
       <c r="B8" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
         <v>69990870</v>
       </c>
       <c r="B8" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
         <v>69990870</v>
       </c>
       <c r="B8" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -1492,7 +1492,7 @@
         <v>69990870</v>
       </c>
       <c r="B8" t="n">
-        <v>97917</v>
+        <v>97919</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 48241-2024 artfynd.xlsx
+++ b/artfynd/A 48241-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY424"/>
+  <dimension ref="A1:AZ424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99369913</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116387908</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87645788</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77979531</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,6 +1304,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72151914</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1410,6 +1440,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73078905</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1530,6 +1565,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050703</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1650,6 +1690,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050704</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1770,6 +1815,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050705</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1890,6 +1940,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050706</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2010,6 +2065,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050709</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2130,6 +2190,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050710</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2250,6 +2315,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050711</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2370,6 +2440,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050714</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2490,6 +2565,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050715</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2610,6 +2690,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050716</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2730,6 +2815,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050718</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2850,6 +2940,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050719</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2970,6 +3065,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050720</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3090,6 +3190,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050722</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3207,6 +3312,11 @@
           <t>ÅGP gölgroda</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16451</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3325,6 +3435,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16465346</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3446,6 +3561,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54863459</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3562,6 +3682,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64056680</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3709,6 +3834,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80662245</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3829,6 +3959,11 @@
           <t xml:space="preserve">SKB groddjursinventeringar </t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103952126</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3954,6 +4089,11 @@
           <t xml:space="preserve">SKB groddjursinventeringar </t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103952158</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4060,6 +4200,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423555</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4166,6 +4311,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423556</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4272,6 +4422,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423565</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4378,6 +4533,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423567</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4484,6 +4644,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423569</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4604,6 +4769,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423599</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4734,6 +4904,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423712</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4859,6 +5034,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423730</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4989,6 +5169,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046283</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5119,6 +5304,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046284</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5249,6 +5439,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046285</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5379,6 +5574,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046297</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5509,6 +5709,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046302</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5639,6 +5844,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046318</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5769,6 +5979,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046320</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5899,6 +6114,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046321</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6029,6 +6249,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046325</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6159,6 +6384,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046328</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6289,6 +6519,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046329</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6419,6 +6654,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046330</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6549,6 +6789,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046333</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6679,6 +6924,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046334</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6809,6 +7059,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046335</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6939,6 +7194,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046337</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7069,6 +7329,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046338</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7199,6 +7464,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046339</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7329,6 +7599,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046341</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7459,6 +7734,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046342</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7589,6 +7869,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046343</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7719,6 +8004,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046350</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7849,6 +8139,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046351</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7979,6 +8274,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046353</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8109,6 +8409,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046355</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8239,6 +8544,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046357</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8369,6 +8679,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046359</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8499,6 +8814,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046378</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8629,6 +8949,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046379</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8759,6 +9084,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046380</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8889,6 +9219,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046382</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9019,6 +9354,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046385</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9149,6 +9489,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046386</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9279,6 +9624,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046388</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9409,6 +9759,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046389</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9539,6 +9894,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046405</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9669,6 +10029,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046410</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9799,6 +10164,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046411</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9929,6 +10299,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046412</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10059,6 +10434,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046423</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10189,6 +10569,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046424</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10319,6 +10704,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046428</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10449,6 +10839,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046432</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10579,6 +10974,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046433</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10709,6 +11109,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046434</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10839,6 +11244,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046435</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10969,6 +11379,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046447</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11099,6 +11514,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046460</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11229,6 +11649,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046464</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11359,6 +11784,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046465</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11489,6 +11919,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046468</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11619,6 +12054,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046471</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11749,6 +12189,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046476</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11879,6 +12324,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046490</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12009,6 +12459,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046493</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12144,6 +12599,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046536</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12279,6 +12739,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046564</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12414,6 +12879,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046570</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12549,6 +13019,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046661</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12684,6 +13159,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046683</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12819,6 +13299,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046698</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12954,6 +13439,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046704</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -13089,6 +13579,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046715</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -13214,6 +13709,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050792</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -13340,6 +13840,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54863519</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -13466,6 +13971,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54863520</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13581,6 +14091,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85813813</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -13706,6 +14221,11 @@
           <t xml:space="preserve">SKB groddjursinventeringar </t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103952235</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -13826,6 +14346,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423776</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13932,6 +14457,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423781</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -14038,6 +14568,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423796</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -14163,6 +14698,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423851</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -14298,6 +14838,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046942</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -14433,6 +14978,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046948</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -14568,6 +15118,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046949</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -14703,6 +15258,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046951</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -14838,6 +15398,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046952</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -14973,6 +15538,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130046953</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -15108,6 +15678,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047128</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -15243,6 +15818,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047131</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -15378,6 +15958,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047134</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -15513,6 +16098,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047136</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -15648,6 +16238,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047139</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -15783,6 +16378,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047144</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -15918,6 +16518,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047146</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -16053,6 +16658,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047148</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -16188,6 +16798,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047155</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -16323,6 +16938,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047159</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -16458,6 +17078,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047176</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -16593,6 +17218,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047196</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -16728,6 +17358,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047198</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -16863,6 +17498,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047242</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -16998,6 +17638,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047244</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -17133,6 +17778,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047271</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -17268,6 +17918,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047288</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -17403,6 +18058,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047295</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -17538,6 +18198,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047342</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -17673,6 +18338,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047343</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -17808,6 +18478,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047346</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -17943,6 +18618,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047374</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -18078,6 +18758,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047378</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -18213,6 +18898,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047380</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -18348,6 +19038,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047381</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -18483,6 +19178,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047383</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -18618,6 +19318,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047400</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -18753,6 +19458,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047401</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -18888,6 +19598,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047403</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -19023,6 +19738,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047404</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -19158,6 +19878,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047408</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -19293,6 +20018,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130047410</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -19418,6 +20148,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049893</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -19548,6 +20283,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049894</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -19673,6 +20413,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049895</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -19803,6 +20548,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049945</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -19933,6 +20683,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049949</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -20063,6 +20818,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050019</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -20193,6 +20953,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050067</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -20323,6 +21088,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050097</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -20453,6 +21223,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050450</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -20578,6 +21353,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050454</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -20703,6 +21483,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050465</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -20828,6 +21613,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050467</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -20953,6 +21743,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050468</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -21078,6 +21873,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050469</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -21203,6 +22003,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050470</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -21328,6 +22133,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050472</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -21453,6 +22263,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050487</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -21578,6 +22393,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050491</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -21703,6 +22523,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050506</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -21828,6 +22653,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050513</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -21953,6 +22783,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050517</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -22083,6 +22918,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050520</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -22213,6 +23053,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050524</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -22338,6 +23183,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050525</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -22463,6 +23313,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050527</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -22588,6 +23443,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050542</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -22713,6 +23573,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050543</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -22838,6 +23703,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050544</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -22968,6 +23838,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050549</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -23098,6 +23973,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050550</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -23223,6 +24103,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050558</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -23348,6 +24233,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050570</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -23478,6 +24368,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050575</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -23608,6 +24503,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050576</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -23733,6 +24633,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050577</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -23858,6 +24763,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050589</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -23988,6 +24898,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050607</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -24113,6 +25028,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050608</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -24243,6 +25163,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050612</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -24362,6 +25287,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120848351</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -24497,6 +25427,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73078912</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -24612,6 +25547,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99318429</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -24721,6 +25661,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100236402</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -24830,6 +25775,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85813879</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -24945,6 +25895,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99341169</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -25060,6 +26015,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99318423</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -25175,6 +26135,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99341160</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -25290,6 +26255,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99341161</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -25406,6 +26376,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99369916</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -25521,6 +26496,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99370832</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -25636,6 +26616,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99317919</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -25751,6 +26736,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99370824</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -25867,6 +26857,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99369904</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -25982,6 +26977,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99304776</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -26097,6 +27097,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99365968</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -26213,6 +27218,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99370766</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -26328,6 +27338,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99318370</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -26448,6 +27463,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101283900</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -26563,6 +27583,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99365975</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -26679,6 +27704,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99328900</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -26794,6 +27824,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99370826</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -26909,6 +27944,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99317917</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -27024,6 +28064,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99318430</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -27139,6 +28184,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99370758</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -27255,6 +28305,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99370764</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -27370,6 +28425,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99317922</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -27485,6 +28545,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99318394</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -27600,6 +28665,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99341159</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -27715,6 +28785,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99318428</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -27830,6 +28905,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85813925</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -27956,6 +29036,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54863489</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -28068,6 +29153,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80664636</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -28183,6 +29273,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85813817</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -28308,6 +29403,11 @@
           <t xml:space="preserve">SKB groddjursinventeringar </t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103952236</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -28428,6 +29528,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113423928</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -28553,6 +29658,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048645</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -28678,6 +29788,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048646</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -28808,6 +29923,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048655</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -28938,6 +30058,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048657</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -29068,6 +30193,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048664</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -29198,6 +30328,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048669</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -29328,6 +30463,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048676</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -29458,6 +30598,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048680</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -29588,6 +30733,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049259</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -29713,6 +30863,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049410</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -29843,6 +30998,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049411</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -29973,6 +31133,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049412</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -30103,6 +31268,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049414</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -30228,6 +31398,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049415</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -30358,6 +31533,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049416</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -30488,6 +31668,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049417</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -30618,6 +31803,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049430</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -30748,6 +31938,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049431</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -30878,6 +32073,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049432</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -31008,6 +32208,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049433</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -31138,6 +32343,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049441</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -31268,6 +32478,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049447</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -31398,6 +32613,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049457</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -31528,6 +32748,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049460</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -31658,6 +32883,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049463</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -31788,6 +33018,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049464</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -31918,6 +33153,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049465</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -32048,6 +33288,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049466</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -32178,6 +33423,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049470</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -32308,6 +33558,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049475</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -32438,6 +33693,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049476</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -32568,6 +33828,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049481</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -32698,6 +33963,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049485</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -32828,6 +34098,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049493</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -32958,6 +34233,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049494</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -33088,6 +34368,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049503</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -33218,6 +34503,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049504</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -33348,6 +34638,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049506</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -33478,6 +34773,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049512</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -33608,6 +34908,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049513</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -33738,6 +35043,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049514</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -33868,6 +35178,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049517</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -33998,6 +35313,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049521</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -34128,6 +35448,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049522</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -34258,6 +35583,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049526</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -34388,6 +35718,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049528</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -34518,6 +35853,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049530</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -34648,6 +35988,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049532</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -34778,6 +36123,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049604</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -34908,6 +36258,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049607</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -35028,6 +36383,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049610</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -35148,6 +36508,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049614</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -35268,6 +36633,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049616</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -35398,6 +36768,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049618</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -35528,6 +36903,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049623</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -35648,6 +37028,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049702</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -35779,6 +37164,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73078741</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -35894,6 +37284,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85813809</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -36005,6 +37400,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89737403</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -36130,6 +37530,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113424165</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -36255,6 +37660,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048062</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -36385,6 +37795,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048088</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -36515,6 +37930,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048089</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -36645,6 +38065,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048090</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -36770,6 +38195,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048092</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -36895,6 +38325,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048093</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -37020,6 +38455,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048100</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -37145,6 +38585,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048103</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -37275,6 +38720,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048107</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -37400,6 +38850,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048110</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -37525,6 +38980,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048111</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -37645,6 +39105,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048132</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -37770,6 +39235,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048133</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -37890,6 +39360,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048138</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -38010,6 +39485,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048139</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -38135,6 +39615,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048140</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -38255,6 +39740,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048141</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -38375,6 +39865,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048142</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -38495,6 +39990,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048143</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -38620,6 +40120,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048144</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -38745,6 +40250,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048145</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -38870,6 +40380,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048148</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -38995,6 +40510,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048149</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -39120,6 +40640,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048155</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -39245,6 +40770,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048159</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -39365,6 +40895,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048161</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -39490,6 +41025,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048163</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -39610,6 +41150,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048166</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -39730,6 +41275,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048168</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -39855,6 +41405,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048169</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -39985,6 +41540,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048171</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -40110,6 +41670,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048174</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -40240,6 +41805,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048177</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -40365,6 +41935,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048181</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -40490,6 +42065,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048182</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -40615,6 +42195,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048185</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -40740,6 +42325,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048186</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -40865,6 +42455,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048187</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -40990,6 +42585,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048188</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -41115,6 +42715,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048191</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -41240,6 +42845,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048192</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -41365,6 +42975,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048195</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -41490,6 +43105,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048196</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -41610,6 +43230,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048198</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -41735,6 +43360,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048199</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -41860,6 +43490,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048200</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -41985,6 +43620,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048201</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -42110,6 +43750,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048227</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -42235,6 +43880,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048229</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -42360,6 +44010,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048231</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -42490,6 +44145,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048234</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -42615,6 +44275,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048236</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -42740,6 +44405,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048237</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -42865,6 +44535,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048238</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -42990,6 +44665,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048239</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -43120,6 +44800,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048241</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -43245,6 +44930,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048243</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -43375,6 +45065,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048244</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -43505,6 +45200,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048247</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -43635,6 +45335,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048248</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -43765,6 +45470,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048253</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -43895,6 +45605,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048255</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -44020,6 +45735,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048258</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -44150,6 +45870,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048259</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -44280,6 +46005,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048260</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -44410,6 +46140,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048278</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -44530,6 +46265,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048282</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -44650,6 +46390,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048283</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -44770,6 +46515,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048285</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -44900,6 +46650,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048288</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -45030,6 +46785,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048289</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -45160,6 +46920,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048293</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -45280,6 +47045,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048298</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -45400,6 +47170,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048306</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -45520,6 +47295,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048307</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -45640,6 +47420,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048313</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -45765,6 +47550,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048314</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -45885,6 +47675,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048316</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -46005,6 +47800,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048371</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -46125,6 +47925,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048376</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -46245,6 +48050,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048378</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -46365,6 +48175,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048391</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -46485,6 +48300,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048413</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -46605,6 +48425,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048433</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -46725,6 +48550,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048495</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -46845,6 +48675,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130048539</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -46977,6 +48812,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73078571</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -47102,6 +48942,11 @@
           <t xml:space="preserve">SKB groddjursinventeringar </t>
         </is>
       </c>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103952241</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -47227,6 +49072,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049814</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -47357,6 +49207,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049815</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -47487,6 +49342,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049819</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -47617,6 +49477,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049820</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -47737,6 +49602,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049828</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -47857,6 +49727,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049829</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -47977,6 +49852,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049830</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -48097,6 +49977,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049831</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -48217,6 +50102,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049832</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -48337,6 +50227,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049834</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -48457,6 +50352,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049837</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -48577,6 +50477,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049838</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -48697,6 +50602,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049840</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -48827,6 +50737,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049842</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -48947,6 +50862,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049843</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -49067,6 +50987,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049844</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -49197,6 +51122,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049846</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -49317,6 +51247,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049848</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -49437,6 +51372,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049851</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -49557,6 +51497,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049855</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -49677,6 +51622,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049856</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -49797,6 +51747,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049857</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -49917,6 +51872,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049861</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -50037,6 +51997,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049863</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -50157,6 +52122,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049864</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -50277,6 +52247,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049865</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -50407,6 +52382,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049786</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -50532,6 +52512,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049790</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -50662,6 +52647,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049791</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -50792,6 +52782,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049792</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -50912,6 +52907,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049793</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -51032,6 +53032,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049794</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -51152,6 +53157,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049795</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -51272,6 +53282,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049796</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -51392,6 +53407,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049797</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -51512,6 +53532,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049798</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -51632,6 +53657,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049800</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -51752,6 +53782,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049801</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -51872,6 +53907,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049803</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -51992,6 +54032,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049804</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -52112,6 +54157,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130049808</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -52232,6 +54282,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050692</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -52352,6 +54407,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050693</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -52472,6 +54532,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050697</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -52592,6 +54657,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050777</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -52712,6 +54782,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050778</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -52832,6 +54907,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050779</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -52952,6 +55032,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050781</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -53072,6 +55157,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050782</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -53190,6 +55280,11 @@
       <c r="AY419" t="inlineStr">
         <is>
           <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130050775</t>
         </is>
       </c>
     </row>
@@ -53303,6 +55398,11 @@
         </is>
       </c>
       <c r="AY420" t="inlineStr"/>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101130566</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -53414,6 +55514,11 @@
         </is>
       </c>
       <c r="AY421" t="inlineStr"/>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101130573</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -53525,6 +55630,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69990731</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -53636,6 +55746,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69990870</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -53747,8 +55862,438 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69988669</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>